--- a/test.xlsx
+++ b/test.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>|</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>мо</t>
+  </si>
+  <si>
+    <t>15.11.25</t>
   </si>
 </sst>
 </file>
@@ -694,7 +697,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1" s="11">
         <v>9</v>
@@ -782,7 +785,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="11">
         <v>9</v>
@@ -870,7 +873,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="11">
         <v>9</v>
@@ -958,7 +961,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="11">
         <v>9</v>
@@ -992,7 +995,9 @@
       <c r="A17" s="3"/>
       <c r="B17" s="10"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="2"/>
@@ -1006,7 +1011,9 @@
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+      <c r="D18" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="10"/>
@@ -1020,7 +1027,9 @@
       <c r="A19" s="9"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
+      <c r="D19" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="10"/>
@@ -1034,7 +1043,9 @@
       <c r="A20" s="9"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
+      <c r="D20" s="10" t="s">
+        <v>10</v>
+      </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="10"/>
@@ -1046,7 +1057,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B21" s="11">
         <v>9</v>
@@ -1080,9 +1091,7 @@
       <c r="A22" s="3"/>
       <c r="B22" s="10"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="2"/>
@@ -1096,9 +1105,7 @@
       <c r="A23" s="9"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="D23" s="10"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="10"/>
@@ -1112,9 +1119,7 @@
       <c r="A24" s="9"/>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
-      <c r="D24" s="10" t="s">
-        <v>9</v>
-      </c>
+      <c r="D24" s="10"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="10"/>
@@ -1128,9 +1133,7 @@
       <c r="A25" s="9"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
-      <c r="D25" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="D25" s="10"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="10"/>
@@ -1142,7 +1145,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B26" s="11">
         <v>9</v>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" s="11">
         <v>9</v>
@@ -1318,7 +1321,7 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" s="11">
         <v>9</v>
@@ -1406,7 +1409,7 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B41" s="11">
         <v>9</v>
@@ -1439,7 +1442,9 @@
     <row r="42" spans="1:10">
       <c r="A42" s="3"/>
       <c r="B42" s="10"/>
-      <c r="C42" s="2"/>
+      <c r="C42" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="D42" s="2"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -1453,7 +1458,9 @@
     <row r="43" spans="1:10">
       <c r="A43" s="9"/>
       <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
+      <c r="C43" s="10" t="s">
+        <v>16</v>
+      </c>
       <c r="D43" s="10"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -1467,7 +1474,9 @@
     <row r="44" spans="1:10">
       <c r="A44" s="9"/>
       <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
+      <c r="C44" s="10" t="s">
+        <v>17</v>
+      </c>
       <c r="D44" s="10"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -1481,7 +1490,9 @@
     <row r="45" spans="1:10">
       <c r="A45" s="9"/>
       <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
+      <c r="C45" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="D45" s="10"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -1494,7 +1505,7 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B46" s="11">
         <v>9</v>
@@ -1527,9 +1538,7 @@
     <row r="47" spans="1:10">
       <c r="A47" s="3"/>
       <c r="B47" s="10"/>
-      <c r="C47" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -1543,9 +1552,7 @@
     <row r="48" spans="1:10">
       <c r="A48" s="9"/>
       <c r="B48" s="10"/>
-      <c r="C48" s="10" t="s">
-        <v>16</v>
-      </c>
+      <c r="C48" s="10"/>
       <c r="D48" s="10"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -1559,9 +1566,7 @@
     <row r="49" spans="1:10">
       <c r="A49" s="9"/>
       <c r="B49" s="10"/>
-      <c r="C49" s="10" t="s">
-        <v>17</v>
-      </c>
+      <c r="C49" s="10"/>
       <c r="D49" s="10"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -1575,9 +1580,7 @@
     <row r="50" spans="1:10">
       <c r="A50" s="9"/>
       <c r="B50" s="10"/>
-      <c r="C50" s="10" t="s">
-        <v>18</v>
-      </c>
+      <c r="C50" s="10"/>
       <c r="D50" s="10"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -1590,7 +1593,7 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" s="11">
         <v>9</v>
@@ -1622,7 +1625,9 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="3"/>
-      <c r="B52" s="10"/>
+      <c r="B52" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="1"/>
@@ -1636,7 +1641,9 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="9"/>
-      <c r="B53" s="10"/>
+      <c r="B53" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
       <c r="E53" s="1"/>
@@ -1650,7 +1657,9 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="9"/>
-      <c r="B54" s="10"/>
+      <c r="B54" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
       <c r="E54" s="1"/>
@@ -1664,7 +1673,9 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="9"/>
-      <c r="B55" s="10"/>
+      <c r="B55" s="10" t="s">
+        <v>22</v>
+      </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
       <c r="E55" s="1"/>
@@ -1678,7 +1689,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B56" s="11">
         <v>9</v>
@@ -1710,9 +1721,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="3"/>
-      <c r="B57" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="B57" s="10"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="1"/>
@@ -1726,9 +1735,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="9"/>
-      <c r="B58" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="1"/>
@@ -1742,9 +1749,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="9"/>
-      <c r="B59" s="10" t="s">
-        <v>21</v>
-      </c>
+      <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="1"/>
@@ -1758,9 +1763,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="9"/>
-      <c r="B60" s="10" t="s">
-        <v>22</v>
-      </c>
+      <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="1"/>
@@ -1774,7 +1777,7 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B61" s="11">
         <v>9</v>
@@ -1808,11 +1811,15 @@
       <c r="A62" s="3"/>
       <c r="B62" s="10"/>
       <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="D62" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
+      <c r="H62" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="I62" s="2"/>
       <c r="J62" t="s">
         <v>0</v>
@@ -1822,11 +1829,15 @@
       <c r="A63" s="9"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
+      <c r="D63" s="10" t="s">
+        <v>10</v>
+      </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
+      <c r="H63" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="I63" s="10"/>
       <c r="J63" t="s">
         <v>0</v>
@@ -1836,11 +1847,15 @@
       <c r="A64" s="9"/>
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
+      <c r="D64" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
+      <c r="H64" s="10" t="s">
+        <v>28</v>
+      </c>
       <c r="I64" s="10"/>
       <c r="J64" t="s">
         <v>0</v>
@@ -1850,11 +1865,15 @@
       <c r="A65" s="9"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
+      <c r="D65" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
+      <c r="H65" s="10" t="s">
+        <v>29</v>
+      </c>
       <c r="I65" s="10"/>
       <c r="J65" t="s">
         <v>0</v>
@@ -1862,7 +1881,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B66" s="11">
         <v>9</v>
@@ -1896,15 +1915,11 @@
       <c r="A67" s="3"/>
       <c r="B67" s="10"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="D67" s="2"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" t="s">
         <v>0</v>
@@ -1914,15 +1929,11 @@
       <c r="A68" s="9"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
-      <c r="D68" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="D68" s="10"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="10"/>
-      <c r="H68" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="H68" s="10"/>
       <c r="I68" s="10"/>
       <c r="J68" t="s">
         <v>0</v>
@@ -1932,15 +1943,11 @@
       <c r="A69" s="9"/>
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
-      <c r="D69" s="10" t="s">
-        <v>27</v>
-      </c>
+      <c r="D69" s="10"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="10"/>
-      <c r="H69" s="10" t="s">
-        <v>28</v>
-      </c>
+      <c r="H69" s="10"/>
       <c r="I69" s="10"/>
       <c r="J69" t="s">
         <v>0</v>
@@ -1950,15 +1957,11 @@
       <c r="A70" s="9"/>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="10" t="s">
-        <v>25</v>
-      </c>
+      <c r="D70" s="10"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="10"/>
-      <c r="H70" s="10" t="s">
-        <v>29</v>
-      </c>
+      <c r="H70" s="10"/>
       <c r="I70" s="10"/>
       <c r="J70" t="s">
         <v>0</v>
@@ -1966,7 +1969,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B71" s="11">
         <v>9</v>
@@ -2002,7 +2005,9 @@
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
+      <c r="F72" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -2016,7 +2021,9 @@
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
+      <c r="F73" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="G73" s="10"/>
       <c r="H73" s="10"/>
       <c r="I73" s="10"/>
@@ -2030,7 +2037,9 @@
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
+      <c r="F74" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
       <c r="I74" s="10"/>
@@ -2044,7 +2053,9 @@
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
+      <c r="F75" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="G75" s="10"/>
       <c r="H75" s="10"/>
       <c r="I75" s="10"/>
@@ -2054,7 +2065,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B76" s="11">
         <v>9</v>
@@ -2088,12 +2099,14 @@
       <c r="A77" s="3"/>
       <c r="B77" s="10"/>
       <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
+      <c r="D77" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E77" s="1"/>
-      <c r="F77" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G77" s="2"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" t="s">
@@ -2104,12 +2117,14 @@
       <c r="A78" s="9"/>
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
+      <c r="D78" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="E78" s="1"/>
-      <c r="F78" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G78" s="10"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="H78" s="10"/>
       <c r="I78" s="10"/>
       <c r="J78" t="s">
@@ -2120,12 +2135,14 @@
       <c r="A79" s="9"/>
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
+      <c r="D79" s="10" t="s">
+        <v>37</v>
+      </c>
       <c r="E79" s="1"/>
-      <c r="F79" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G79" s="10"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="H79" s="10"/>
       <c r="I79" s="10"/>
       <c r="J79" t="s">
@@ -2136,12 +2153,14 @@
       <c r="A80" s="9"/>
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
+      <c r="D80" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="E80" s="1"/>
-      <c r="F80" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G80" s="10"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="H80" s="10"/>
       <c r="I80" s="10"/>
       <c r="J80" t="s">
@@ -2149,112 +2168,60 @@
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B81" s="11">
-        <v>9</v>
-      </c>
-      <c r="C81" s="4">
-        <v>10</v>
-      </c>
-      <c r="D81" s="6">
-        <v>11</v>
-      </c>
-      <c r="E81" s="4">
-        <v>14</v>
-      </c>
-      <c r="F81" s="8">
-        <v>15</v>
-      </c>
-      <c r="G81" s="7">
-        <v>16</v>
-      </c>
-      <c r="H81" s="4">
-        <v>17</v>
-      </c>
-      <c r="I81" s="4">
-        <v>18</v>
+      <c r="A81" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" t="s">
+        <v>42</v>
+      </c>
+      <c r="C81" t="s">
+        <v>43</v>
+      </c>
+      <c r="D81" t="s">
+        <v>44</v>
+      </c>
+      <c r="E81" t="s">
+        <v>45</v>
+      </c>
+      <c r="F81" t="s">
+        <v>46</v>
+      </c>
+      <c r="G81" t="s">
+        <v>47</v>
+      </c>
+      <c r="H81" t="s">
+        <v>48</v>
+      </c>
+      <c r="I81" t="s">
+        <v>49</v>
       </c>
       <c r="J81" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="3"/>
-      <c r="B82" s="10"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
       <c r="J82" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="9"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
       <c r="J83" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="9"/>
-      <c r="B84" s="10"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H84" s="10"/>
-      <c r="I84" s="10"/>
       <c r="J84" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="9"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
       <c r="J85" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B86" t="s">
         <v>42</v>
@@ -2306,7 +2273,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B91" t="s">
         <v>42</v>
@@ -2358,7 +2325,7 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B96" t="s">
         <v>42</v>
@@ -2389,28 +2356,40 @@
       </c>
     </row>
     <row r="97" spans="1:10">
+      <c r="E97" t="s">
+        <v>54</v>
+      </c>
       <c r="J97" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:10">
+      <c r="E98" t="s">
+        <v>55</v>
+      </c>
       <c r="J98" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:10">
+      <c r="E99" t="s">
+        <v>56</v>
+      </c>
       <c r="J99" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:10">
+      <c r="E100" t="s">
+        <v>57</v>
+      </c>
       <c r="J100" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B101" t="s">
         <v>42</v>
@@ -2441,40 +2420,28 @@
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="E102" t="s">
-        <v>54</v>
-      </c>
       <c r="J102" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="E103" t="s">
-        <v>55</v>
-      </c>
       <c r="J103" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="E104" t="s">
-        <v>56</v>
-      </c>
       <c r="J104" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="E105" t="s">
-        <v>57</v>
-      </c>
       <c r="J105" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B106" t="s">
         <v>42</v>
@@ -2505,28 +2472,40 @@
       </c>
     </row>
     <row r="107" spans="1:10">
+      <c r="H107" t="s">
+        <v>59</v>
+      </c>
       <c r="J107" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:10">
+      <c r="H108" t="s">
+        <v>60</v>
+      </c>
       <c r="J108" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:10">
+      <c r="H109" t="s">
+        <v>61</v>
+      </c>
       <c r="J109" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:10">
+      <c r="H110" t="s">
+        <v>62</v>
+      </c>
       <c r="J110" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B111" t="s">
         <v>42</v>
@@ -2557,40 +2536,28 @@
       </c>
     </row>
     <row r="112" spans="1:10">
-      <c r="H112" t="s">
-        <v>59</v>
-      </c>
       <c r="J112" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="H113" t="s">
-        <v>60</v>
-      </c>
       <c r="J113" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="H114" t="s">
-        <v>61</v>
-      </c>
       <c r="J114" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="H115" t="s">
-        <v>62</v>
-      </c>
       <c r="J115" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B116" t="s">
         <v>42</v>
@@ -2642,7 +2609,7 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B121" t="s">
         <v>42</v>
@@ -2673,28 +2640,40 @@
       </c>
     </row>
     <row r="122" spans="1:10">
+      <c r="D122" t="s">
+        <v>67</v>
+      </c>
       <c r="J122" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:10">
+      <c r="D123" t="s">
+        <v>68</v>
+      </c>
       <c r="J123" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:10">
+      <c r="D124" t="s">
+        <v>56</v>
+      </c>
       <c r="J124" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:10">
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
       <c r="J125" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:10">
       <c r="A126" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B126" t="s">
         <v>42</v>
@@ -2725,23 +2704,23 @@
       </c>
     </row>
     <row r="127" spans="1:10">
-      <c r="D127" t="s">
-        <v>67</v>
+      <c r="C127" t="s">
+        <v>71</v>
       </c>
       <c r="J127" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="D128" t="s">
-        <v>68</v>
+      <c r="C128" t="s">
+        <v>72</v>
       </c>
       <c r="J128" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="D129" t="s">
+      <c r="C129" t="s">
         <v>56</v>
       </c>
       <c r="J129" t="s">
@@ -2749,8 +2728,8 @@
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="D130" t="s">
-        <v>69</v>
+      <c r="C130" t="s">
+        <v>71</v>
       </c>
       <c r="J130" t="s">
         <v>0</v>
@@ -2758,7 +2737,7 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B131" t="s">
         <v>42</v>
@@ -2789,23 +2768,23 @@
       </c>
     </row>
     <row r="132" spans="1:10">
-      <c r="C132" t="s">
-        <v>71</v>
+      <c r="D132" t="s">
+        <v>74</v>
       </c>
       <c r="J132" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="C133" t="s">
-        <v>72</v>
+      <c r="D133" t="s">
+        <v>75</v>
       </c>
       <c r="J133" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="C134" t="s">
+      <c r="D134" t="s">
         <v>56</v>
       </c>
       <c r="J134" t="s">
@@ -2813,8 +2792,8 @@
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="C135" t="s">
-        <v>71</v>
+      <c r="D135" t="s">
+        <v>76</v>
       </c>
       <c r="J135" t="s">
         <v>0</v>
@@ -2822,7 +2801,7 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B136" t="s">
         <v>42</v>
@@ -2833,8 +2812,8 @@
       <c r="D136" t="s">
         <v>44</v>
       </c>
-      <c r="E136" t="s">
-        <v>45</v>
+      <c r="E136">
+        <v>14</v>
       </c>
       <c r="F136" t="s">
         <v>46</v>
@@ -2853,32 +2832,32 @@
       </c>
     </row>
     <row r="137" spans="1:10">
-      <c r="D137" t="s">
-        <v>74</v>
+      <c r="E137" t="s">
+        <v>79</v>
       </c>
       <c r="J137" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="D138" t="s">
-        <v>75</v>
+      <c r="E138" t="s">
+        <v>79</v>
       </c>
       <c r="J138" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="D139" t="s">
-        <v>56</v>
+      <c r="E139" t="s">
+        <v>79</v>
       </c>
       <c r="J139" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="D140" t="s">
-        <v>76</v>
+      <c r="E140" t="s">
+        <v>78</v>
       </c>
       <c r="J140" t="s">
         <v>0</v>
@@ -2886,7 +2865,7 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B141" t="s">
         <v>42</v>
@@ -2897,8 +2876,8 @@
       <c r="D141" t="s">
         <v>44</v>
       </c>
-      <c r="E141">
-        <v>14</v>
+      <c r="E141" t="s">
+        <v>45</v>
       </c>
       <c r="F141" t="s">
         <v>46</v>
@@ -2917,7 +2896,7 @@
       </c>
     </row>
     <row r="142" spans="1:10">
-      <c r="E142" t="s">
+      <c r="D142" t="s">
         <v>79</v>
       </c>
       <c r="J142" t="s">
@@ -2925,7 +2904,7 @@
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="E143" t="s">
+      <c r="D143" t="s">
         <v>79</v>
       </c>
       <c r="J143" t="s">
@@ -2933,7 +2912,7 @@
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="E144" t="s">
+      <c r="D144" t="s">
         <v>79</v>
       </c>
       <c r="J144" t="s">
@@ -2941,16 +2920,16 @@
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="E145" t="s">
-        <v>78</v>
+      <c r="D145" t="s">
+        <v>79</v>
       </c>
       <c r="J145" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146">
       <c r="A146" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B146" t="s">
         <v>42</v>
@@ -2980,41 +2959,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
-      <c r="D147" t="s">
-        <v>79</v>
-      </c>
+    <row r="147">
       <c r="J147" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
-      <c r="D148" t="s">
-        <v>79</v>
-      </c>
+    <row r="148">
       <c r="J148" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
-      <c r="D149" t="s">
-        <v>79</v>
-      </c>
+    <row r="149">
       <c r="J149" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
-      <c r="D150" t="s">
-        <v>79</v>
-      </c>
+    <row r="150">
       <c r="J150" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B151" t="s">
         <v>42</v>

--- a/test.xlsx
+++ b/test.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>1.10.2025</t>
   </si>
@@ -231,6 +231,78 @@
   </si>
   <si>
     <t>хочу тортик тирамису</t>
+  </si>
+  <si>
+    <t>89157447546</t>
+  </si>
+  <si>
+    <t>поарапоа</t>
+  </si>
+  <si>
+    <t>Алсуш</t>
+  </si>
+  <si>
+    <t>Нагиева</t>
+  </si>
+  <si>
+    <t>+79000179800</t>
+  </si>
+  <si>
+    <t>мяумямулютебякотик</t>
+  </si>
+  <si>
+    <t>Максимка</t>
+  </si>
+  <si>
+    <t>Новикова</t>
+  </si>
+  <si>
+    <t>Мяумямямямя</t>
+  </si>
+  <si>
+    <t>пибл</t>
+  </si>
+  <si>
+    <t>пибловский</t>
+  </si>
+  <si>
+    <t>+79457891234</t>
+  </si>
+  <si>
+    <t>ваш май бэли</t>
+  </si>
+  <si>
+    <t>Няшка</t>
+  </si>
+  <si>
+    <t>Милашкинс</t>
+  </si>
+  <si>
+    <t>89000179800</t>
+  </si>
+  <si>
+    <t>ныгяшфнйой</t>
+  </si>
+  <si>
+    <t>Алсо</t>
+  </si>
+  <si>
+    <t>Пидараска</t>
+  </si>
+  <si>
+    <t>быбыбыбуббебебебеб</t>
+  </si>
+  <si>
+    <t>героинчик</t>
+  </si>
+  <si>
+    <t>мяммямямя</t>
+  </si>
+  <si>
+    <t>поопоа</t>
+  </si>
+  <si>
+    <t>сосоп</t>
   </si>
 </sst>
 </file>
@@ -4051,8 +4123,12 @@
       <c r="B127" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
+      <c r="C127" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
       <c r="G127" s="9"/>
@@ -4067,8 +4143,12 @@
       <c r="B128" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C128" s="39"/>
-      <c r="D128" s="39"/>
+      <c r="C128" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="D128" s="39" t="s">
+        <v>77</v>
+      </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="39"/>
@@ -4083,8 +4163,12 @@
       <c r="B129" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C129" s="39"/>
-      <c r="D129" s="39"/>
+      <c r="C129" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="D129" s="39" t="s">
+        <v>78</v>
+      </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
       <c r="G129" s="39"/>
@@ -4099,8 +4183,12 @@
       <c r="B130" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="C130" s="39"/>
-      <c r="D130" s="39"/>
+      <c r="C130" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D130" s="39" t="s">
+        <v>79</v>
+      </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="39"/>
@@ -4144,10 +4232,18 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="12"/>
-      <c r="B132" s="39"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="5"/>
+      <c r="B132" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="F132" s="5"/>
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
@@ -4158,10 +4254,18 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="36"/>
-      <c r="B133" s="39"/>
-      <c r="C133" s="39"/>
-      <c r="D133" s="39"/>
-      <c r="E133" s="5"/>
+      <c r="B133" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C133" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="D133" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="F133" s="5"/>
       <c r="G133" s="39"/>
       <c r="H133" s="39"/>
@@ -4172,10 +4276,18 @@
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="36"/>
-      <c r="B134" s="39"/>
-      <c r="C134" s="39"/>
-      <c r="D134" s="39"/>
-      <c r="E134" s="5"/>
+      <c r="B134" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C134" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="D134" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="F134" s="5"/>
       <c r="G134" s="39"/>
       <c r="H134" s="39"/>
@@ -4186,10 +4298,18 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="36"/>
-      <c r="B135" s="39"/>
-      <c r="C135" s="39"/>
-      <c r="D135" s="39"/>
-      <c r="E135" s="5"/>
+      <c r="B135" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C135" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="D135" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="F135" s="5"/>
       <c r="G135" s="39"/>
       <c r="H135" s="39"/>
@@ -4233,11 +4353,15 @@
     <row r="137" spans="1:10">
       <c r="A137" s="12"/>
       <c r="B137" s="39"/>
-      <c r="C137" s="9"/>
+      <c r="C137" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="D137" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E137" s="5"/>
+      <c r="E137" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="F137" s="5"/>
       <c r="G137" s="9"/>
       <c r="H137" s="9" t="s">
@@ -4251,11 +4375,15 @@
     <row r="138" spans="1:10">
       <c r="A138" s="36"/>
       <c r="B138" s="39"/>
-      <c r="C138" s="39"/>
+      <c r="C138" s="39" t="s">
+        <v>70</v>
+      </c>
       <c r="D138" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="E138" s="5"/>
+      <c r="E138" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="F138" s="5"/>
       <c r="G138" s="39"/>
       <c r="H138" s="39" t="s">
@@ -4269,11 +4397,15 @@
     <row r="139" spans="1:10">
       <c r="A139" s="36"/>
       <c r="B139" s="39"/>
-      <c r="C139" s="39"/>
+      <c r="C139" s="39" t="s">
+        <v>71</v>
+      </c>
       <c r="D139" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="E139" s="5"/>
+      <c r="E139" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="F139" s="5"/>
       <c r="G139" s="39"/>
       <c r="H139" s="39" t="s">
@@ -4287,11 +4419,15 @@
     <row r="140" spans="1:10">
       <c r="A140" s="36"/>
       <c r="B140" s="39"/>
-      <c r="C140" s="39"/>
+      <c r="C140" s="39" t="s">
+        <v>72</v>
+      </c>
       <c r="D140" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E140" s="5"/>
+      <c r="E140" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="F140" s="5"/>
       <c r="G140" s="39"/>
       <c r="H140" s="39" t="s">
@@ -4521,7 +4657,9 @@
     <row r="152" spans="1:10">
       <c r="A152" s="12"/>
       <c r="B152" s="39"/>
-      <c r="C152" s="9"/>
+      <c r="C152" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="D152" s="9" t="s">
         <v>51</v>
       </c>
@@ -4539,7 +4677,9 @@
     <row r="153" spans="1:10">
       <c r="A153" s="36"/>
       <c r="B153" s="39"/>
-      <c r="C153" s="39"/>
+      <c r="C153" s="39" t="s">
+        <v>45</v>
+      </c>
       <c r="D153" s="39" t="s">
         <v>45</v>
       </c>
@@ -4557,7 +4697,9 @@
     <row r="154" spans="1:10">
       <c r="A154" s="36"/>
       <c r="B154" s="39"/>
-      <c r="C154" s="39"/>
+      <c r="C154" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="D154" s="39" t="s">
         <v>59</v>
       </c>
@@ -4575,7 +4717,9 @@
     <row r="155" spans="1:10">
       <c r="A155" s="36"/>
       <c r="B155" s="39"/>
-      <c r="C155" s="39"/>
+      <c r="C155" s="39" t="s">
+        <v>68</v>
+      </c>
       <c r="D155" s="39" t="s">
         <v>60</v>
       </c>

--- a/test.xlsx
+++ b/test.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>1.10.2025</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>сосоп</t>
+  </si>
+  <si>
+    <t>стаоа</t>
   </si>
 </sst>
 </file>
@@ -4474,7 +4477,9 @@
       <c r="A142" s="12"/>
       <c r="B142" s="39"/>
       <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
+      <c r="D142" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="9"/>
@@ -4488,7 +4493,9 @@
       <c r="A143" s="36"/>
       <c r="B143" s="39"/>
       <c r="C143" s="39"/>
-      <c r="D143" s="39"/>
+      <c r="D143" s="39" t="s">
+        <v>45</v>
+      </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="39"/>
@@ -4502,7 +4509,9 @@
       <c r="A144" s="36"/>
       <c r="B144" s="39"/>
       <c r="C144" s="39"/>
-      <c r="D144" s="39"/>
+      <c r="D144" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="39"/>
@@ -4516,7 +4525,9 @@
       <c r="A145" s="36"/>
       <c r="B145" s="39"/>
       <c r="C145" s="39"/>
-      <c r="D145" s="39"/>
+      <c r="D145" s="39" t="s">
+        <v>91</v>
+      </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
       <c r="G145" s="39"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -30,9 +30,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
-  <si>
-    <t>1.10.2025</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+  <si>
+    <t>1.10.25</t>
   </si>
   <si>
     <t>|</t>
@@ -65,94 +65,85 @@
     <t>bgdgdfg</t>
   </si>
   <si>
-    <t>2.10.2025</t>
-  </si>
-  <si>
-    <t>3.10.2025</t>
-  </si>
-  <si>
-    <t>4.10.2025</t>
-  </si>
-  <si>
-    <t>5.10.2025</t>
-  </si>
-  <si>
-    <t>6.10.2025</t>
-  </si>
-  <si>
-    <t>7.10.2025</t>
-  </si>
-  <si>
-    <t>8.10.2025</t>
-  </si>
-  <si>
-    <t>9.10.2025</t>
-  </si>
-  <si>
-    <t>10.10.2025</t>
-  </si>
-  <si>
-    <t>11.10.2025</t>
-  </si>
-  <si>
-    <t>12.10.2025</t>
-  </si>
-  <si>
-    <t>13.10.2025</t>
-  </si>
-  <si>
-    <t>14.10.2025</t>
-  </si>
-  <si>
-    <t>15.10.2025</t>
-  </si>
-  <si>
-    <t>16.10.2025</t>
-  </si>
-  <si>
-    <t>17.10.2025</t>
-  </si>
-  <si>
-    <t>18.10.2025</t>
-  </si>
-  <si>
-    <t>19.10.2025</t>
-  </si>
-  <si>
-    <t>20.10.2025</t>
-  </si>
-  <si>
-    <t>21.10.2025</t>
-  </si>
-  <si>
-    <t>22.10.2025</t>
-  </si>
-  <si>
-    <t>23.10.2025</t>
-  </si>
-  <si>
-    <t>24.10.2025</t>
-  </si>
-  <si>
-    <t>25.10.2025</t>
-  </si>
-  <si>
-    <t>26.10.2025</t>
-  </si>
-  <si>
-    <t>27.10.2025</t>
-  </si>
-  <si>
-    <t>28.10.2025</t>
-  </si>
-  <si>
-    <t>29.10.2025</t>
-  </si>
-  <si>
-    <t>30.10.2025</t>
-  </si>
-  <si>
-    <t>31.10.2025</t>
+    <t>2.10.25</t>
+  </si>
+  <si>
+    <t>3.10.25</t>
+  </si>
+  <si>
+    <t>4.10.25</t>
+  </si>
+  <si>
+    <t>5.10.25</t>
+  </si>
+  <si>
+    <t>6.10.25</t>
+  </si>
+  <si>
+    <t>7.10.25</t>
+  </si>
+  <si>
+    <t>8.10.25</t>
+  </si>
+  <si>
+    <t>9.10.25</t>
+  </si>
+  <si>
+    <t>10.10.25</t>
+  </si>
+  <si>
+    <t>11.10.25</t>
+  </si>
+  <si>
+    <t>12.10.25</t>
+  </si>
+  <si>
+    <t>13.10.25</t>
+  </si>
+  <si>
+    <t>14.10.25</t>
+  </si>
+  <si>
+    <t>15.10.25</t>
+  </si>
+  <si>
+    <t>16.10.25</t>
+  </si>
+  <si>
+    <t>17.10.25</t>
+  </si>
+  <si>
+    <t>18.10.25</t>
+  </si>
+  <si>
+    <t>19.10.25</t>
+  </si>
+  <si>
+    <t>максим</t>
+  </si>
+  <si>
+    <t>новиков</t>
+  </si>
+  <si>
+    <t>по оа</t>
+  </si>
+  <si>
+    <t>аоа</t>
+  </si>
+  <si>
+    <t>20.10.25</t>
+  </si>
+  <si>
+    <t>21.10.25</t>
+  </si>
+  <si>
+    <t>22.10.25</t>
+  </si>
+  <si>
+    <t>23.10.25</t>
+  </si>
+  <si>
+    <t>24.10.25</t>
   </si>
   <si>
     <t>поа</t>
@@ -164,148 +155,169 @@
     <t>моп</t>
   </si>
   <si>
+    <t>25.10.25</t>
+  </si>
+  <si>
+    <t>хело</t>
+  </si>
+  <si>
+    <t>кити</t>
+  </si>
+  <si>
+    <t>0045</t>
+  </si>
+  <si>
+    <t>хочу тортик тирамису</t>
+  </si>
+  <si>
+    <t>26.10.25</t>
+  </si>
+  <si>
+    <t>пибл</t>
+  </si>
+  <si>
+    <t>пибловский</t>
+  </si>
+  <si>
+    <t>аооа</t>
+  </si>
+  <si>
+    <t>89157447546</t>
+  </si>
+  <si>
+    <t>+79457891234</t>
+  </si>
+  <si>
+    <t>ар Ра</t>
+  </si>
+  <si>
+    <t>сосоп</t>
+  </si>
+  <si>
+    <t>ваш май бэли</t>
+  </si>
+  <si>
+    <t>27.10.25</t>
+  </si>
+  <si>
+    <t>Няшка</t>
+  </si>
+  <si>
+    <t>Максимка</t>
+  </si>
+  <si>
+    <t>Алсо</t>
+  </si>
+  <si>
     <t>алсу</t>
   </si>
   <si>
-    <t>новиков</t>
+    <t>Милашкинс</t>
+  </si>
+  <si>
+    <t>Новикова</t>
+  </si>
+  <si>
+    <t>Пидараска</t>
+  </si>
+  <si>
+    <t>героинчик</t>
+  </si>
+  <si>
+    <t>89000179800</t>
+  </si>
+  <si>
+    <t>+79000179800</t>
+  </si>
+  <si>
+    <t>ныгяшфнйой</t>
+  </si>
+  <si>
+    <t>Мяумямямямя</t>
+  </si>
+  <si>
+    <t>быбыбыбуббебебебеб</t>
+  </si>
+  <si>
+    <t>мяммямямя</t>
+  </si>
+  <si>
+    <t>28.10.25</t>
+  </si>
+  <si>
+    <t>Алсуш</t>
+  </si>
+  <si>
+    <t>аопо</t>
+  </si>
+  <si>
+    <t>Нагиева</t>
+  </si>
+  <si>
+    <t>вооа</t>
   </si>
   <si>
     <t>000171</t>
   </si>
   <si>
+    <t>мяумямулютебякотик</t>
+  </si>
+  <si>
+    <t>поопоа</t>
+  </si>
+  <si>
     <t>мямя</t>
   </si>
   <si>
-    <t>аопо</t>
-  </si>
-  <si>
-    <t>аоа</t>
-  </si>
-  <si>
-    <t>вооа</t>
-  </si>
-  <si>
-    <t>максим</t>
+    <t>29.10.25</t>
+  </si>
+  <si>
+    <t>стаоа</t>
+  </si>
+  <si>
+    <t>30.10.25</t>
+  </si>
+  <si>
+    <t>Рао</t>
+  </si>
+  <si>
+    <t>Ара</t>
+  </si>
+  <si>
+    <t>Поп</t>
+  </si>
+  <si>
+    <t>Аоп</t>
+  </si>
+  <si>
+    <t>31.10.25</t>
+  </si>
+  <si>
+    <t>ар им</t>
   </si>
   <si>
     <t>оаоп</t>
   </si>
   <si>
+    <t>поарапоа</t>
+  </si>
+  <si>
+    <t>арар</t>
+  </si>
+  <si>
     <t>врра</t>
   </si>
   <si>
-    <t>Рао</t>
-  </si>
-  <si>
-    <t>Ара</t>
-  </si>
-  <si>
-    <t>Поп</t>
-  </si>
-  <si>
-    <t>Аоп</t>
-  </si>
-  <si>
-    <t>по оа</t>
-  </si>
-  <si>
-    <t>ар им</t>
-  </si>
-  <si>
-    <t>арар</t>
-  </si>
-  <si>
-    <t>аооа</t>
-  </si>
-  <si>
-    <t>ар Ра</t>
-  </si>
-  <si>
-    <t>хело</t>
-  </si>
-  <si>
-    <t>кити</t>
-  </si>
-  <si>
-    <t>0045</t>
-  </si>
-  <si>
-    <t>хочу тортик тирамису</t>
-  </si>
-  <si>
-    <t>89157447546</t>
-  </si>
-  <si>
-    <t>поарапоа</t>
-  </si>
-  <si>
-    <t>Алсуш</t>
-  </si>
-  <si>
-    <t>Нагиева</t>
-  </si>
-  <si>
-    <t>+79000179800</t>
-  </si>
-  <si>
-    <t>мяумямулютебякотик</t>
-  </si>
-  <si>
-    <t>Максимка</t>
-  </si>
-  <si>
-    <t>Новикова</t>
-  </si>
-  <si>
-    <t>Мяумямямямя</t>
-  </si>
-  <si>
-    <t>пибл</t>
-  </si>
-  <si>
-    <t>пибловский</t>
-  </si>
-  <si>
-    <t>+79457891234</t>
-  </si>
-  <si>
-    <t>ваш май бэли</t>
-  </si>
-  <si>
-    <t>Няшка</t>
-  </si>
-  <si>
-    <t>Милашкинс</t>
-  </si>
-  <si>
-    <t>89000179800</t>
-  </si>
-  <si>
-    <t>ныгяшфнйой</t>
-  </si>
-  <si>
-    <t>Алсо</t>
-  </si>
-  <si>
-    <t>Пидараска</t>
-  </si>
-  <si>
-    <t>быбыбыбуббебебебеб</t>
-  </si>
-  <si>
-    <t>героинчик</t>
-  </si>
-  <si>
-    <t>мяммямямя</t>
-  </si>
-  <si>
-    <t>поопоа</t>
-  </si>
-  <si>
-    <t>сосоп</t>
-  </si>
-  <si>
-    <t>стаоа</t>
+    <t>поао</t>
+  </si>
+  <si>
+    <t>попр</t>
+  </si>
+  <si>
+    <t>89157446546</t>
+  </si>
+  <si>
+    <t>аооппо</t>
   </si>
 </sst>
 </file>
@@ -536,9 +548,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -562,9 +571,6 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -600,6 +606,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -902,31 +914,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="18.75" customHeight="true">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34">
+      <c r="B1" s="32">
         <v>9</v>
       </c>
-      <c r="C1" s="25">
+      <c r="C1" s="24">
         <v>10</v>
       </c>
-      <c r="D1" s="25">
+      <c r="D1" s="24">
         <v>11</v>
       </c>
-      <c r="E1" s="25">
+      <c r="E1" s="24">
         <v>14</v>
       </c>
-      <c r="F1" s="35">
+      <c r="F1" s="33">
         <v>15</v>
       </c>
-      <c r="G1" s="25">
+      <c r="G1" s="24">
         <v>16</v>
       </c>
-      <c r="H1" s="25">
+      <c r="H1" s="24">
         <v>17</v>
       </c>
-      <c r="I1" s="25">
+      <c r="I1" s="24">
         <v>18</v>
       </c>
       <c r="J1" t="s">
@@ -941,20 +953,20 @@
       <c r="U1" s="6"/>
       <c r="V1" s="6"/>
       <c r="W1" s="6"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="43"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
     </row>
     <row r="2" spans="1:34">
-      <c r="A2" s="36"/>
+      <c r="A2" s="34"/>
       <c r="B2" s="13" t="s">
         <v>2</v>
       </c>
@@ -987,20 +999,20 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
       <c r="AG2" s="1"/>
       <c r="AH2" s="1"/>
     </row>
     <row r="3" spans="1:34">
-      <c r="A3" s="36"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
@@ -1033,20 +1045,20 @@
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
       <c r="AG3" s="1"/>
       <c r="AH3" s="1"/>
     </row>
     <row r="4" spans="1:34">
-      <c r="A4" s="36"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="5">
         <v>54656</v>
       </c>
@@ -1092,7 +1104,7 @@
       <c r="AH4" s="1"/>
     </row>
     <row r="5" spans="1:34">
-      <c r="A5" s="36"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -1138,31 +1150,31 @@
       <c r="AH5" s="1"/>
     </row>
     <row r="6" spans="1:34">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="35">
         <v>9</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>10</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="26">
         <v>11</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="26">
         <v>14</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="36">
         <v>15</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="26">
         <v>16</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="26">
         <v>17</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="26">
         <v>18</v>
       </c>
       <c r="J6" t="s">
@@ -1185,18 +1197,18 @@
     </row>
     <row r="7" spans="1:34">
       <c r="A7" s="12"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
       <c r="D7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
       <c r="G7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
       <c r="J7" t="s">
         <v>1</v>
       </c>
@@ -1204,11 +1216,11 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="23"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
@@ -1216,19 +1228,19 @@
       <c r="AF7" s="6"/>
     </row>
     <row r="8" spans="1:34">
-      <c r="A8" s="36"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
       <c r="D8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
       <c r="G8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
       <c r="J8" t="s">
         <v>1</v>
       </c>
@@ -1236,11 +1248,11 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
+      <c r="W8" s="44"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="44"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="44"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -1248,19 +1260,19 @@
       <c r="AF8" s="6"/>
     </row>
     <row r="9" spans="1:34">
-      <c r="A9" s="36"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="16">
         <v>6574565</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
       <c r="G9" s="16">
         <v>3129792</v>
       </c>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
       <c r="J9" t="s">
         <v>1</v>
       </c>
@@ -1269,8 +1281,8 @@
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="4"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
@@ -1280,19 +1292,19 @@
       <c r="AF9" s="6"/>
     </row>
     <row r="10" spans="1:34">
-      <c r="A10" s="36"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
       <c r="D10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
       <c r="G10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
       <c r="J10" t="s">
         <v>1</v>
       </c>
@@ -1312,31 +1324,31 @@
       <c r="AF10" s="6"/>
     </row>
     <row r="11" spans="1:34">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="32">
         <v>9</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="24">
         <v>10</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="24">
         <v>11</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="24">
         <v>14</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="33">
         <v>15</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="24">
         <v>16</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="24">
         <v>17</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="24">
         <v>18</v>
       </c>
       <c r="J11" t="s">
@@ -1359,11 +1371,11 @@
     </row>
     <row r="12" spans="1:34">
       <c r="A12" s="12"/>
-      <c r="B12" s="41"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
-      <c r="F12" s="42"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
@@ -1387,14 +1399,14 @@
     </row>
     <row r="13" spans="1:34">
       <c r="A13" s="12"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
       <c r="J13" t="s">
         <v>1</v>
       </c>
@@ -1414,15 +1426,15 @@
       <c r="AF13" s="6"/>
     </row>
     <row r="14" spans="1:34">
-      <c r="A14" s="36"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
       <c r="J14" t="s">
         <v>1</v>
       </c>
@@ -1442,15 +1454,15 @@
       <c r="AF14" s="6"/>
     </row>
     <row r="15" spans="1:34">
-      <c r="A15" s="36"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
       <c r="J15" t="s">
         <v>1</v>
       </c>
@@ -1470,31 +1482,31 @@
       <c r="AF15" s="6"/>
     </row>
     <row r="16" spans="1:34">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="41">
         <v>9</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>10</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="26">
         <v>11</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="24">
         <v>14</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="33">
         <v>15</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="24">
         <v>16</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="24">
         <v>17</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="24">
         <v>18</v>
       </c>
       <c r="J16" t="s">
@@ -1604,7 +1616,7 @@
       <c r="AF18" s="6"/>
     </row>
     <row r="19" spans="1:32">
-      <c r="A19" s="36"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="5">
         <v>6574565</v>
       </c>
@@ -1648,7 +1660,7 @@
       <c r="AF19" s="6"/>
     </row>
     <row r="20" spans="1:32">
-      <c r="A20" s="36"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
@@ -1684,7 +1696,7 @@
       <c r="X20" s="17"/>
       <c r="Y20" s="17"/>
       <c r="Z20" s="17"/>
-      <c r="AA20" s="23"/>
+      <c r="AA20" s="31"/>
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="2"/>
@@ -1692,31 +1704,31 @@
       <c r="AF20" s="6"/>
     </row>
     <row r="21" spans="1:32">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="35">
         <v>9</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>10</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="26">
         <v>11</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="26">
         <v>14</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="36">
         <v>15</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="26">
         <v>16</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="26">
         <v>17</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="26">
         <v>18</v>
       </c>
       <c r="J21" t="s">
@@ -1730,7 +1742,7 @@
       <c r="X21" s="17"/>
       <c r="Y21" s="17"/>
       <c r="Z21" s="17"/>
-      <c r="AA21" s="23"/>
+      <c r="AA21" s="31"/>
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
@@ -1739,7 +1751,7 @@
     </row>
     <row r="22" spans="1:32">
       <c r="A22" s="12"/>
-      <c r="B22" s="39"/>
+      <c r="B22" s="37"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="5" t="s">
@@ -1770,19 +1782,19 @@
       <c r="AF22" s="6"/>
     </row>
     <row r="23" spans="1:32">
-      <c r="A23" s="36"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
       <c r="E23" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
       <c r="J23" t="s">
         <v>1</v>
       </c>
@@ -1791,8 +1803,8 @@
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="4"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
       <c r="AB23" s="2"/>
@@ -1802,19 +1814,19 @@
       <c r="AF23" s="6"/>
     </row>
     <row r="24" spans="1:32">
-      <c r="A24" s="36"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
       <c r="E24" s="5">
         <v>6574565</v>
       </c>
       <c r="F24" s="5">
         <v>6574565</v>
       </c>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
       <c r="J24" t="s">
         <v>1</v>
       </c>
@@ -1823,8 +1835,8 @@
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
       <c r="W24" s="4"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="31"/>
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
@@ -1834,19 +1846,19 @@
       <c r="AF24" s="6"/>
     </row>
     <row r="25" spans="1:32">
-      <c r="A25" s="36"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
       <c r="E25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
       <c r="J25" t="s">
         <v>1</v>
       </c>
@@ -1855,8 +1867,8 @@
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
       <c r="W25" s="4"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="31"/>
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
@@ -1866,31 +1878,31 @@
       <c r="AF25" s="6"/>
     </row>
     <row r="26" spans="1:32">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="35">
         <v>9</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <v>10</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="27">
         <v>11</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="26">
         <v>14</v>
       </c>
-      <c r="F26" s="38">
+      <c r="F26" s="36">
         <v>15</v>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="28">
         <v>16</v>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="26">
         <v>17</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="26">
         <v>18</v>
       </c>
       <c r="J26" t="s">
@@ -1913,7 +1925,7 @@
     </row>
     <row r="27" spans="1:32">
       <c r="A27" s="12"/>
-      <c r="B27" s="39"/>
+      <c r="B27" s="37"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="5"/>
@@ -1929,8 +1941,8 @@
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
       <c r="W27" s="4"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="31"/>
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
@@ -1940,15 +1952,15 @@
       <c r="AF27" s="6"/>
     </row>
     <row r="28" spans="1:32">
-      <c r="A28" s="36"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
       <c r="J28" t="s">
         <v>1</v>
       </c>
@@ -1957,8 +1969,8 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="4"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
       <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
@@ -1968,15 +1980,15 @@
       <c r="AF28" s="6"/>
     </row>
     <row r="29" spans="1:32">
-      <c r="A29" s="36"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
       <c r="J29" t="s">
         <v>1</v>
       </c>
@@ -1996,15 +2008,15 @@
       <c r="AF29" s="6"/>
     </row>
     <row r="30" spans="1:32">
-      <c r="A30" s="36"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
       <c r="J30" t="s">
         <v>1</v>
       </c>
@@ -2024,31 +2036,31 @@
       <c r="AF30" s="6"/>
     </row>
     <row r="31" spans="1:32">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="44">
+      <c r="B31" s="42">
         <v>9</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="24">
         <v>10</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="29">
         <v>11</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="24">
         <v>14</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="33">
         <v>15</v>
       </c>
-      <c r="G31" s="31">
+      <c r="G31" s="30">
         <v>16</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="24">
         <v>17</v>
       </c>
-      <c r="I31" s="25">
+      <c r="I31" s="24">
         <v>18</v>
       </c>
       <c r="J31" t="s">
@@ -2071,7 +2083,7 @@
     </row>
     <row r="32" spans="1:32">
       <c r="A32" s="12"/>
-      <c r="B32" s="39"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="5"/>
@@ -2098,15 +2110,15 @@
       <c r="AF32" s="6"/>
     </row>
     <row r="33" spans="1:32">
-      <c r="A33" s="36"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
       <c r="J33" t="s">
         <v>1</v>
       </c>
@@ -2131,15 +2143,15 @@
       <c r="AF33" s="6"/>
     </row>
     <row r="34" spans="1:32">
-      <c r="A34" s="36"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
       <c r="J34" t="s">
         <v>1</v>
       </c>
@@ -2164,15 +2176,15 @@
       <c r="AF34" s="6"/>
     </row>
     <row r="35" spans="1:32">
-      <c r="A35" s="36"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
       <c r="J35" t="s">
         <v>1</v>
       </c>
@@ -2197,31 +2209,31 @@
       <c r="AF35" s="6"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="44">
+      <c r="B36" s="42">
         <v>9</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="24">
         <v>10</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="29">
         <v>11</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="24">
         <v>14</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="33">
         <v>15</v>
       </c>
-      <c r="G36" s="31">
+      <c r="G36" s="30">
         <v>16</v>
       </c>
-      <c r="H36" s="25">
+      <c r="H36" s="24">
         <v>17</v>
       </c>
-      <c r="I36" s="25">
+      <c r="I36" s="24">
         <v>18</v>
       </c>
       <c r="J36" t="s">
@@ -2249,7 +2261,7 @@
     </row>
     <row r="37" spans="1:32">
       <c r="A37" s="12"/>
-      <c r="B37" s="39"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="5"/>
@@ -2281,15 +2293,15 @@
       <c r="AF37" s="6"/>
     </row>
     <row r="38" spans="1:32">
-      <c r="A38" s="36"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="37"/>
       <c r="J38" t="s">
         <v>1</v>
       </c>
@@ -2314,15 +2326,15 @@
       <c r="AF38" s="6"/>
     </row>
     <row r="39" spans="1:32">
-      <c r="A39" s="36"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="37"/>
+      <c r="I39" s="37"/>
       <c r="J39" t="s">
         <v>1</v>
       </c>
@@ -2347,15 +2359,15 @@
       <c r="AF39" s="6"/>
     </row>
     <row r="40" spans="1:32">
-      <c r="A40" s="36"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
+      <c r="I40" s="37"/>
       <c r="J40" t="s">
         <v>1</v>
       </c>
@@ -2380,31 +2392,31 @@
       <c r="AF40" s="6"/>
     </row>
     <row r="41" spans="1:32">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="44">
+      <c r="B41" s="42">
         <v>9</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="24">
         <v>10</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="29">
         <v>11</v>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="24">
         <v>14</v>
       </c>
-      <c r="F41" s="35">
+      <c r="F41" s="33">
         <v>15</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="30">
         <v>16</v>
       </c>
-      <c r="H41" s="25">
+      <c r="H41" s="24">
         <v>17</v>
       </c>
-      <c r="I41" s="25">
+      <c r="I41" s="24">
         <v>18</v>
       </c>
       <c r="J41" t="s">
@@ -2432,7 +2444,7 @@
     </row>
     <row r="42" spans="1:32">
       <c r="A42" s="12"/>
-      <c r="B42" s="39"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="5"/>
@@ -2464,15 +2476,15 @@
       <c r="AF42" s="6"/>
     </row>
     <row r="43" spans="1:32">
-      <c r="A43" s="36"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
+      <c r="A43" s="34"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
       <c r="J43" t="s">
         <v>1</v>
       </c>
@@ -2497,15 +2509,15 @@
       <c r="AF43" s="6"/>
     </row>
     <row r="44" spans="1:32">
-      <c r="A44" s="36"/>
-      <c r="B44" s="39"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
+      <c r="A44" s="34"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="39"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
       <c r="J44" t="s">
         <v>1</v>
       </c>
@@ -2530,15 +2542,15 @@
       <c r="AF44" s="6"/>
     </row>
     <row r="45" spans="1:32">
-      <c r="A45" s="36"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="39"/>
+      <c r="A45" s="34"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="39"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
       <c r="J45" t="s">
         <v>1</v>
       </c>
@@ -2563,31 +2575,31 @@
       <c r="AF45" s="6"/>
     </row>
     <row r="46" spans="1:32">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B46" s="44">
+      <c r="B46" s="42">
         <v>9</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="24">
         <v>10</v>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="29">
         <v>11</v>
       </c>
-      <c r="E46" s="25">
+      <c r="E46" s="24">
         <v>14</v>
       </c>
-      <c r="F46" s="35">
+      <c r="F46" s="33">
         <v>15</v>
       </c>
-      <c r="G46" s="31">
+      <c r="G46" s="30">
         <v>16</v>
       </c>
-      <c r="H46" s="25">
+      <c r="H46" s="24">
         <v>17</v>
       </c>
-      <c r="I46" s="25">
+      <c r="I46" s="24">
         <v>18</v>
       </c>
       <c r="J46" t="s">
@@ -2615,7 +2627,7 @@
     </row>
     <row r="47" spans="1:32">
       <c r="A47" s="12"/>
-      <c r="B47" s="39"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="5"/>
@@ -2647,15 +2659,15 @@
       <c r="AF47" s="6"/>
     </row>
     <row r="48" spans="1:32">
-      <c r="A48" s="36"/>
-      <c r="B48" s="39"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
-      <c r="G48" s="39"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="39"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
       <c r="J48" t="s">
         <v>1</v>
       </c>
@@ -2680,15 +2692,15 @@
       <c r="AF48" s="6"/>
     </row>
     <row r="49" spans="1:32">
-      <c r="A49" s="36"/>
-      <c r="B49" s="39"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="39"/>
+      <c r="A49" s="34"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
-      <c r="G49" s="39"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="39"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="37"/>
+      <c r="I49" s="37"/>
       <c r="J49" t="s">
         <v>1</v>
       </c>
@@ -2713,15 +2725,15 @@
       <c r="AF49" s="6"/>
     </row>
     <row r="50" spans="1:32">
-      <c r="A50" s="36"/>
-      <c r="B50" s="39"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
+      <c r="A50" s="34"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
-      <c r="G50" s="39"/>
-      <c r="H50" s="39"/>
-      <c r="I50" s="39"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="37"/>
+      <c r="I50" s="37"/>
       <c r="J50" t="s">
         <v>1</v>
       </c>
@@ -2746,31 +2758,31 @@
       <c r="AF50" s="6"/>
     </row>
     <row r="51" spans="1:32">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B51" s="44">
+      <c r="B51" s="42">
         <v>9</v>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="24">
         <v>10</v>
       </c>
-      <c r="D51" s="30">
+      <c r="D51" s="29">
         <v>11</v>
       </c>
-      <c r="E51" s="25">
+      <c r="E51" s="24">
         <v>14</v>
       </c>
-      <c r="F51" s="35">
+      <c r="F51" s="33">
         <v>15</v>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="30">
         <v>16</v>
       </c>
-      <c r="H51" s="25">
+      <c r="H51" s="24">
         <v>17</v>
       </c>
-      <c r="I51" s="25">
+      <c r="I51" s="24">
         <v>18</v>
       </c>
       <c r="J51" t="s">
@@ -2779,7 +2791,7 @@
     </row>
     <row r="52" spans="1:32">
       <c r="A52" s="12"/>
-      <c r="B52" s="39"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="5"/>
@@ -2792,73 +2804,73 @@
       </c>
     </row>
     <row r="53" spans="1:32">
-      <c r="A53" s="36"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
+      <c r="A53" s="34"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
+      <c r="G53" s="37"/>
+      <c r="H53" s="37"/>
+      <c r="I53" s="37"/>
       <c r="J53" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:32">
-      <c r="A54" s="36"/>
-      <c r="B54" s="39"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="39"/>
+      <c r="A54" s="34"/>
+      <c r="B54" s="37"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="37"/>
+      <c r="I54" s="37"/>
       <c r="J54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:32">
-      <c r="A55" s="36"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="39"/>
+      <c r="A55" s="34"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
+      <c r="G55" s="37"/>
+      <c r="H55" s="37"/>
+      <c r="I55" s="37"/>
       <c r="J55" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:32">
-      <c r="A56" s="26" t="s">
+      <c r="A56" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="44">
+      <c r="B56" s="42">
         <v>9</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="24">
         <v>10</v>
       </c>
-      <c r="D56" s="30">
+      <c r="D56" s="29">
         <v>11</v>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="24">
         <v>14</v>
       </c>
-      <c r="F56" s="35">
+      <c r="F56" s="33">
         <v>15</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="30">
         <v>16</v>
       </c>
-      <c r="H56" s="25">
+      <c r="H56" s="24">
         <v>17</v>
       </c>
-      <c r="I56" s="25">
+      <c r="I56" s="24">
         <v>18</v>
       </c>
       <c r="J56" t="s">
@@ -2867,7 +2879,7 @@
     </row>
     <row r="57" spans="1:32">
       <c r="A57" s="12"/>
-      <c r="B57" s="39"/>
+      <c r="B57" s="37"/>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="5"/>
@@ -2880,73 +2892,73 @@
       </c>
     </row>
     <row r="58" spans="1:32">
-      <c r="A58" s="36"/>
-      <c r="B58" s="39"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="39"/>
+      <c r="A58" s="34"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="39"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="37"/>
+      <c r="I58" s="37"/>
       <c r="J58" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:32">
-      <c r="A59" s="36"/>
-      <c r="B59" s="39"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="39"/>
+      <c r="A59" s="34"/>
+      <c r="B59" s="37"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="37"/>
+      <c r="I59" s="37"/>
       <c r="J59" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:32">
-      <c r="A60" s="36"/>
-      <c r="B60" s="39"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
+      <c r="A60" s="34"/>
+      <c r="B60" s="37"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="39"/>
-      <c r="I60" s="39"/>
+      <c r="G60" s="37"/>
+      <c r="H60" s="37"/>
+      <c r="I60" s="37"/>
       <c r="J60" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:32">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B61" s="44">
+      <c r="B61" s="42">
         <v>9</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="24">
         <v>10</v>
       </c>
-      <c r="D61" s="30">
+      <c r="D61" s="29">
         <v>11</v>
       </c>
-      <c r="E61" s="25">
+      <c r="E61" s="24">
         <v>14</v>
       </c>
-      <c r="F61" s="35">
+      <c r="F61" s="33">
         <v>15</v>
       </c>
-      <c r="G61" s="31">
+      <c r="G61" s="30">
         <v>16</v>
       </c>
-      <c r="H61" s="25">
+      <c r="H61" s="24">
         <v>17</v>
       </c>
-      <c r="I61" s="25">
+      <c r="I61" s="24">
         <v>18</v>
       </c>
       <c r="J61" t="s">
@@ -2955,7 +2967,7 @@
     </row>
     <row r="62" spans="1:32">
       <c r="A62" s="12"/>
-      <c r="B62" s="39"/>
+      <c r="B62" s="37"/>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="5"/>
@@ -2968,73 +2980,73 @@
       </c>
     </row>
     <row r="63" spans="1:32">
-      <c r="A63" s="36"/>
-      <c r="B63" s="39"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="39"/>
+      <c r="A63" s="34"/>
+      <c r="B63" s="37"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="39"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="37"/>
+      <c r="I63" s="37"/>
       <c r="J63" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:32">
-      <c r="A64" s="36"/>
-      <c r="B64" s="39"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
+      <c r="A64" s="34"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="39"/>
-      <c r="I64" s="39"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="37"/>
+      <c r="I64" s="37"/>
       <c r="J64" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="36"/>
-      <c r="B65" s="39"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
+      <c r="A65" s="34"/>
+      <c r="B65" s="37"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
-      <c r="G65" s="39"/>
-      <c r="H65" s="39"/>
-      <c r="I65" s="39"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="37"/>
+      <c r="I65" s="37"/>
       <c r="J65" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="26" t="s">
+      <c r="A66" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B66" s="44">
+      <c r="B66" s="42">
         <v>9</v>
       </c>
-      <c r="C66" s="25">
+      <c r="C66" s="24">
         <v>10</v>
       </c>
-      <c r="D66" s="30">
+      <c r="D66" s="29">
         <v>11</v>
       </c>
-      <c r="E66" s="25">
+      <c r="E66" s="24">
         <v>14</v>
       </c>
-      <c r="F66" s="35">
+      <c r="F66" s="33">
         <v>15</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="30">
         <v>16</v>
       </c>
-      <c r="H66" s="25">
+      <c r="H66" s="24">
         <v>17</v>
       </c>
-      <c r="I66" s="25">
+      <c r="I66" s="24">
         <v>18</v>
       </c>
       <c r="J66" t="s">
@@ -3043,7 +3055,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="12"/>
-      <c r="B67" s="39"/>
+      <c r="B67" s="37"/>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
       <c r="E67" s="5"/>
@@ -3056,73 +3068,73 @@
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="36"/>
-      <c r="B68" s="39"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="39"/>
+      <c r="A68" s="34"/>
+      <c r="B68" s="37"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
-      <c r="G68" s="39"/>
-      <c r="H68" s="39"/>
-      <c r="I68" s="39"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="37"/>
+      <c r="I68" s="37"/>
       <c r="J68" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="36"/>
-      <c r="B69" s="39"/>
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
+      <c r="A69" s="34"/>
+      <c r="B69" s="37"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
-      <c r="G69" s="39"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="39"/>
+      <c r="G69" s="37"/>
+      <c r="H69" s="37"/>
+      <c r="I69" s="37"/>
       <c r="J69" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="36"/>
-      <c r="B70" s="39"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
+      <c r="A70" s="34"/>
+      <c r="B70" s="37"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
-      <c r="G70" s="39"/>
-      <c r="H70" s="39"/>
-      <c r="I70" s="39"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="37"/>
+      <c r="I70" s="37"/>
       <c r="J70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="26" t="s">
+      <c r="A71" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B71" s="44">
+      <c r="B71" s="42">
         <v>9</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="24">
         <v>10</v>
       </c>
-      <c r="D71" s="30">
+      <c r="D71" s="29">
         <v>11</v>
       </c>
-      <c r="E71" s="25">
+      <c r="E71" s="24">
         <v>14</v>
       </c>
-      <c r="F71" s="35">
+      <c r="F71" s="33">
         <v>15</v>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="30">
         <v>16</v>
       </c>
-      <c r="H71" s="25">
+      <c r="H71" s="24">
         <v>17</v>
       </c>
-      <c r="I71" s="25">
+      <c r="I71" s="24">
         <v>18</v>
       </c>
       <c r="J71" t="s">
@@ -3131,7 +3143,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="12"/>
-      <c r="B72" s="39"/>
+      <c r="B72" s="37"/>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="5"/>
@@ -3144,73 +3156,73 @@
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="36"/>
-      <c r="B73" s="39"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
+      <c r="A73" s="34"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
-      <c r="G73" s="39"/>
-      <c r="H73" s="39"/>
-      <c r="I73" s="39"/>
+      <c r="G73" s="37"/>
+      <c r="H73" s="37"/>
+      <c r="I73" s="37"/>
       <c r="J73" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="36"/>
-      <c r="B74" s="39"/>
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
+      <c r="A74" s="34"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
-      <c r="G74" s="39"/>
-      <c r="H74" s="39"/>
-      <c r="I74" s="39"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
       <c r="J74" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="36"/>
-      <c r="B75" s="39"/>
-      <c r="C75" s="39"/>
-      <c r="D75" s="39"/>
+      <c r="A75" s="34"/>
+      <c r="B75" s="37"/>
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
-      <c r="G75" s="39"/>
-      <c r="H75" s="39"/>
-      <c r="I75" s="39"/>
+      <c r="G75" s="37"/>
+      <c r="H75" s="37"/>
+      <c r="I75" s="37"/>
       <c r="J75" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="26" t="s">
+      <c r="A76" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B76" s="44">
+      <c r="B76" s="42">
         <v>9</v>
       </c>
-      <c r="C76" s="25">
+      <c r="C76" s="24">
         <v>10</v>
       </c>
-      <c r="D76" s="30">
+      <c r="D76" s="29">
         <v>11</v>
       </c>
-      <c r="E76" s="25">
+      <c r="E76" s="24">
         <v>14</v>
       </c>
-      <c r="F76" s="35">
+      <c r="F76" s="33">
         <v>15</v>
       </c>
-      <c r="G76" s="31">
+      <c r="G76" s="30">
         <v>16</v>
       </c>
-      <c r="H76" s="25">
+      <c r="H76" s="24">
         <v>17</v>
       </c>
-      <c r="I76" s="25">
+      <c r="I76" s="24">
         <v>18</v>
       </c>
       <c r="J76" t="s">
@@ -3219,7 +3231,7 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="12"/>
-      <c r="B77" s="39"/>
+      <c r="B77" s="37"/>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="5"/>
@@ -3232,73 +3244,73 @@
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="36"/>
-      <c r="B78" s="39"/>
-      <c r="C78" s="39"/>
-      <c r="D78" s="39"/>
+      <c r="A78" s="34"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
-      <c r="G78" s="39"/>
-      <c r="H78" s="39"/>
-      <c r="I78" s="39"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="37"/>
+      <c r="I78" s="37"/>
       <c r="J78" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="36"/>
-      <c r="B79" s="39"/>
-      <c r="C79" s="39"/>
-      <c r="D79" s="39"/>
+      <c r="A79" s="34"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
-      <c r="G79" s="39"/>
-      <c r="H79" s="39"/>
-      <c r="I79" s="39"/>
+      <c r="G79" s="37"/>
+      <c r="H79" s="37"/>
+      <c r="I79" s="37"/>
       <c r="J79" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="36"/>
-      <c r="B80" s="39"/>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
+      <c r="A80" s="34"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
-      <c r="G80" s="39"/>
-      <c r="H80" s="39"/>
-      <c r="I80" s="39"/>
+      <c r="G80" s="37"/>
+      <c r="H80" s="37"/>
+      <c r="I80" s="37"/>
       <c r="J80" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="26" t="s">
+      <c r="A81" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B81" s="44">
+      <c r="B81" s="42">
         <v>9</v>
       </c>
-      <c r="C81" s="25">
+      <c r="C81" s="24">
         <v>10</v>
       </c>
-      <c r="D81" s="30">
+      <c r="D81" s="29">
         <v>11</v>
       </c>
-      <c r="E81" s="25">
+      <c r="E81" s="24">
         <v>14</v>
       </c>
-      <c r="F81" s="35">
+      <c r="F81" s="33">
         <v>15</v>
       </c>
-      <c r="G81" s="31">
+      <c r="G81" s="30">
         <v>16</v>
       </c>
-      <c r="H81" s="25">
+      <c r="H81" s="24">
         <v>17</v>
       </c>
-      <c r="I81" s="25">
+      <c r="I81" s="24">
         <v>18</v>
       </c>
       <c r="J81" t="s">
@@ -3307,7 +3319,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="12"/>
-      <c r="B82" s="39"/>
+      <c r="B82" s="37"/>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="5"/>
@@ -3320,73 +3332,73 @@
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="36"/>
-      <c r="B83" s="39"/>
-      <c r="C83" s="39"/>
-      <c r="D83" s="39"/>
+      <c r="A83" s="34"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="37"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
-      <c r="G83" s="39"/>
-      <c r="H83" s="39"/>
-      <c r="I83" s="39"/>
+      <c r="G83" s="37"/>
+      <c r="H83" s="37"/>
+      <c r="I83" s="37"/>
       <c r="J83" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="36"/>
-      <c r="B84" s="39"/>
-      <c r="C84" s="39"/>
-      <c r="D84" s="39"/>
+      <c r="A84" s="34"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="37"/>
+      <c r="D84" s="37"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
-      <c r="G84" s="39"/>
-      <c r="H84" s="39"/>
-      <c r="I84" s="39"/>
+      <c r="G84" s="37"/>
+      <c r="H84" s="37"/>
+      <c r="I84" s="37"/>
       <c r="J84" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="36"/>
-      <c r="B85" s="39"/>
-      <c r="C85" s="39"/>
-      <c r="D85" s="39"/>
+      <c r="A85" s="34"/>
+      <c r="B85" s="37"/>
+      <c r="C85" s="37"/>
+      <c r="D85" s="37"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
-      <c r="G85" s="39"/>
-      <c r="H85" s="39"/>
-      <c r="I85" s="39"/>
+      <c r="G85" s="37"/>
+      <c r="H85" s="37"/>
+      <c r="I85" s="37"/>
       <c r="J85" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="26" t="s">
+      <c r="A86" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B86" s="44">
+      <c r="B86" s="42">
         <v>9</v>
       </c>
-      <c r="C86" s="25">
+      <c r="C86" s="24">
         <v>10</v>
       </c>
-      <c r="D86" s="30">
+      <c r="D86" s="29">
         <v>11</v>
       </c>
-      <c r="E86" s="25">
+      <c r="E86" s="24">
         <v>14</v>
       </c>
-      <c r="F86" s="35">
+      <c r="F86" s="33">
         <v>15</v>
       </c>
-      <c r="G86" s="31">
+      <c r="G86" s="30">
         <v>16</v>
       </c>
-      <c r="H86" s="25">
+      <c r="H86" s="24">
         <v>17</v>
       </c>
-      <c r="I86" s="25">
+      <c r="I86" s="24">
         <v>18</v>
       </c>
       <c r="J86" t="s">
@@ -3395,7 +3407,7 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="12"/>
-      <c r="B87" s="39"/>
+      <c r="B87" s="37"/>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
       <c r="E87" s="5"/>
@@ -3408,73 +3420,73 @@
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="36"/>
-      <c r="B88" s="39"/>
-      <c r="C88" s="39"/>
-      <c r="D88" s="39"/>
+      <c r="A88" s="34"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="37"/>
+      <c r="D88" s="37"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
-      <c r="G88" s="39"/>
-      <c r="H88" s="39"/>
-      <c r="I88" s="39"/>
+      <c r="G88" s="37"/>
+      <c r="H88" s="37"/>
+      <c r="I88" s="37"/>
       <c r="J88" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="36"/>
-      <c r="B89" s="39"/>
-      <c r="C89" s="39"/>
-      <c r="D89" s="39"/>
+      <c r="A89" s="34"/>
+      <c r="B89" s="37"/>
+      <c r="C89" s="37"/>
+      <c r="D89" s="37"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
-      <c r="G89" s="39"/>
-      <c r="H89" s="39"/>
-      <c r="I89" s="39"/>
+      <c r="G89" s="37"/>
+      <c r="H89" s="37"/>
+      <c r="I89" s="37"/>
       <c r="J89" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="36"/>
-      <c r="B90" s="39"/>
-      <c r="C90" s="39"/>
-      <c r="D90" s="39"/>
+      <c r="A90" s="34"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37"/>
+      <c r="D90" s="37"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
-      <c r="G90" s="39"/>
-      <c r="H90" s="39"/>
-      <c r="I90" s="39"/>
+      <c r="G90" s="37"/>
+      <c r="H90" s="37"/>
+      <c r="I90" s="37"/>
       <c r="J90" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="26" t="s">
+      <c r="A91" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B91" s="44">
+      <c r="B91" s="42">
         <v>9</v>
       </c>
-      <c r="C91" s="25">
+      <c r="C91" s="24">
         <v>10</v>
       </c>
-      <c r="D91" s="30">
+      <c r="D91" s="29">
         <v>11</v>
       </c>
-      <c r="E91" s="25">
+      <c r="E91" s="24">
         <v>14</v>
       </c>
-      <c r="F91" s="35">
+      <c r="F91" s="33">
         <v>15</v>
       </c>
-      <c r="G91" s="31">
+      <c r="G91" s="30">
         <v>16</v>
       </c>
-      <c r="H91" s="25">
+      <c r="H91" s="24">
         <v>17</v>
       </c>
-      <c r="I91" s="25">
+      <c r="I91" s="24">
         <v>18</v>
       </c>
       <c r="J91" t="s">
@@ -3483,10 +3495,10 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="12"/>
-      <c r="B92" s="39"/>
+      <c r="B92" s="37"/>
       <c r="C92" s="9"/>
       <c r="D92" s="9" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
@@ -3498,79 +3510,79 @@
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="36"/>
-      <c r="B93" s="39"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39" t="s">
-        <v>45</v>
+      <c r="A93" s="34"/>
+      <c r="B93" s="37"/>
+      <c r="C93" s="37"/>
+      <c r="D93" s="37" t="s">
+        <v>30</v>
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
-      <c r="G93" s="39"/>
-      <c r="H93" s="39"/>
-      <c r="I93" s="39"/>
+      <c r="G93" s="37"/>
+      <c r="H93" s="37"/>
+      <c r="I93" s="37"/>
       <c r="J93" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="36"/>
-      <c r="B94" s="39"/>
-      <c r="C94" s="39"/>
-      <c r="D94" s="39" t="s">
-        <v>58</v>
+      <c r="A94" s="34"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37"/>
+      <c r="D94" s="37" t="s">
+        <v>31</v>
       </c>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
-      <c r="G94" s="39"/>
-      <c r="H94" s="39"/>
-      <c r="I94" s="39"/>
+      <c r="G94" s="37"/>
+      <c r="H94" s="37"/>
+      <c r="I94" s="37"/>
       <c r="J94" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="36"/>
-      <c r="B95" s="39"/>
-      <c r="C95" s="39"/>
-      <c r="D95" s="39" t="s">
-        <v>49</v>
+      <c r="A95" s="34"/>
+      <c r="B95" s="37"/>
+      <c r="C95" s="37"/>
+      <c r="D95" s="37" t="s">
+        <v>32</v>
       </c>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
-      <c r="G95" s="39"/>
-      <c r="H95" s="39"/>
-      <c r="I95" s="39"/>
+      <c r="G95" s="37"/>
+      <c r="H95" s="37"/>
+      <c r="I95" s="37"/>
       <c r="J95" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B96" s="44">
+      <c r="A96" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B96" s="42">
         <v>9</v>
       </c>
-      <c r="C96" s="25">
+      <c r="C96" s="24">
         <v>10</v>
       </c>
-      <c r="D96" s="30">
+      <c r="D96" s="29">
         <v>11</v>
       </c>
-      <c r="E96" s="25">
+      <c r="E96" s="24">
         <v>14</v>
       </c>
-      <c r="F96" s="35">
+      <c r="F96" s="33">
         <v>15</v>
       </c>
-      <c r="G96" s="31">
+      <c r="G96" s="30">
         <v>16</v>
       </c>
-      <c r="H96" s="25">
+      <c r="H96" s="24">
         <v>17</v>
       </c>
-      <c r="I96" s="25">
+      <c r="I96" s="24">
         <v>18</v>
       </c>
       <c r="J96" t="s">
@@ -3579,7 +3591,7 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="12"/>
-      <c r="B97" s="39"/>
+      <c r="B97" s="37"/>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
       <c r="E97" s="5"/>
@@ -3592,73 +3604,73 @@
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="36"/>
-      <c r="B98" s="39"/>
-      <c r="C98" s="39"/>
-      <c r="D98" s="39"/>
+      <c r="A98" s="34"/>
+      <c r="B98" s="37"/>
+      <c r="C98" s="37"/>
+      <c r="D98" s="37"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
-      <c r="G98" s="39"/>
-      <c r="H98" s="39"/>
-      <c r="I98" s="39"/>
+      <c r="G98" s="37"/>
+      <c r="H98" s="37"/>
+      <c r="I98" s="37"/>
       <c r="J98" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="36"/>
-      <c r="B99" s="39"/>
-      <c r="C99" s="39"/>
-      <c r="D99" s="39"/>
+      <c r="A99" s="34"/>
+      <c r="B99" s="37"/>
+      <c r="C99" s="37"/>
+      <c r="D99" s="37"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
-      <c r="G99" s="39"/>
-      <c r="H99" s="39"/>
-      <c r="I99" s="39"/>
+      <c r="G99" s="37"/>
+      <c r="H99" s="37"/>
+      <c r="I99" s="37"/>
       <c r="J99" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="36"/>
-      <c r="B100" s="39"/>
-      <c r="C100" s="39"/>
-      <c r="D100" s="39"/>
+      <c r="A100" s="34"/>
+      <c r="B100" s="37"/>
+      <c r="C100" s="37"/>
+      <c r="D100" s="37"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
-      <c r="G100" s="39"/>
-      <c r="H100" s="39"/>
-      <c r="I100" s="39"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
       <c r="J100" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B101" s="44">
+      <c r="A101" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B101" s="42">
         <v>9</v>
       </c>
-      <c r="C101" s="25">
+      <c r="C101" s="24">
         <v>10</v>
       </c>
-      <c r="D101" s="30">
+      <c r="D101" s="29">
         <v>11</v>
       </c>
-      <c r="E101" s="25">
+      <c r="E101" s="24">
         <v>14</v>
       </c>
-      <c r="F101" s="35">
+      <c r="F101" s="33">
         <v>15</v>
       </c>
-      <c r="G101" s="31">
+      <c r="G101" s="30">
         <v>16</v>
       </c>
-      <c r="H101" s="25">
+      <c r="H101" s="24">
         <v>17</v>
       </c>
-      <c r="I101" s="25">
+      <c r="I101" s="24">
         <v>18</v>
       </c>
       <c r="J101" t="s">
@@ -3667,7 +3679,7 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="12"/>
-      <c r="B102" s="39"/>
+      <c r="B102" s="37"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
       <c r="E102" s="5"/>
@@ -3680,73 +3692,73 @@
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="36"/>
-      <c r="B103" s="39"/>
-      <c r="C103" s="39"/>
-      <c r="D103" s="39"/>
+      <c r="A103" s="34"/>
+      <c r="B103" s="37"/>
+      <c r="C103" s="37"/>
+      <c r="D103" s="37"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
-      <c r="G103" s="39"/>
-      <c r="H103" s="39"/>
-      <c r="I103" s="39"/>
+      <c r="G103" s="37"/>
+      <c r="H103" s="37"/>
+      <c r="I103" s="37"/>
       <c r="J103" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="36"/>
-      <c r="B104" s="39"/>
-      <c r="C104" s="39"/>
-      <c r="D104" s="39"/>
+      <c r="A104" s="34"/>
+      <c r="B104" s="37"/>
+      <c r="C104" s="37"/>
+      <c r="D104" s="37"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
-      <c r="G104" s="39"/>
-      <c r="H104" s="39"/>
-      <c r="I104" s="39"/>
+      <c r="G104" s="37"/>
+      <c r="H104" s="37"/>
+      <c r="I104" s="37"/>
       <c r="J104" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="36"/>
-      <c r="B105" s="39"/>
-      <c r="C105" s="39"/>
-      <c r="D105" s="39"/>
+      <c r="A105" s="34"/>
+      <c r="B105" s="37"/>
+      <c r="C105" s="37"/>
+      <c r="D105" s="37"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5"/>
-      <c r="G105" s="39"/>
-      <c r="H105" s="39"/>
-      <c r="I105" s="39"/>
+      <c r="G105" s="37"/>
+      <c r="H105" s="37"/>
+      <c r="I105" s="37"/>
       <c r="J105" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B106" s="44">
+      <c r="A106" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B106" s="42">
         <v>9</v>
       </c>
-      <c r="C106" s="25">
+      <c r="C106" s="24">
         <v>10</v>
       </c>
-      <c r="D106" s="30">
+      <c r="D106" s="29">
         <v>11</v>
       </c>
-      <c r="E106" s="25">
+      <c r="E106" s="24">
         <v>14</v>
       </c>
-      <c r="F106" s="35">
+      <c r="F106" s="33">
         <v>15</v>
       </c>
-      <c r="G106" s="31">
+      <c r="G106" s="30">
         <v>16</v>
       </c>
-      <c r="H106" s="25">
+      <c r="H106" s="24">
         <v>17</v>
       </c>
-      <c r="I106" s="25">
+      <c r="I106" s="24">
         <v>18</v>
       </c>
       <c r="J106" t="s">
@@ -3755,7 +3767,7 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="12"/>
-      <c r="B107" s="39"/>
+      <c r="B107" s="37"/>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="5"/>
@@ -3768,73 +3780,73 @@
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="36"/>
-      <c r="B108" s="39"/>
-      <c r="C108" s="39"/>
-      <c r="D108" s="39"/>
+      <c r="A108" s="34"/>
+      <c r="B108" s="37"/>
+      <c r="C108" s="37"/>
+      <c r="D108" s="37"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
-      <c r="G108" s="39"/>
-      <c r="H108" s="39"/>
-      <c r="I108" s="39"/>
+      <c r="G108" s="37"/>
+      <c r="H108" s="37"/>
+      <c r="I108" s="37"/>
       <c r="J108" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="36"/>
-      <c r="B109" s="39"/>
-      <c r="C109" s="39"/>
-      <c r="D109" s="39"/>
+      <c r="A109" s="34"/>
+      <c r="B109" s="37"/>
+      <c r="C109" s="37"/>
+      <c r="D109" s="37"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
-      <c r="G109" s="39"/>
-      <c r="H109" s="39"/>
-      <c r="I109" s="39"/>
+      <c r="G109" s="37"/>
+      <c r="H109" s="37"/>
+      <c r="I109" s="37"/>
       <c r="J109" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="36"/>
-      <c r="B110" s="39"/>
-      <c r="C110" s="39"/>
-      <c r="D110" s="39"/>
+      <c r="A110" s="34"/>
+      <c r="B110" s="37"/>
+      <c r="C110" s="37"/>
+      <c r="D110" s="37"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
-      <c r="G110" s="39"/>
-      <c r="H110" s="39"/>
-      <c r="I110" s="39"/>
+      <c r="G110" s="37"/>
+      <c r="H110" s="37"/>
+      <c r="I110" s="37"/>
       <c r="J110" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B111" s="44">
+      <c r="A111" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B111" s="42">
         <v>9</v>
       </c>
-      <c r="C111" s="25">
+      <c r="C111" s="24">
         <v>10</v>
       </c>
-      <c r="D111" s="30">
+      <c r="D111" s="29">
         <v>11</v>
       </c>
-      <c r="E111" s="25">
+      <c r="E111" s="24">
         <v>14</v>
       </c>
-      <c r="F111" s="35">
+      <c r="F111" s="33">
         <v>15</v>
       </c>
-      <c r="G111" s="31">
+      <c r="G111" s="30">
         <v>16</v>
       </c>
-      <c r="H111" s="25">
+      <c r="H111" s="24">
         <v>17</v>
       </c>
-      <c r="I111" s="25">
+      <c r="I111" s="24">
         <v>18</v>
       </c>
       <c r="J111" t="s">
@@ -3843,7 +3855,7 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="12"/>
-      <c r="B112" s="39"/>
+      <c r="B112" s="37"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="5"/>
@@ -3856,73 +3868,73 @@
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="36"/>
-      <c r="B113" s="39"/>
-      <c r="C113" s="39"/>
-      <c r="D113" s="39"/>
+      <c r="A113" s="34"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="37"/>
+      <c r="D113" s="37"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
-      <c r="G113" s="39"/>
-      <c r="H113" s="39"/>
-      <c r="I113" s="39"/>
+      <c r="G113" s="37"/>
+      <c r="H113" s="37"/>
+      <c r="I113" s="37"/>
       <c r="J113" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="36"/>
-      <c r="B114" s="39"/>
-      <c r="C114" s="39"/>
-      <c r="D114" s="39"/>
+      <c r="A114" s="34"/>
+      <c r="B114" s="37"/>
+      <c r="C114" s="37"/>
+      <c r="D114" s="37"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
-      <c r="G114" s="39"/>
-      <c r="H114" s="39"/>
-      <c r="I114" s="39"/>
+      <c r="G114" s="37"/>
+      <c r="H114" s="37"/>
+      <c r="I114" s="37"/>
       <c r="J114" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="36"/>
-      <c r="B115" s="39"/>
-      <c r="C115" s="39"/>
-      <c r="D115" s="39"/>
+      <c r="A115" s="34"/>
+      <c r="B115" s="37"/>
+      <c r="C115" s="37"/>
+      <c r="D115" s="37"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
-      <c r="G115" s="39"/>
-      <c r="H115" s="39"/>
-      <c r="I115" s="39"/>
+      <c r="G115" s="37"/>
+      <c r="H115" s="37"/>
+      <c r="I115" s="37"/>
       <c r="J115" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B116" s="44">
+      <c r="A116" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B116" s="42">
         <v>9</v>
       </c>
-      <c r="C116" s="25">
+      <c r="C116" s="24">
         <v>10</v>
       </c>
-      <c r="D116" s="30">
+      <c r="D116" s="29">
         <v>11</v>
       </c>
-      <c r="E116" s="25">
+      <c r="E116" s="24">
         <v>14</v>
       </c>
-      <c r="F116" s="35">
+      <c r="F116" s="33">
         <v>15</v>
       </c>
-      <c r="G116" s="31">
+      <c r="G116" s="30">
         <v>16</v>
       </c>
-      <c r="H116" s="25">
+      <c r="H116" s="24">
         <v>17</v>
       </c>
-      <c r="I116" s="25">
+      <c r="I116" s="24">
         <v>18</v>
       </c>
       <c r="J116" t="s">
@@ -3931,9 +3943,9 @@
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="12"/>
-      <c r="B117" s="39"/>
+      <c r="B117" s="37"/>
       <c r="C117" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D117" s="9"/>
       <c r="E117" s="5"/>
@@ -3946,79 +3958,79 @@
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="36"/>
-      <c r="B118" s="39"/>
-      <c r="C118" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D118" s="39"/>
+      <c r="A118" s="34"/>
+      <c r="B118" s="37"/>
+      <c r="C118" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D118" s="37"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
-      <c r="G118" s="39"/>
-      <c r="H118" s="39"/>
-      <c r="I118" s="39"/>
+      <c r="G118" s="37"/>
+      <c r="H118" s="37"/>
+      <c r="I118" s="37"/>
       <c r="J118" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="36"/>
-      <c r="B119" s="39"/>
-      <c r="C119" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="D119" s="39"/>
+      <c r="A119" s="34"/>
+      <c r="B119" s="37"/>
+      <c r="C119" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D119" s="37"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
-      <c r="G119" s="39"/>
-      <c r="H119" s="39"/>
-      <c r="I119" s="39"/>
+      <c r="G119" s="37"/>
+      <c r="H119" s="37"/>
+      <c r="I119" s="37"/>
       <c r="J119" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="36"/>
-      <c r="B120" s="39"/>
-      <c r="C120" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D120" s="39"/>
+      <c r="A120" s="34"/>
+      <c r="B120" s="37"/>
+      <c r="C120" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D120" s="37"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
-      <c r="G120" s="39"/>
-      <c r="H120" s="39"/>
-      <c r="I120" s="39"/>
+      <c r="G120" s="37"/>
+      <c r="H120" s="37"/>
+      <c r="I120" s="37"/>
       <c r="J120" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B121" s="44">
+      <c r="A121" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B121" s="42">
         <v>9</v>
       </c>
-      <c r="C121" s="25">
+      <c r="C121" s="24">
         <v>10</v>
       </c>
-      <c r="D121" s="30">
+      <c r="D121" s="29">
         <v>11</v>
       </c>
-      <c r="E121" s="25">
+      <c r="E121" s="24">
         <v>14</v>
       </c>
-      <c r="F121" s="35">
+      <c r="F121" s="33">
         <v>15</v>
       </c>
-      <c r="G121" s="31">
+      <c r="G121" s="30">
         <v>16</v>
       </c>
-      <c r="H121" s="25">
+      <c r="H121" s="24">
         <v>17</v>
       </c>
-      <c r="I121" s="25">
+      <c r="I121" s="24">
         <v>18</v>
       </c>
       <c r="J121" t="s">
@@ -4027,11 +4039,11 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="12"/>
-      <c r="B122" s="39"/>
+      <c r="B122" s="37"/>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="F122" s="5"/>
       <c r="G122" s="9"/>
@@ -4042,79 +4054,79 @@
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="36"/>
-      <c r="B123" s="39"/>
-      <c r="C123" s="39"/>
-      <c r="D123" s="39"/>
+      <c r="A123" s="34"/>
+      <c r="B123" s="37"/>
+      <c r="C123" s="37"/>
+      <c r="D123" s="37"/>
       <c r="E123" s="5" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="F123" s="5"/>
-      <c r="G123" s="39"/>
-      <c r="H123" s="39"/>
-      <c r="I123" s="39"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
       <c r="J123" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="36"/>
-      <c r="B124" s="39"/>
-      <c r="C124" s="39"/>
-      <c r="D124" s="39"/>
+      <c r="A124" s="34"/>
+      <c r="B124" s="37"/>
+      <c r="C124" s="37"/>
+      <c r="D124" s="37"/>
       <c r="E124" s="5" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="F124" s="5"/>
-      <c r="G124" s="39"/>
-      <c r="H124" s="39"/>
-      <c r="I124" s="39"/>
+      <c r="G124" s="37"/>
+      <c r="H124" s="37"/>
+      <c r="I124" s="37"/>
       <c r="J124" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="36"/>
-      <c r="B125" s="39"/>
-      <c r="C125" s="39"/>
-      <c r="D125" s="39"/>
+      <c r="A125" s="34"/>
+      <c r="B125" s="37"/>
+      <c r="C125" s="37"/>
+      <c r="D125" s="37"/>
       <c r="E125" s="5" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F125" s="5"/>
-      <c r="G125" s="39"/>
-      <c r="H125" s="39"/>
-      <c r="I125" s="39"/>
+      <c r="G125" s="37"/>
+      <c r="H125" s="37"/>
+      <c r="I125" s="37"/>
       <c r="J125" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:10">
-      <c r="A126" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B126" s="44">
+      <c r="A126" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B126" s="42">
         <v>9</v>
       </c>
-      <c r="C126" s="25">
+      <c r="C126" s="24">
         <v>10</v>
       </c>
-      <c r="D126" s="30">
+      <c r="D126" s="29">
         <v>11</v>
       </c>
-      <c r="E126" s="25">
+      <c r="E126" s="24">
         <v>14</v>
       </c>
-      <c r="F126" s="35">
+      <c r="F126" s="33">
         <v>15</v>
       </c>
-      <c r="G126" s="31">
+      <c r="G126" s="30">
         <v>16</v>
       </c>
-      <c r="H126" s="25">
+      <c r="H126" s="24">
         <v>17</v>
       </c>
-      <c r="I126" s="25">
+      <c r="I126" s="24">
         <v>18</v>
       </c>
       <c r="J126" t="s">
@@ -4123,14 +4135,14 @@
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="12"/>
-      <c r="B127" s="39" t="s">
-        <v>51</v>
+      <c r="B127" s="37" t="s">
+        <v>29</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -4142,91 +4154,91 @@
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="A128" s="36"/>
-      <c r="B128" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C128" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D128" s="39" t="s">
-        <v>77</v>
+      <c r="A128" s="34"/>
+      <c r="B128" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C128" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D128" s="37" t="s">
+        <v>48</v>
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
-      <c r="G128" s="39"/>
-      <c r="H128" s="39"/>
-      <c r="I128" s="39"/>
+      <c r="G128" s="37"/>
+      <c r="H128" s="37"/>
+      <c r="I128" s="37"/>
       <c r="J128" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" s="36"/>
-      <c r="B129" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="C129" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="D129" s="39" t="s">
-        <v>78</v>
+      <c r="A129" s="34"/>
+      <c r="B129" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C129" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D129" s="37" t="s">
+        <v>51</v>
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
-      <c r="G129" s="39"/>
-      <c r="H129" s="39"/>
-      <c r="I129" s="39"/>
+      <c r="G129" s="37"/>
+      <c r="H129" s="37"/>
+      <c r="I129" s="37"/>
       <c r="J129" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="36"/>
-      <c r="B130" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="C130" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="D130" s="39" t="s">
-        <v>79</v>
+      <c r="A130" s="34"/>
+      <c r="B130" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C130" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D130" s="37" t="s">
+        <v>54</v>
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
-      <c r="G130" s="39"/>
-      <c r="H130" s="39"/>
-      <c r="I130" s="39"/>
+      <c r="G130" s="37"/>
+      <c r="H130" s="37"/>
+      <c r="I130" s="37"/>
       <c r="J130" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B131" s="44">
+      <c r="A131" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B131" s="42">
         <v>9</v>
       </c>
-      <c r="C131" s="25">
+      <c r="C131" s="24">
         <v>10</v>
       </c>
-      <c r="D131" s="30">
+      <c r="D131" s="29">
         <v>11</v>
       </c>
-      <c r="E131" s="25">
+      <c r="E131" s="24">
         <v>14</v>
       </c>
-      <c r="F131" s="35">
+      <c r="F131" s="33">
         <v>15</v>
       </c>
-      <c r="G131" s="31">
+      <c r="G131" s="30">
         <v>16</v>
       </c>
-      <c r="H131" s="25">
+      <c r="H131" s="24">
         <v>17</v>
       </c>
-      <c r="I131" s="25">
+      <c r="I131" s="24">
         <v>18</v>
       </c>
       <c r="J131" t="s">
@@ -4235,17 +4247,17 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="12"/>
-      <c r="B132" s="39" t="s">
-        <v>80</v>
+      <c r="B132" s="37" t="s">
+        <v>56</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F132" s="5"/>
       <c r="G132" s="9"/>
@@ -4256,97 +4268,97 @@
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" s="36"/>
-      <c r="B133" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C133" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="D133" s="39" t="s">
-        <v>85</v>
+      <c r="A133" s="34"/>
+      <c r="B133" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C133" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D133" s="37" t="s">
+        <v>62</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="F133" s="5"/>
-      <c r="G133" s="39"/>
-      <c r="H133" s="39"/>
-      <c r="I133" s="39"/>
+      <c r="G133" s="37"/>
+      <c r="H133" s="37"/>
+      <c r="I133" s="37"/>
       <c r="J133" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="36"/>
-      <c r="B134" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C134" s="39" t="s">
+      <c r="A134" s="34"/>
+      <c r="B134" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="C134" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D134" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F134" s="5"/>
+      <c r="G134" s="37"/>
+      <c r="H134" s="37"/>
+      <c r="I134" s="37"/>
+      <c r="J134" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" s="34"/>
+      <c r="B135" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C135" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="D134" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F134" s="5"/>
-      <c r="G134" s="39"/>
-      <c r="H134" s="39"/>
-      <c r="I134" s="39"/>
-      <c r="J134" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10">
-      <c r="A135" s="36"/>
-      <c r="B135" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="C135" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="D135" s="39" t="s">
-        <v>86</v>
+      <c r="D135" s="37" t="s">
+        <v>68</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F135" s="5"/>
-      <c r="G135" s="39"/>
-      <c r="H135" s="39"/>
-      <c r="I135" s="39"/>
+      <c r="G135" s="37"/>
+      <c r="H135" s="37"/>
+      <c r="I135" s="37"/>
       <c r="J135" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:10">
-      <c r="A136" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B136" s="44">
+      <c r="A136" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B136" s="42">
         <v>9</v>
       </c>
-      <c r="C136" s="25">
+      <c r="C136" s="24">
         <v>10</v>
       </c>
-      <c r="D136" s="30">
+      <c r="D136" s="29">
         <v>11</v>
       </c>
-      <c r="E136" s="25">
+      <c r="E136" s="24">
         <v>14</v>
       </c>
-      <c r="F136" s="35">
+      <c r="F136" s="33">
         <v>15</v>
       </c>
-      <c r="G136" s="31">
+      <c r="G136" s="30">
         <v>16</v>
       </c>
-      <c r="H136" s="25">
+      <c r="H136" s="24">
         <v>17</v>
       </c>
-      <c r="I136" s="25">
+      <c r="I136" s="24">
         <v>18</v>
       </c>
       <c r="J136" t="s">
@@ -4355,20 +4367,20 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="12"/>
-      <c r="B137" s="39"/>
+      <c r="B137" s="37"/>
       <c r="C137" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="F137" s="5"/>
       <c r="G137" s="9"/>
       <c r="H137" s="9" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" t="s">
@@ -4376,97 +4388,97 @@
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="36"/>
-      <c r="B138" s="39"/>
-      <c r="C138" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="D138" s="39" t="s">
-        <v>49</v>
+      <c r="A138" s="34"/>
+      <c r="B138" s="37"/>
+      <c r="C138" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D138" s="37" t="s">
+        <v>32</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="F138" s="5"/>
-      <c r="G138" s="39"/>
-      <c r="H138" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="I138" s="39"/>
+      <c r="G138" s="37"/>
+      <c r="H138" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="I138" s="37"/>
       <c r="J138" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="36"/>
-      <c r="B139" s="39"/>
-      <c r="C139" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="D139" s="39" t="s">
+      <c r="A139" s="34"/>
+      <c r="B139" s="37"/>
+      <c r="C139" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="D139" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E139" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E139" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="F139" s="5"/>
-      <c r="G139" s="39"/>
-      <c r="H139" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I139" s="39"/>
+      <c r="G139" s="37"/>
+      <c r="H139" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="I139" s="37"/>
       <c r="J139" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" s="36"/>
-      <c r="B140" s="39"/>
-      <c r="C140" s="39" t="s">
+      <c r="A140" s="34"/>
+      <c r="B140" s="37"/>
+      <c r="C140" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D140" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="D140" s="39" t="s">
-        <v>48</v>
-      </c>
       <c r="E140" s="5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F140" s="5"/>
-      <c r="G140" s="39"/>
-      <c r="H140" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="I140" s="39"/>
+      <c r="G140" s="37"/>
+      <c r="H140" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I140" s="37"/>
       <c r="J140" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B141" s="44">
+      <c r="A141" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B141" s="42">
         <v>9</v>
       </c>
-      <c r="C141" s="25">
+      <c r="C141" s="24">
         <v>10</v>
       </c>
-      <c r="D141" s="30">
+      <c r="D141" s="29">
         <v>11</v>
       </c>
-      <c r="E141" s="25">
+      <c r="E141" s="24">
         <v>14</v>
       </c>
-      <c r="F141" s="35">
+      <c r="F141" s="33">
         <v>15</v>
       </c>
-      <c r="G141" s="31">
+      <c r="G141" s="30">
         <v>16</v>
       </c>
-      <c r="H141" s="25">
+      <c r="H141" s="24">
         <v>17</v>
       </c>
-      <c r="I141" s="25">
+      <c r="I141" s="24">
         <v>18</v>
       </c>
       <c r="J141" t="s">
@@ -4475,10 +4487,10 @@
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="12"/>
-      <c r="B142" s="39"/>
+      <c r="B142" s="37"/>
       <c r="C142" s="9"/>
       <c r="D142" s="9" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
@@ -4490,79 +4502,79 @@
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="36"/>
-      <c r="B143" s="39"/>
-      <c r="C143" s="39"/>
-      <c r="D143" s="39" t="s">
-        <v>45</v>
+      <c r="A143" s="34"/>
+      <c r="B143" s="37"/>
+      <c r="C143" s="37"/>
+      <c r="D143" s="37" t="s">
+        <v>30</v>
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
-      <c r="G143" s="39"/>
-      <c r="H143" s="39"/>
-      <c r="I143" s="39"/>
+      <c r="G143" s="37"/>
+      <c r="H143" s="37"/>
+      <c r="I143" s="37"/>
       <c r="J143" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" s="36"/>
-      <c r="B144" s="39"/>
-      <c r="C144" s="39"/>
-      <c r="D144" s="39" t="s">
-        <v>67</v>
+      <c r="A144" s="34"/>
+      <c r="B144" s="37"/>
+      <c r="C144" s="37"/>
+      <c r="D144" s="37" t="s">
+        <v>50</v>
       </c>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
-      <c r="G144" s="39"/>
-      <c r="H144" s="39"/>
-      <c r="I144" s="39"/>
+      <c r="G144" s="37"/>
+      <c r="H144" s="37"/>
+      <c r="I144" s="37"/>
       <c r="J144" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" s="36"/>
-      <c r="B145" s="39"/>
-      <c r="C145" s="39"/>
-      <c r="D145" s="39" t="s">
-        <v>91</v>
+      <c r="A145" s="34"/>
+      <c r="B145" s="37"/>
+      <c r="C145" s="37"/>
+      <c r="D145" s="37" t="s">
+        <v>80</v>
       </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
-      <c r="G145" s="39"/>
-      <c r="H145" s="39"/>
-      <c r="I145" s="39"/>
+      <c r="G145" s="37"/>
+      <c r="H145" s="37"/>
+      <c r="I145" s="37"/>
       <c r="J145" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B146" s="44">
+      <c r="A146" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B146" s="42">
         <v>9</v>
       </c>
-      <c r="C146" s="25">
+      <c r="C146" s="24">
         <v>10</v>
       </c>
-      <c r="D146" s="30">
+      <c r="D146" s="29">
         <v>11</v>
       </c>
-      <c r="E146" s="25">
+      <c r="E146" s="24">
         <v>14</v>
       </c>
-      <c r="F146" s="35">
+      <c r="F146" s="33">
         <v>15</v>
       </c>
-      <c r="G146" s="31">
+      <c r="G146" s="30">
         <v>16</v>
       </c>
-      <c r="H146" s="25">
+      <c r="H146" s="24">
         <v>17</v>
       </c>
-      <c r="I146" s="25">
+      <c r="I146" s="24">
         <v>18</v>
       </c>
       <c r="J146" t="s">
@@ -4571,12 +4583,14 @@
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="12"/>
-      <c r="B147" s="39"/>
-      <c r="C147" s="9"/>
+      <c r="B147" s="37"/>
+      <c r="C147" s="9" t="s">
+        <v>92</v>
+      </c>
       <c r="D147" s="9"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
@@ -4586,79 +4600,85 @@
       </c>
     </row>
     <row r="148" spans="1:10">
-      <c r="A148" s="36"/>
-      <c r="B148" s="39"/>
-      <c r="C148" s="39"/>
-      <c r="D148" s="39"/>
+      <c r="A148" s="34"/>
+      <c r="B148" s="37"/>
+      <c r="C148" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D148" s="37"/>
       <c r="E148" s="5"/>
       <c r="F148" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G148" s="39"/>
-      <c r="H148" s="39"/>
-      <c r="I148" s="39"/>
+        <v>83</v>
+      </c>
+      <c r="G148" s="37"/>
+      <c r="H148" s="37"/>
+      <c r="I148" s="37"/>
       <c r="J148" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" s="36"/>
-      <c r="B149" s="39"/>
-      <c r="C149" s="39"/>
-      <c r="D149" s="39"/>
+      <c r="A149" s="34"/>
+      <c r="B149" s="37"/>
+      <c r="C149" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D149" s="37"/>
       <c r="E149" s="5"/>
       <c r="F149" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G149" s="39"/>
-      <c r="H149" s="39"/>
-      <c r="I149" s="39"/>
+        <v>84</v>
+      </c>
+      <c r="G149" s="37"/>
+      <c r="H149" s="37"/>
+      <c r="I149" s="37"/>
       <c r="J149" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" s="36"/>
-      <c r="B150" s="39"/>
-      <c r="C150" s="39"/>
-      <c r="D150" s="39"/>
+      <c r="A150" s="34"/>
+      <c r="B150" s="37"/>
+      <c r="C150" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="D150" s="37"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G150" s="39"/>
-      <c r="H150" s="39"/>
-      <c r="I150" s="39"/>
+        <v>85</v>
+      </c>
+      <c r="G150" s="37"/>
+      <c r="H150" s="37"/>
+      <c r="I150" s="37"/>
       <c r="J150" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B151" s="44">
+      <c r="A151" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B151" s="42">
         <v>9</v>
       </c>
-      <c r="C151" s="25">
+      <c r="C151" s="24">
         <v>10</v>
       </c>
-      <c r="D151" s="30">
+      <c r="D151" s="29">
         <v>11</v>
       </c>
-      <c r="E151" s="25">
+      <c r="E151" s="24">
         <v>14</v>
       </c>
-      <c r="F151" s="35">
+      <c r="F151" s="33">
         <v>15</v>
       </c>
-      <c r="G151" s="31">
+      <c r="G151" s="30">
         <v>16</v>
       </c>
-      <c r="H151" s="25">
+      <c r="H151" s="24">
         <v>17</v>
       </c>
-      <c r="I151" s="25">
+      <c r="I151" s="24">
         <v>18</v>
       </c>
       <c r="J151" t="s">
@@ -4667,17 +4687,17 @@
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="12"/>
-      <c r="B152" s="39"/>
+      <c r="B152" s="37"/>
       <c r="C152" s="9" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="9" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="H152" s="9"/>
       <c r="I152" s="9"/>
@@ -4686,61 +4706,61 @@
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="36"/>
-      <c r="B153" s="39"/>
-      <c r="C153" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D153" s="39" t="s">
-        <v>45</v>
+      <c r="A153" s="34"/>
+      <c r="B153" s="37"/>
+      <c r="C153" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D153" s="37" t="s">
+        <v>30</v>
       </c>
       <c r="E153" s="5"/>
       <c r="F153" s="5"/>
-      <c r="G153" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="H153" s="39"/>
-      <c r="I153" s="39"/>
+      <c r="G153" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H153" s="37"/>
+      <c r="I153" s="37"/>
       <c r="J153" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="36"/>
-      <c r="B154" s="39"/>
-      <c r="C154" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="D154" s="39" t="s">
-        <v>59</v>
+      <c r="A154" s="34"/>
+      <c r="B154" s="37"/>
+      <c r="C154" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D154" s="37" t="s">
+        <v>87</v>
       </c>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
-      <c r="G154" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="H154" s="39"/>
-      <c r="I154" s="39"/>
+      <c r="G154" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="H154" s="37"/>
+      <c r="I154" s="37"/>
       <c r="J154" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="36"/>
-      <c r="B155" s="39"/>
-      <c r="C155" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="D155" s="39" t="s">
-        <v>60</v>
+      <c r="A155" s="34"/>
+      <c r="B155" s="37"/>
+      <c r="C155" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="D155" s="37" t="s">
+        <v>90</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
-      <c r="G155" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="H155" s="39"/>
-      <c r="I155" s="39"/>
+      <c r="G155" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H155" s="37"/>
+      <c r="I155" s="37"/>
       <c r="J155" t="s">
         <v>1</v>
       </c>

--- a/test.xlsx
+++ b/test.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>1.10.25</t>
   </si>
@@ -318,6 +318,54 @@
   </si>
   <si>
     <t>аооппо</t>
+  </si>
+  <si>
+    <t>Алсу</t>
+  </si>
+  <si>
+    <t>я люблю тебя</t>
+  </si>
+  <si>
+    <t>мосо</t>
+  </si>
+  <si>
+    <t>мтвт</t>
+  </si>
+  <si>
+    <t>мослпл</t>
+  </si>
+  <si>
+    <t>моа</t>
+  </si>
+  <si>
+    <t>мооа</t>
+  </si>
+  <si>
+    <t>моаоом</t>
+  </si>
+  <si>
+    <t>мадп</t>
+  </si>
+  <si>
+    <t>мопо</t>
+  </si>
+  <si>
+    <t>мллслп</t>
+  </si>
+  <si>
+    <t>Любитмаксимку</t>
+  </si>
+  <si>
+    <t>ятактебялюблюкошкаааа</t>
+  </si>
+  <si>
+    <t>мара</t>
+  </si>
+  <si>
+    <t>аттпа</t>
+  </si>
+  <si>
+    <t>плпооп</t>
   </si>
 </sst>
 </file>
@@ -4488,7 +4536,9 @@
     <row r="142" spans="1:10">
       <c r="A142" s="12"/>
       <c r="B142" s="37"/>
-      <c r="C142" s="9"/>
+      <c r="C142" s="9" t="s">
+        <v>109</v>
+      </c>
       <c r="D142" s="9" t="s">
         <v>29</v>
       </c>
@@ -4504,7 +4554,9 @@
     <row r="143" spans="1:10">
       <c r="A143" s="34"/>
       <c r="B143" s="37"/>
-      <c r="C143" s="37"/>
+      <c r="C143" s="37" t="s">
+        <v>110</v>
+      </c>
       <c r="D143" s="37" t="s">
         <v>30</v>
       </c>
@@ -4520,7 +4572,9 @@
     <row r="144" spans="1:10">
       <c r="A144" s="34"/>
       <c r="B144" s="37"/>
-      <c r="C144" s="37"/>
+      <c r="C144" s="37" t="s">
+        <v>50</v>
+      </c>
       <c r="D144" s="37" t="s">
         <v>50</v>
       </c>
@@ -4536,7 +4590,9 @@
     <row r="145" spans="1:10">
       <c r="A145" s="34"/>
       <c r="B145" s="37"/>
-      <c r="C145" s="37"/>
+      <c r="C145" s="37" t="s">
+        <v>111</v>
+      </c>
       <c r="D145" s="37" t="s">
         <v>80</v>
       </c>
@@ -4583,7 +4639,9 @@
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="12"/>
-      <c r="B147" s="37"/>
+      <c r="B147" s="37" t="s">
+        <v>104</v>
+      </c>
       <c r="C147" s="9" t="s">
         <v>92</v>
       </c>
@@ -4601,7 +4659,9 @@
     </row>
     <row r="148" spans="1:10">
       <c r="A148" s="34"/>
-      <c r="B148" s="37"/>
+      <c r="B148" s="37" t="s">
+        <v>105</v>
+      </c>
       <c r="C148" s="37" t="s">
         <v>93</v>
       </c>
@@ -4619,7 +4679,9 @@
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="34"/>
-      <c r="B149" s="37"/>
+      <c r="B149" s="37" t="s">
+        <v>50</v>
+      </c>
       <c r="C149" s="37" t="s">
         <v>94</v>
       </c>
@@ -4637,7 +4699,9 @@
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="34"/>
-      <c r="B150" s="37"/>
+      <c r="B150" s="37" t="s">
+        <v>106</v>
+      </c>
       <c r="C150" s="37" t="s">
         <v>95</v>
       </c>
@@ -4687,19 +4751,27 @@
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="12"/>
-      <c r="B152" s="37"/>
+      <c r="B152" s="37" t="s">
+        <v>96</v>
+      </c>
       <c r="C152" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D152" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
+      <c r="E152" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="G152" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H152" s="9"/>
+      <c r="H152" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="I152" s="9"/>
       <c r="J152" t="s">
         <v>1</v>
@@ -4707,19 +4779,27 @@
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="34"/>
-      <c r="B153" s="37"/>
+      <c r="B153" s="37" t="s">
+        <v>73</v>
+      </c>
       <c r="C153" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D153" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E153" s="5"/>
-      <c r="F153" s="5"/>
+      <c r="E153" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>102</v>
+      </c>
       <c r="G153" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="H153" s="37"/>
+      <c r="H153" s="37" t="s">
+        <v>107</v>
+      </c>
       <c r="I153" s="37"/>
       <c r="J153" t="s">
         <v>1</v>
@@ -4727,19 +4807,27 @@
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="34"/>
-      <c r="B154" s="37"/>
+      <c r="B154" s="37" t="s">
+        <v>65</v>
+      </c>
       <c r="C154" s="37" t="s">
         <v>50</v>
       </c>
       <c r="D154" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="E154" s="5"/>
-      <c r="F154" s="5"/>
+      <c r="E154" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="G154" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H154" s="37"/>
+      <c r="H154" s="37" t="s">
+        <v>65</v>
+      </c>
       <c r="I154" s="37"/>
       <c r="J154" t="s">
         <v>1</v>
@@ -4747,19 +4835,27 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="34"/>
-      <c r="B155" s="37"/>
+      <c r="B155" s="37" t="s">
+        <v>97</v>
+      </c>
       <c r="C155" s="37" t="s">
         <v>89</v>
       </c>
       <c r="D155" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="E155" s="5"/>
-      <c r="F155" s="5"/>
+      <c r="E155" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="G155" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="H155" s="37"/>
+      <c r="H155" s="37" t="s">
+        <v>108</v>
+      </c>
       <c r="I155" s="37"/>
       <c r="J155" t="s">
         <v>1</v>

--- a/test.xlsx
+++ b/test.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29420"/>
   <workbookPr filterPrivacy="true"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
@@ -30,9 +30,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
-  <si>
-    <t>1.10.25</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+  <si>
+    <t>01.10.25</t>
   </si>
   <si>
     <t>|</t>
@@ -65,28 +65,28 @@
     <t>bgdgdfg</t>
   </si>
   <si>
-    <t>2.10.25</t>
-  </si>
-  <si>
-    <t>3.10.25</t>
-  </si>
-  <si>
-    <t>4.10.25</t>
-  </si>
-  <si>
-    <t>5.10.25</t>
-  </si>
-  <si>
-    <t>6.10.25</t>
-  </si>
-  <si>
-    <t>7.10.25</t>
-  </si>
-  <si>
-    <t>8.10.25</t>
-  </si>
-  <si>
-    <t>9.10.25</t>
+    <t>02.10.25</t>
+  </si>
+  <si>
+    <t>03.10.25</t>
+  </si>
+  <si>
+    <t>04.10.25</t>
+  </si>
+  <si>
+    <t>05.10.25</t>
+  </si>
+  <si>
+    <t>06.10.25</t>
+  </si>
+  <si>
+    <t>07.10.25</t>
+  </si>
+  <si>
+    <t>08.10.25</t>
+  </si>
+  <si>
+    <t>09.10.25</t>
   </si>
   <si>
     <t>10.10.25</t>
@@ -272,100 +272,112 @@
     <t>29.10.25</t>
   </si>
   <si>
+    <t>мара</t>
+  </si>
+  <si>
+    <t>аттпа</t>
+  </si>
+  <si>
+    <t>плпооп</t>
+  </si>
+  <si>
     <t>стаоа</t>
   </si>
   <si>
     <t>30.10.25</t>
   </si>
   <si>
+    <t>мадп</t>
+  </si>
+  <si>
+    <t>поао</t>
+  </si>
+  <si>
     <t>Рао</t>
   </si>
   <si>
+    <t>мопо</t>
+  </si>
+  <si>
+    <t>попр</t>
+  </si>
+  <si>
     <t>Ара</t>
   </si>
   <si>
+    <t>89157446546</t>
+  </si>
+  <si>
     <t>Поп</t>
   </si>
   <si>
+    <t>мллслп</t>
+  </si>
+  <si>
+    <t>аооппо</t>
+  </si>
+  <si>
     <t>Аоп</t>
   </si>
   <si>
     <t>31.10.25</t>
   </si>
   <si>
+    <t>Алсу</t>
+  </si>
+  <si>
+    <t>мосо</t>
+  </si>
+  <si>
+    <t>моа</t>
+  </si>
+  <si>
+    <t>мтвт</t>
+  </si>
+  <si>
+    <t>мооа</t>
+  </si>
+  <si>
+    <t>Любитмаксимку</t>
+  </si>
+  <si>
     <t>ар им</t>
   </si>
   <si>
     <t>оаоп</t>
   </si>
   <si>
+    <t>я люблю тебя</t>
+  </si>
+  <si>
     <t>поарапоа</t>
   </si>
   <si>
     <t>арар</t>
   </si>
   <si>
+    <t>мослпл</t>
+  </si>
+  <si>
+    <t>моаоом</t>
+  </si>
+  <si>
     <t>врра</t>
   </si>
   <si>
-    <t>поао</t>
-  </si>
-  <si>
-    <t>попр</t>
-  </si>
-  <si>
-    <t>89157446546</t>
-  </si>
-  <si>
-    <t>аооппо</t>
-  </si>
-  <si>
-    <t>Алсу</t>
-  </si>
-  <si>
-    <t>я люблю тебя</t>
-  </si>
-  <si>
-    <t>мосо</t>
-  </si>
-  <si>
-    <t>мтвт</t>
-  </si>
-  <si>
-    <t>мослпл</t>
-  </si>
-  <si>
-    <t>моа</t>
-  </si>
-  <si>
-    <t>мооа</t>
-  </si>
-  <si>
-    <t>моаоом</t>
-  </si>
-  <si>
-    <t>мадп</t>
-  </si>
-  <si>
-    <t>мопо</t>
-  </si>
-  <si>
-    <t>мллслп</t>
-  </si>
-  <si>
-    <t>Любитмаксимку</t>
-  </si>
-  <si>
     <t>ятактебялюблюкошкаааа</t>
   </si>
   <si>
-    <t>мара</t>
-  </si>
-  <si>
-    <t>аттпа</t>
-  </si>
-  <si>
-    <t>плпооп</t>
+    <t>имя</t>
+  </si>
+  <si>
+    <t>фамилия</t>
+  </si>
+  <si>
+    <t>+78765678765</t>
+  </si>
+  <si>
+    <t>описание</t>
   </si>
 </sst>
 </file>
@@ -620,9 +632,6 @@
     <xf numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
@@ -654,6 +663,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="true" applyAlignment="true">
@@ -965,7 +977,7 @@
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32">
+      <c r="B1" s="31">
         <v>9</v>
       </c>
       <c r="C1" s="24">
@@ -977,7 +989,7 @@
       <c r="E1" s="24">
         <v>14</v>
       </c>
-      <c r="F1" s="33">
+      <c r="F1" s="32">
         <v>15</v>
       </c>
       <c r="G1" s="24">
@@ -1014,7 +1026,7 @@
       <c r="AH1" s="1"/>
     </row>
     <row r="2" spans="1:34">
-      <c r="A2" s="34"/>
+      <c r="A2" s="33"/>
       <c r="B2" s="13" t="s">
         <v>2</v>
       </c>
@@ -1060,7 +1072,7 @@
       <c r="AH2" s="1"/>
     </row>
     <row r="3" spans="1:34">
-      <c r="A3" s="34"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
@@ -1106,7 +1118,7 @@
       <c r="AH3" s="1"/>
     </row>
     <row r="4" spans="1:34">
-      <c r="A4" s="34"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="5">
         <v>54656</v>
       </c>
@@ -1152,7 +1164,7 @@
       <c r="AH4" s="1"/>
     </row>
     <row r="5" spans="1:34">
-      <c r="A5" s="34"/>
+      <c r="A5" s="33"/>
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -1201,7 +1213,7 @@
       <c r="A6" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="34">
         <v>9</v>
       </c>
       <c r="C6" s="26">
@@ -1213,7 +1225,7 @@
       <c r="E6" s="26">
         <v>14</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="35">
         <v>15</v>
       </c>
       <c r="G6" s="26">
@@ -1245,18 +1257,18 @@
     </row>
     <row r="7" spans="1:34">
       <c r="A7" s="12"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
       <c r="D7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
       <c r="G7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
       <c r="J7" t="s">
         <v>1</v>
       </c>
@@ -1264,11 +1276,11 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="31"/>
-      <c r="AA7" s="31"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="42"/>
+      <c r="Y7" s="42"/>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="42"/>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
@@ -1276,19 +1288,19 @@
       <c r="AF7" s="6"/>
     </row>
     <row r="8" spans="1:34">
-      <c r="A8" s="34"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
       <c r="G8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
       <c r="J8" t="s">
         <v>1</v>
       </c>
@@ -1308,19 +1320,19 @@
       <c r="AF8" s="6"/>
     </row>
     <row r="9" spans="1:34">
-      <c r="A9" s="34"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
       <c r="D9" s="16">
         <v>6574565</v>
       </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
       <c r="G9" s="16">
         <v>3129792</v>
       </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
       <c r="J9" t="s">
         <v>1</v>
       </c>
@@ -1329,8 +1341,8 @@
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="4"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="31"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="42"/>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
@@ -1340,19 +1352,19 @@
       <c r="AF9" s="6"/>
     </row>
     <row r="10" spans="1:34">
-      <c r="A10" s="34"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
       <c r="D10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
       <c r="G10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
       <c r="J10" t="s">
         <v>1</v>
       </c>
@@ -1375,7 +1387,7 @@
       <c r="A11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="31">
         <v>9</v>
       </c>
       <c r="C11" s="24">
@@ -1387,7 +1399,7 @@
       <c r="E11" s="24">
         <v>14</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="32">
         <v>15</v>
       </c>
       <c r="G11" s="24">
@@ -1419,11 +1431,11 @@
     </row>
     <row r="12" spans="1:34">
       <c r="A12" s="12"/>
-      <c r="B12" s="39"/>
+      <c r="B12" s="38"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
-      <c r="F12" s="40"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
@@ -1447,14 +1459,14 @@
     </row>
     <row r="13" spans="1:34">
       <c r="A13" s="12"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
       <c r="J13" t="s">
         <v>1</v>
       </c>
@@ -1474,15 +1486,15 @@
       <c r="AF13" s="6"/>
     </row>
     <row r="14" spans="1:34">
-      <c r="A14" s="34"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
       <c r="J14" t="s">
         <v>1</v>
       </c>
@@ -1502,15 +1514,15 @@
       <c r="AF14" s="6"/>
     </row>
     <row r="15" spans="1:34">
-      <c r="A15" s="34"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
       <c r="J15" t="s">
         <v>1</v>
       </c>
@@ -1533,7 +1545,7 @@
       <c r="A16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="40">
         <v>9</v>
       </c>
       <c r="C16" s="26">
@@ -1545,7 +1557,7 @@
       <c r="E16" s="24">
         <v>14</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="32">
         <v>15</v>
       </c>
       <c r="G16" s="24">
@@ -1664,7 +1676,7 @@
       <c r="AF18" s="6"/>
     </row>
     <row r="19" spans="1:32">
-      <c r="A19" s="34"/>
+      <c r="A19" s="33"/>
       <c r="B19" s="5">
         <v>6574565</v>
       </c>
@@ -1708,7 +1720,7 @@
       <c r="AF19" s="6"/>
     </row>
     <row r="20" spans="1:32">
-      <c r="A20" s="34"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
@@ -1744,7 +1756,7 @@
       <c r="X20" s="17"/>
       <c r="Y20" s="17"/>
       <c r="Z20" s="17"/>
-      <c r="AA20" s="31"/>
+      <c r="AA20" s="42"/>
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="2"/>
@@ -1755,7 +1767,7 @@
       <c r="A21" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="34">
         <v>9</v>
       </c>
       <c r="C21" s="26">
@@ -1767,7 +1779,7 @@
       <c r="E21" s="26">
         <v>14</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="35">
         <v>15</v>
       </c>
       <c r="G21" s="26">
@@ -1790,7 +1802,7 @@
       <c r="X21" s="17"/>
       <c r="Y21" s="17"/>
       <c r="Z21" s="17"/>
-      <c r="AA21" s="31"/>
+      <c r="AA21" s="42"/>
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
@@ -1799,7 +1811,7 @@
     </row>
     <row r="22" spans="1:32">
       <c r="A22" s="12"/>
-      <c r="B22" s="37"/>
+      <c r="B22" s="36"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="5" t="s">
@@ -1830,19 +1842,19 @@
       <c r="AF22" s="6"/>
     </row>
     <row r="23" spans="1:32">
-      <c r="A23" s="34"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
       <c r="E23" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
       <c r="J23" t="s">
         <v>1</v>
       </c>
@@ -1851,8 +1863,8 @@
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="4"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
+      <c r="X23" s="42"/>
+      <c r="Y23" s="42"/>
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
       <c r="AB23" s="2"/>
@@ -1862,19 +1874,19 @@
       <c r="AF23" s="6"/>
     </row>
     <row r="24" spans="1:32">
-      <c r="A24" s="34"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
       <c r="E24" s="5">
         <v>6574565</v>
       </c>
       <c r="F24" s="5">
         <v>6574565</v>
       </c>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
       <c r="J24" t="s">
         <v>1</v>
       </c>
@@ -1883,8 +1895,8 @@
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
       <c r="W24" s="4"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
+      <c r="X24" s="42"/>
+      <c r="Y24" s="42"/>
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
@@ -1894,19 +1906,19 @@
       <c r="AF24" s="6"/>
     </row>
     <row r="25" spans="1:32">
-      <c r="A25" s="34"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
       <c r="E25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
       <c r="J25" t="s">
         <v>1</v>
       </c>
@@ -1915,8 +1927,8 @@
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
       <c r="W25" s="4"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
+      <c r="X25" s="42"/>
+      <c r="Y25" s="42"/>
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
@@ -1929,7 +1941,7 @@
       <c r="A26" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="35">
+      <c r="B26" s="34">
         <v>9</v>
       </c>
       <c r="C26" s="26">
@@ -1941,7 +1953,7 @@
       <c r="E26" s="26">
         <v>14</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="35">
         <v>15</v>
       </c>
       <c r="G26" s="28">
@@ -1973,7 +1985,7 @@
     </row>
     <row r="27" spans="1:32">
       <c r="A27" s="12"/>
-      <c r="B27" s="37"/>
+      <c r="B27" s="36"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="5"/>
@@ -1989,8 +2001,8 @@
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
       <c r="W27" s="4"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
+      <c r="X27" s="42"/>
+      <c r="Y27" s="42"/>
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
@@ -2000,15 +2012,15 @@
       <c r="AF27" s="6"/>
     </row>
     <row r="28" spans="1:32">
-      <c r="A28" s="34"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
+      <c r="A28" s="33"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
       <c r="J28" t="s">
         <v>1</v>
       </c>
@@ -2017,8 +2029,8 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="4"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
+      <c r="X28" s="42"/>
+      <c r="Y28" s="42"/>
       <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
@@ -2028,15 +2040,15 @@
       <c r="AF28" s="6"/>
     </row>
     <row r="29" spans="1:32">
-      <c r="A29" s="34"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
       <c r="J29" t="s">
         <v>1</v>
       </c>
@@ -2056,15 +2068,15 @@
       <c r="AF29" s="6"/>
     </row>
     <row r="30" spans="1:32">
-      <c r="A30" s="34"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
+      <c r="A30" s="33"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="37"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
       <c r="J30" t="s">
         <v>1</v>
       </c>
@@ -2087,7 +2099,7 @@
       <c r="A31" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="42">
+      <c r="B31" s="41">
         <v>9</v>
       </c>
       <c r="C31" s="24">
@@ -2099,7 +2111,7 @@
       <c r="E31" s="24">
         <v>14</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="32">
         <v>15</v>
       </c>
       <c r="G31" s="30">
@@ -2131,7 +2143,7 @@
     </row>
     <row r="32" spans="1:32">
       <c r="A32" s="12"/>
-      <c r="B32" s="37"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="5"/>
@@ -2158,15 +2170,15 @@
       <c r="AF32" s="6"/>
     </row>
     <row r="33" spans="1:32">
-      <c r="A33" s="34"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="37"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
       <c r="J33" t="s">
         <v>1</v>
       </c>
@@ -2191,15 +2203,15 @@
       <c r="AF33" s="6"/>
     </row>
     <row r="34" spans="1:32">
-      <c r="A34" s="34"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
       <c r="J34" t="s">
         <v>1</v>
       </c>
@@ -2224,15 +2236,15 @@
       <c r="AF34" s="6"/>
     </row>
     <row r="35" spans="1:32">
-      <c r="A35" s="34"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
       <c r="J35" t="s">
         <v>1</v>
       </c>
@@ -2260,7 +2272,7 @@
       <c r="A36" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="42">
+      <c r="B36" s="41">
         <v>9</v>
       </c>
       <c r="C36" s="24">
@@ -2272,7 +2284,7 @@
       <c r="E36" s="24">
         <v>14</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="32">
         <v>15</v>
       </c>
       <c r="G36" s="30">
@@ -2309,7 +2321,7 @@
     </row>
     <row r="37" spans="1:32">
       <c r="A37" s="12"/>
-      <c r="B37" s="37"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="5"/>
@@ -2341,15 +2353,15 @@
       <c r="AF37" s="6"/>
     </row>
     <row r="38" spans="1:32">
-      <c r="A38" s="34"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
       <c r="J38" t="s">
         <v>1</v>
       </c>
@@ -2374,15 +2386,15 @@
       <c r="AF38" s="6"/>
     </row>
     <row r="39" spans="1:32">
-      <c r="A39" s="34"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
       <c r="J39" t="s">
         <v>1</v>
       </c>
@@ -2407,15 +2419,15 @@
       <c r="AF39" s="6"/>
     </row>
     <row r="40" spans="1:32">
-      <c r="A40" s="34"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
       <c r="J40" t="s">
         <v>1</v>
       </c>
@@ -2443,7 +2455,7 @@
       <c r="A41" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="42">
+      <c r="B41" s="41">
         <v>9</v>
       </c>
       <c r="C41" s="24">
@@ -2455,7 +2467,7 @@
       <c r="E41" s="24">
         <v>14</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="32">
         <v>15</v>
       </c>
       <c r="G41" s="30">
@@ -2492,7 +2504,7 @@
     </row>
     <row r="42" spans="1:32">
       <c r="A42" s="12"/>
-      <c r="B42" s="37"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="5"/>
@@ -2524,15 +2536,15 @@
       <c r="AF42" s="6"/>
     </row>
     <row r="43" spans="1:32">
-      <c r="A43" s="34"/>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
       <c r="J43" t="s">
         <v>1</v>
       </c>
@@ -2557,15 +2569,15 @@
       <c r="AF43" s="6"/>
     </row>
     <row r="44" spans="1:32">
-      <c r="A44" s="34"/>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
+      <c r="A44" s="33"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
       <c r="J44" t="s">
         <v>1</v>
       </c>
@@ -2590,15 +2602,15 @@
       <c r="AF44" s="6"/>
     </row>
     <row r="45" spans="1:32">
-      <c r="A45" s="34"/>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="36"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="37"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
       <c r="J45" t="s">
         <v>1</v>
       </c>
@@ -2626,7 +2638,7 @@
       <c r="A46" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B46" s="42">
+      <c r="B46" s="41">
         <v>9</v>
       </c>
       <c r="C46" s="24">
@@ -2638,7 +2650,7 @@
       <c r="E46" s="24">
         <v>14</v>
       </c>
-      <c r="F46" s="33">
+      <c r="F46" s="32">
         <v>15</v>
       </c>
       <c r="G46" s="30">
@@ -2675,7 +2687,7 @@
     </row>
     <row r="47" spans="1:32">
       <c r="A47" s="12"/>
-      <c r="B47" s="37"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="5"/>
@@ -2707,15 +2719,15 @@
       <c r="AF47" s="6"/>
     </row>
     <row r="48" spans="1:32">
-      <c r="A48" s="34"/>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="36"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
       <c r="J48" t="s">
         <v>1</v>
       </c>
@@ -2740,15 +2752,15 @@
       <c r="AF48" s="6"/>
     </row>
     <row r="49" spans="1:32">
-      <c r="A49" s="34"/>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="36"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="37"/>
-      <c r="I49" s="37"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="36"/>
       <c r="J49" t="s">
         <v>1</v>
       </c>
@@ -2773,15 +2785,15 @@
       <c r="AF49" s="6"/>
     </row>
     <row r="50" spans="1:32">
-      <c r="A50" s="34"/>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="37"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
       <c r="J50" t="s">
         <v>1</v>
       </c>
@@ -2809,7 +2821,7 @@
       <c r="A51" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B51" s="42">
+      <c r="B51" s="41">
         <v>9</v>
       </c>
       <c r="C51" s="24">
@@ -2821,7 +2833,7 @@
       <c r="E51" s="24">
         <v>14</v>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="32">
         <v>15</v>
       </c>
       <c r="G51" s="30">
@@ -2839,7 +2851,7 @@
     </row>
     <row r="52" spans="1:32">
       <c r="A52" s="12"/>
-      <c r="B52" s="37"/>
+      <c r="B52" s="36"/>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="5"/>
@@ -2852,43 +2864,43 @@
       </c>
     </row>
     <row r="53" spans="1:32">
-      <c r="A53" s="34"/>
-      <c r="B53" s="37"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="37"/>
-      <c r="I53" s="37"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
       <c r="J53" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:32">
-      <c r="A54" s="34"/>
-      <c r="B54" s="37"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
+      <c r="A54" s="33"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="37"/>
-      <c r="I54" s="37"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36"/>
       <c r="J54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:32">
-      <c r="A55" s="34"/>
-      <c r="B55" s="37"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
+      <c r="A55" s="33"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
-      <c r="G55" s="37"/>
-      <c r="H55" s="37"/>
-      <c r="I55" s="37"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
       <c r="J55" t="s">
         <v>1</v>
       </c>
@@ -2897,7 +2909,7 @@
       <c r="A56" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="42">
+      <c r="B56" s="41">
         <v>9</v>
       </c>
       <c r="C56" s="24">
@@ -2909,7 +2921,7 @@
       <c r="E56" s="24">
         <v>14</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="32">
         <v>15</v>
       </c>
       <c r="G56" s="30">
@@ -2927,7 +2939,7 @@
     </row>
     <row r="57" spans="1:32">
       <c r="A57" s="12"/>
-      <c r="B57" s="37"/>
+      <c r="B57" s="36"/>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="5"/>
@@ -2940,43 +2952,43 @@
       </c>
     </row>
     <row r="58" spans="1:32">
-      <c r="A58" s="34"/>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
+      <c r="A58" s="33"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="36"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="37"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="36"/>
       <c r="J58" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:32">
-      <c r="A59" s="34"/>
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
+      <c r="A59" s="33"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36"/>
       <c r="J59" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:32">
-      <c r="A60" s="34"/>
-      <c r="B60" s="37"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
+      <c r="A60" s="33"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="36"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="37"/>
+      <c r="G60" s="36"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="36"/>
       <c r="J60" t="s">
         <v>1</v>
       </c>
@@ -2985,7 +2997,7 @@
       <c r="A61" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B61" s="42">
+      <c r="B61" s="41">
         <v>9</v>
       </c>
       <c r="C61" s="24">
@@ -2997,7 +3009,7 @@
       <c r="E61" s="24">
         <v>14</v>
       </c>
-      <c r="F61" s="33">
+      <c r="F61" s="32">
         <v>15</v>
       </c>
       <c r="G61" s="30">
@@ -3015,7 +3027,7 @@
     </row>
     <row r="62" spans="1:32">
       <c r="A62" s="12"/>
-      <c r="B62" s="37"/>
+      <c r="B62" s="36"/>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="5"/>
@@ -3028,43 +3040,43 @@
       </c>
     </row>
     <row r="63" spans="1:32">
-      <c r="A63" s="34"/>
-      <c r="B63" s="37"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
+      <c r="A63" s="33"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="36"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="37"/>
-      <c r="I63" s="37"/>
+      <c r="G63" s="36"/>
+      <c r="H63" s="36"/>
+      <c r="I63" s="36"/>
       <c r="J63" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:32">
-      <c r="A64" s="34"/>
-      <c r="B64" s="37"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
+      <c r="A64" s="33"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
-      <c r="I64" s="37"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="36"/>
+      <c r="I64" s="36"/>
       <c r="J64" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="34"/>
-      <c r="B65" s="37"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="37"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="36"/>
       <c r="J65" t="s">
         <v>1</v>
       </c>
@@ -3073,7 +3085,7 @@
       <c r="A66" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B66" s="42">
+      <c r="B66" s="41">
         <v>9</v>
       </c>
       <c r="C66" s="24">
@@ -3085,7 +3097,7 @@
       <c r="E66" s="24">
         <v>14</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="32">
         <v>15</v>
       </c>
       <c r="G66" s="30">
@@ -3103,7 +3115,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="12"/>
-      <c r="B67" s="37"/>
+      <c r="B67" s="36"/>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
       <c r="E67" s="5"/>
@@ -3116,43 +3128,43 @@
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="34"/>
-      <c r="B68" s="37"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="37"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="I68" s="36"/>
       <c r="J68" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="34"/>
-      <c r="B69" s="37"/>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
+      <c r="A69" s="33"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
-      <c r="G69" s="37"/>
-      <c r="H69" s="37"/>
-      <c r="I69" s="37"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="36"/>
+      <c r="I69" s="36"/>
       <c r="J69" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="34"/>
-      <c r="B70" s="37"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
       <c r="J70" t="s">
         <v>1</v>
       </c>
@@ -3161,7 +3173,7 @@
       <c r="A71" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B71" s="42">
+      <c r="B71" s="41">
         <v>9</v>
       </c>
       <c r="C71" s="24">
@@ -3173,7 +3185,7 @@
       <c r="E71" s="24">
         <v>14</v>
       </c>
-      <c r="F71" s="33">
+      <c r="F71" s="32">
         <v>15</v>
       </c>
       <c r="G71" s="30">
@@ -3191,7 +3203,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="12"/>
-      <c r="B72" s="37"/>
+      <c r="B72" s="36"/>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="5"/>
@@ -3204,43 +3216,43 @@
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="34"/>
-      <c r="B73" s="37"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
+      <c r="A73" s="33"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
       <c r="J73" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="34"/>
-      <c r="B74" s="37"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
+      <c r="A74" s="33"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37"/>
-      <c r="I74" s="37"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
       <c r="J74" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="34"/>
-      <c r="B75" s="37"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
+      <c r="A75" s="33"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
       <c r="J75" t="s">
         <v>1</v>
       </c>
@@ -3249,7 +3261,7 @@
       <c r="A76" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B76" s="42">
+      <c r="B76" s="41">
         <v>9</v>
       </c>
       <c r="C76" s="24">
@@ -3261,7 +3273,7 @@
       <c r="E76" s="24">
         <v>14</v>
       </c>
-      <c r="F76" s="33">
+      <c r="F76" s="32">
         <v>15</v>
       </c>
       <c r="G76" s="30">
@@ -3279,7 +3291,7 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="12"/>
-      <c r="B77" s="37"/>
+      <c r="B77" s="36"/>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="5"/>
@@ -3292,43 +3304,43 @@
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="34"/>
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
+      <c r="A78" s="33"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
+      <c r="G78" s="36"/>
+      <c r="H78" s="36"/>
+      <c r="I78" s="36"/>
       <c r="J78" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="34"/>
-      <c r="B79" s="37"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
-      <c r="G79" s="37"/>
-      <c r="H79" s="37"/>
-      <c r="I79" s="37"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
       <c r="J79" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="34"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
+      <c r="A80" s="33"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
-      <c r="G80" s="37"/>
-      <c r="H80" s="37"/>
-      <c r="I80" s="37"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
       <c r="J80" t="s">
         <v>1</v>
       </c>
@@ -3337,7 +3349,7 @@
       <c r="A81" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B81" s="42">
+      <c r="B81" s="41">
         <v>9</v>
       </c>
       <c r="C81" s="24">
@@ -3349,7 +3361,7 @@
       <c r="E81" s="24">
         <v>14</v>
       </c>
-      <c r="F81" s="33">
+      <c r="F81" s="32">
         <v>15</v>
       </c>
       <c r="G81" s="30">
@@ -3367,7 +3379,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="12"/>
-      <c r="B82" s="37"/>
+      <c r="B82" s="36"/>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="5"/>
@@ -3380,43 +3392,43 @@
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="34"/>
-      <c r="B83" s="37"/>
-      <c r="C83" s="37"/>
-      <c r="D83" s="37"/>
+      <c r="A83" s="33"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="36"/>
+      <c r="D83" s="36"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
-      <c r="G83" s="37"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="37"/>
+      <c r="G83" s="36"/>
+      <c r="H83" s="36"/>
+      <c r="I83" s="36"/>
       <c r="J83" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="34"/>
-      <c r="B84" s="37"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="37"/>
+      <c r="A84" s="33"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
-      <c r="G84" s="37"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="37"/>
+      <c r="G84" s="36"/>
+      <c r="H84" s="36"/>
+      <c r="I84" s="36"/>
       <c r="J84" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="34"/>
-      <c r="B85" s="37"/>
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
+      <c r="A85" s="33"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="36"/>
+      <c r="D85" s="36"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
-      <c r="G85" s="37"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
+      <c r="G85" s="36"/>
+      <c r="H85" s="36"/>
+      <c r="I85" s="36"/>
       <c r="J85" t="s">
         <v>1</v>
       </c>
@@ -3425,7 +3437,7 @@
       <c r="A86" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B86" s="42">
+      <c r="B86" s="41">
         <v>9</v>
       </c>
       <c r="C86" s="24">
@@ -3437,7 +3449,7 @@
       <c r="E86" s="24">
         <v>14</v>
       </c>
-      <c r="F86" s="33">
+      <c r="F86" s="32">
         <v>15</v>
       </c>
       <c r="G86" s="30">
@@ -3455,7 +3467,7 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="12"/>
-      <c r="B87" s="37"/>
+      <c r="B87" s="36"/>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
       <c r="E87" s="5"/>
@@ -3468,43 +3480,43 @@
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="34"/>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
+      <c r="A88" s="33"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="36"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="36"/>
       <c r="J88" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="34"/>
-      <c r="B89" s="37"/>
-      <c r="C89" s="37"/>
-      <c r="D89" s="37"/>
+      <c r="A89" s="33"/>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
-      <c r="G89" s="37"/>
-      <c r="H89" s="37"/>
-      <c r="I89" s="37"/>
+      <c r="G89" s="36"/>
+      <c r="H89" s="36"/>
+      <c r="I89" s="36"/>
       <c r="J89" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="34"/>
-      <c r="B90" s="37"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
+      <c r="A90" s="33"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="36"/>
+      <c r="D90" s="36"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
-      <c r="G90" s="37"/>
-      <c r="H90" s="37"/>
-      <c r="I90" s="37"/>
+      <c r="G90" s="36"/>
+      <c r="H90" s="36"/>
+      <c r="I90" s="36"/>
       <c r="J90" t="s">
         <v>1</v>
       </c>
@@ -3513,7 +3525,7 @@
       <c r="A91" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B91" s="42">
+      <c r="B91" s="41">
         <v>9</v>
       </c>
       <c r="C91" s="24">
@@ -3525,7 +3537,7 @@
       <c r="E91" s="24">
         <v>14</v>
       </c>
-      <c r="F91" s="33">
+      <c r="F91" s="32">
         <v>15</v>
       </c>
       <c r="G91" s="30">
@@ -3543,7 +3555,7 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="12"/>
-      <c r="B92" s="37"/>
+      <c r="B92" s="36"/>
       <c r="C92" s="9"/>
       <c r="D92" s="9" t="s">
         <v>29</v>
@@ -3558,49 +3570,49 @@
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="34"/>
-      <c r="B93" s="37"/>
-      <c r="C93" s="37"/>
-      <c r="D93" s="37" t="s">
+      <c r="A93" s="33"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="36" t="s">
         <v>30</v>
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
-      <c r="G93" s="37"/>
-      <c r="H93" s="37"/>
-      <c r="I93" s="37"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
       <c r="J93" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="34"/>
-      <c r="B94" s="37"/>
-      <c r="C94" s="37"/>
-      <c r="D94" s="37" t="s">
+      <c r="A94" s="33"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="36"/>
+      <c r="D94" s="36" t="s">
         <v>31</v>
       </c>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
-      <c r="G94" s="37"/>
-      <c r="H94" s="37"/>
-      <c r="I94" s="37"/>
+      <c r="G94" s="36"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="36"/>
       <c r="J94" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="34"/>
-      <c r="B95" s="37"/>
-      <c r="C95" s="37"/>
-      <c r="D95" s="37" t="s">
+      <c r="A95" s="33"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36" t="s">
         <v>32</v>
       </c>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
-      <c r="G95" s="37"/>
-      <c r="H95" s="37"/>
-      <c r="I95" s="37"/>
+      <c r="G95" s="36"/>
+      <c r="H95" s="36"/>
+      <c r="I95" s="36"/>
       <c r="J95" t="s">
         <v>1</v>
       </c>
@@ -3609,7 +3621,7 @@
       <c r="A96" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="B96" s="42">
+      <c r="B96" s="41">
         <v>9</v>
       </c>
       <c r="C96" s="24">
@@ -3621,7 +3633,7 @@
       <c r="E96" s="24">
         <v>14</v>
       </c>
-      <c r="F96" s="33">
+      <c r="F96" s="32">
         <v>15</v>
       </c>
       <c r="G96" s="30">
@@ -3639,7 +3651,7 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="12"/>
-      <c r="B97" s="37"/>
+      <c r="B97" s="36"/>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
       <c r="E97" s="5"/>
@@ -3652,43 +3664,43 @@
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="34"/>
-      <c r="B98" s="37"/>
-      <c r="C98" s="37"/>
-      <c r="D98" s="37"/>
+      <c r="A98" s="33"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="36"/>
+      <c r="D98" s="36"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
-      <c r="G98" s="37"/>
-      <c r="H98" s="37"/>
-      <c r="I98" s="37"/>
+      <c r="G98" s="36"/>
+      <c r="H98" s="36"/>
+      <c r="I98" s="36"/>
       <c r="J98" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="34"/>
-      <c r="B99" s="37"/>
-      <c r="C99" s="37"/>
-      <c r="D99" s="37"/>
+      <c r="A99" s="33"/>
+      <c r="B99" s="36"/>
+      <c r="C99" s="36"/>
+      <c r="D99" s="36"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
+      <c r="G99" s="36"/>
+      <c r="H99" s="36"/>
+      <c r="I99" s="36"/>
       <c r="J99" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="34"/>
-      <c r="B100" s="37"/>
-      <c r="C100" s="37"/>
-      <c r="D100" s="37"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="36"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
-      <c r="G100" s="37"/>
-      <c r="H100" s="37"/>
-      <c r="I100" s="37"/>
+      <c r="G100" s="36"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="36"/>
       <c r="J100" t="s">
         <v>1</v>
       </c>
@@ -3697,7 +3709,7 @@
       <c r="A101" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B101" s="42">
+      <c r="B101" s="41">
         <v>9</v>
       </c>
       <c r="C101" s="24">
@@ -3709,7 +3721,7 @@
       <c r="E101" s="24">
         <v>14</v>
       </c>
-      <c r="F101" s="33">
+      <c r="F101" s="32">
         <v>15</v>
       </c>
       <c r="G101" s="30">
@@ -3727,7 +3739,7 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="12"/>
-      <c r="B102" s="37"/>
+      <c r="B102" s="36"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
       <c r="E102" s="5"/>
@@ -3740,43 +3752,43 @@
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="34"/>
-      <c r="B103" s="37"/>
-      <c r="C103" s="37"/>
-      <c r="D103" s="37"/>
+      <c r="A103" s="33"/>
+      <c r="B103" s="36"/>
+      <c r="C103" s="36"/>
+      <c r="D103" s="36"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
-      <c r="G103" s="37"/>
-      <c r="H103" s="37"/>
-      <c r="I103" s="37"/>
+      <c r="G103" s="36"/>
+      <c r="H103" s="36"/>
+      <c r="I103" s="36"/>
       <c r="J103" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="34"/>
-      <c r="B104" s="37"/>
-      <c r="C104" s="37"/>
-      <c r="D104" s="37"/>
+      <c r="A104" s="33"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="36"/>
+      <c r="D104" s="36"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
-      <c r="G104" s="37"/>
-      <c r="H104" s="37"/>
-      <c r="I104" s="37"/>
+      <c r="G104" s="36"/>
+      <c r="H104" s="36"/>
+      <c r="I104" s="36"/>
       <c r="J104" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="34"/>
-      <c r="B105" s="37"/>
-      <c r="C105" s="37"/>
-      <c r="D105" s="37"/>
+      <c r="A105" s="33"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="36"/>
+      <c r="D105" s="36"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5"/>
-      <c r="G105" s="37"/>
-      <c r="H105" s="37"/>
-      <c r="I105" s="37"/>
+      <c r="G105" s="36"/>
+      <c r="H105" s="36"/>
+      <c r="I105" s="36"/>
       <c r="J105" t="s">
         <v>1</v>
       </c>
@@ -3785,7 +3797,7 @@
       <c r="A106" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B106" s="42">
+      <c r="B106" s="41">
         <v>9</v>
       </c>
       <c r="C106" s="24">
@@ -3797,7 +3809,7 @@
       <c r="E106" s="24">
         <v>14</v>
       </c>
-      <c r="F106" s="33">
+      <c r="F106" s="32">
         <v>15</v>
       </c>
       <c r="G106" s="30">
@@ -3815,7 +3827,7 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="12"/>
-      <c r="B107" s="37"/>
+      <c r="B107" s="36"/>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="5"/>
@@ -3828,43 +3840,43 @@
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="34"/>
-      <c r="B108" s="37"/>
-      <c r="C108" s="37"/>
-      <c r="D108" s="37"/>
+      <c r="A108" s="33"/>
+      <c r="B108" s="36"/>
+      <c r="C108" s="36"/>
+      <c r="D108" s="36"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
-      <c r="G108" s="37"/>
-      <c r="H108" s="37"/>
-      <c r="I108" s="37"/>
+      <c r="G108" s="36"/>
+      <c r="H108" s="36"/>
+      <c r="I108" s="36"/>
       <c r="J108" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="34"/>
-      <c r="B109" s="37"/>
-      <c r="C109" s="37"/>
-      <c r="D109" s="37"/>
+      <c r="A109" s="33"/>
+      <c r="B109" s="36"/>
+      <c r="C109" s="36"/>
+      <c r="D109" s="36"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
-      <c r="G109" s="37"/>
-      <c r="H109" s="37"/>
-      <c r="I109" s="37"/>
+      <c r="G109" s="36"/>
+      <c r="H109" s="36"/>
+      <c r="I109" s="36"/>
       <c r="J109" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="34"/>
-      <c r="B110" s="37"/>
-      <c r="C110" s="37"/>
-      <c r="D110" s="37"/>
+      <c r="A110" s="33"/>
+      <c r="B110" s="36"/>
+      <c r="C110" s="36"/>
+      <c r="D110" s="36"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
-      <c r="G110" s="37"/>
-      <c r="H110" s="37"/>
-      <c r="I110" s="37"/>
+      <c r="G110" s="36"/>
+      <c r="H110" s="36"/>
+      <c r="I110" s="36"/>
       <c r="J110" t="s">
         <v>1</v>
       </c>
@@ -3873,7 +3885,7 @@
       <c r="A111" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B111" s="42">
+      <c r="B111" s="41">
         <v>9</v>
       </c>
       <c r="C111" s="24">
@@ -3885,7 +3897,7 @@
       <c r="E111" s="24">
         <v>14</v>
       </c>
-      <c r="F111" s="33">
+      <c r="F111" s="32">
         <v>15</v>
       </c>
       <c r="G111" s="30">
@@ -3903,7 +3915,7 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="12"/>
-      <c r="B112" s="37"/>
+      <c r="B112" s="36"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="5"/>
@@ -3916,43 +3928,43 @@
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="34"/>
-      <c r="B113" s="37"/>
-      <c r="C113" s="37"/>
-      <c r="D113" s="37"/>
+      <c r="A113" s="33"/>
+      <c r="B113" s="36"/>
+      <c r="C113" s="36"/>
+      <c r="D113" s="36"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
-      <c r="G113" s="37"/>
-      <c r="H113" s="37"/>
-      <c r="I113" s="37"/>
+      <c r="G113" s="36"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36"/>
       <c r="J113" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="34"/>
-      <c r="B114" s="37"/>
-      <c r="C114" s="37"/>
-      <c r="D114" s="37"/>
+      <c r="A114" s="33"/>
+      <c r="B114" s="36"/>
+      <c r="C114" s="36"/>
+      <c r="D114" s="36"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
-      <c r="G114" s="37"/>
-      <c r="H114" s="37"/>
-      <c r="I114" s="37"/>
+      <c r="G114" s="36"/>
+      <c r="H114" s="36"/>
+      <c r="I114" s="36"/>
       <c r="J114" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="34"/>
-      <c r="B115" s="37"/>
-      <c r="C115" s="37"/>
-      <c r="D115" s="37"/>
+      <c r="A115" s="33"/>
+      <c r="B115" s="36"/>
+      <c r="C115" s="36"/>
+      <c r="D115" s="36"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
-      <c r="G115" s="37"/>
-      <c r="H115" s="37"/>
-      <c r="I115" s="37"/>
+      <c r="G115" s="36"/>
+      <c r="H115" s="36"/>
+      <c r="I115" s="36"/>
       <c r="J115" t="s">
         <v>1</v>
       </c>
@@ -3961,7 +3973,7 @@
       <c r="A116" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B116" s="42">
+      <c r="B116" s="41">
         <v>9</v>
       </c>
       <c r="C116" s="24">
@@ -3973,7 +3985,7 @@
       <c r="E116" s="24">
         <v>14</v>
       </c>
-      <c r="F116" s="33">
+      <c r="F116" s="32">
         <v>15</v>
       </c>
       <c r="G116" s="30">
@@ -3991,7 +4003,7 @@
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="12"/>
-      <c r="B117" s="37"/>
+      <c r="B117" s="36"/>
       <c r="C117" s="9" t="s">
         <v>38</v>
       </c>
@@ -4006,49 +4018,49 @@
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="34"/>
-      <c r="B118" s="37"/>
-      <c r="C118" s="37" t="s">
+      <c r="A118" s="33"/>
+      <c r="B118" s="36"/>
+      <c r="C118" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D118" s="37"/>
+      <c r="D118" s="36"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
-      <c r="G118" s="37"/>
-      <c r="H118" s="37"/>
-      <c r="I118" s="37"/>
+      <c r="G118" s="36"/>
+      <c r="H118" s="36"/>
+      <c r="I118" s="36"/>
       <c r="J118" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="34"/>
-      <c r="B119" s="37"/>
-      <c r="C119" s="37" t="s">
+      <c r="A119" s="33"/>
+      <c r="B119" s="36"/>
+      <c r="C119" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D119" s="37"/>
+      <c r="D119" s="36"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
-      <c r="G119" s="37"/>
-      <c r="H119" s="37"/>
-      <c r="I119" s="37"/>
+      <c r="G119" s="36"/>
+      <c r="H119" s="36"/>
+      <c r="I119" s="36"/>
       <c r="J119" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="34"/>
-      <c r="B120" s="37"/>
-      <c r="C120" s="37" t="s">
+      <c r="A120" s="33"/>
+      <c r="B120" s="36"/>
+      <c r="C120" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D120" s="37"/>
+      <c r="D120" s="36"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
-      <c r="G120" s="37"/>
-      <c r="H120" s="37"/>
-      <c r="I120" s="37"/>
+      <c r="G120" s="36"/>
+      <c r="H120" s="36"/>
+      <c r="I120" s="36"/>
       <c r="J120" t="s">
         <v>1</v>
       </c>
@@ -4057,7 +4069,7 @@
       <c r="A121" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B121" s="42">
+      <c r="B121" s="41">
         <v>9</v>
       </c>
       <c r="C121" s="24">
@@ -4069,7 +4081,7 @@
       <c r="E121" s="24">
         <v>14</v>
       </c>
-      <c r="F121" s="33">
+      <c r="F121" s="32">
         <v>15</v>
       </c>
       <c r="G121" s="30">
@@ -4087,7 +4099,7 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="12"/>
-      <c r="B122" s="37"/>
+      <c r="B122" s="36"/>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="5" t="s">
@@ -4102,49 +4114,49 @@
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="34"/>
-      <c r="B123" s="37"/>
-      <c r="C123" s="37"/>
-      <c r="D123" s="37"/>
+      <c r="A123" s="33"/>
+      <c r="B123" s="36"/>
+      <c r="C123" s="36"/>
+      <c r="D123" s="36"/>
       <c r="E123" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F123" s="5"/>
-      <c r="G123" s="37"/>
-      <c r="H123" s="37"/>
-      <c r="I123" s="37"/>
+      <c r="G123" s="36"/>
+      <c r="H123" s="36"/>
+      <c r="I123" s="36"/>
       <c r="J123" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="34"/>
-      <c r="B124" s="37"/>
-      <c r="C124" s="37"/>
-      <c r="D124" s="37"/>
+      <c r="A124" s="33"/>
+      <c r="B124" s="36"/>
+      <c r="C124" s="36"/>
+      <c r="D124" s="36"/>
       <c r="E124" s="5" t="s">
         <v>44</v>
       </c>
       <c r="F124" s="5"/>
-      <c r="G124" s="37"/>
-      <c r="H124" s="37"/>
-      <c r="I124" s="37"/>
+      <c r="G124" s="36"/>
+      <c r="H124" s="36"/>
+      <c r="I124" s="36"/>
       <c r="J124" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="34"/>
-      <c r="B125" s="37"/>
-      <c r="C125" s="37"/>
-      <c r="D125" s="37"/>
+      <c r="A125" s="33"/>
+      <c r="B125" s="36"/>
+      <c r="C125" s="36"/>
+      <c r="D125" s="36"/>
       <c r="E125" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F125" s="5"/>
-      <c r="G125" s="37"/>
-      <c r="H125" s="37"/>
-      <c r="I125" s="37"/>
+      <c r="G125" s="36"/>
+      <c r="H125" s="36"/>
+      <c r="I125" s="36"/>
       <c r="J125" t="s">
         <v>1</v>
       </c>
@@ -4153,7 +4165,7 @@
       <c r="A126" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B126" s="42">
+      <c r="B126" s="41">
         <v>9</v>
       </c>
       <c r="C126" s="24">
@@ -4165,7 +4177,7 @@
       <c r="E126" s="24">
         <v>14</v>
       </c>
-      <c r="F126" s="33">
+      <c r="F126" s="32">
         <v>15</v>
       </c>
       <c r="G126" s="30">
@@ -4183,7 +4195,7 @@
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="12"/>
-      <c r="B127" s="37" t="s">
+      <c r="B127" s="36" t="s">
         <v>29</v>
       </c>
       <c r="C127" s="9" t="s">
@@ -4202,61 +4214,61 @@
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="A128" s="34"/>
-      <c r="B128" s="37" t="s">
+      <c r="A128" s="33"/>
+      <c r="B128" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="C128" s="37" t="s">
+      <c r="C128" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D128" s="37" t="s">
+      <c r="D128" s="36" t="s">
         <v>48</v>
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
-      <c r="G128" s="37"/>
-      <c r="H128" s="37"/>
-      <c r="I128" s="37"/>
+      <c r="G128" s="36"/>
+      <c r="H128" s="36"/>
+      <c r="I128" s="36"/>
       <c r="J128" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" s="34"/>
-      <c r="B129" s="37" t="s">
+      <c r="A129" s="33"/>
+      <c r="B129" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="C129" s="37" t="s">
+      <c r="C129" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D129" s="37" t="s">
+      <c r="D129" s="36" t="s">
         <v>51</v>
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
-      <c r="G129" s="37"/>
-      <c r="H129" s="37"/>
-      <c r="I129" s="37"/>
+      <c r="G129" s="36"/>
+      <c r="H129" s="36"/>
+      <c r="I129" s="36"/>
       <c r="J129" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="34"/>
-      <c r="B130" s="37" t="s">
+      <c r="A130" s="33"/>
+      <c r="B130" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C130" s="37" t="s">
+      <c r="C130" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D130" s="37" t="s">
+      <c r="D130" s="36" t="s">
         <v>54</v>
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
-      <c r="G130" s="37"/>
-      <c r="H130" s="37"/>
-      <c r="I130" s="37"/>
+      <c r="G130" s="36"/>
+      <c r="H130" s="36"/>
+      <c r="I130" s="36"/>
       <c r="J130" t="s">
         <v>1</v>
       </c>
@@ -4265,7 +4277,7 @@
       <c r="A131" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="B131" s="42">
+      <c r="B131" s="41">
         <v>9</v>
       </c>
       <c r="C131" s="24">
@@ -4277,7 +4289,7 @@
       <c r="E131" s="24">
         <v>14</v>
       </c>
-      <c r="F131" s="33">
+      <c r="F131" s="32">
         <v>15</v>
       </c>
       <c r="G131" s="30">
@@ -4295,7 +4307,7 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="12"/>
-      <c r="B132" s="37" t="s">
+      <c r="B132" s="36" t="s">
         <v>56</v>
       </c>
       <c r="C132" s="9" t="s">
@@ -4316,67 +4328,67 @@
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" s="34"/>
-      <c r="B133" s="37" t="s">
+      <c r="A133" s="33"/>
+      <c r="B133" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="C133" s="37" t="s">
+      <c r="C133" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D133" s="37" t="s">
+      <c r="D133" s="36" t="s">
         <v>62</v>
       </c>
       <c r="E133" s="5" t="s">
         <v>63</v>
       </c>
       <c r="F133" s="5"/>
-      <c r="G133" s="37"/>
-      <c r="H133" s="37"/>
-      <c r="I133" s="37"/>
+      <c r="G133" s="36"/>
+      <c r="H133" s="36"/>
+      <c r="I133" s="36"/>
       <c r="J133" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="34"/>
-      <c r="B134" s="37" t="s">
+      <c r="A134" s="33"/>
+      <c r="B134" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C134" s="37" t="s">
+      <c r="C134" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D134" s="37" t="s">
+      <c r="D134" s="36" t="s">
         <v>65</v>
       </c>
       <c r="E134" s="5" t="s">
         <v>65</v>
       </c>
       <c r="F134" s="5"/>
-      <c r="G134" s="37"/>
-      <c r="H134" s="37"/>
-      <c r="I134" s="37"/>
+      <c r="G134" s="36"/>
+      <c r="H134" s="36"/>
+      <c r="I134" s="36"/>
       <c r="J134" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="A135" s="34"/>
-      <c r="B135" s="37" t="s">
+      <c r="A135" s="33"/>
+      <c r="B135" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C135" s="37" t="s">
+      <c r="C135" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D135" s="37" t="s">
+      <c r="D135" s="36" t="s">
         <v>68</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F135" s="5"/>
-      <c r="G135" s="37"/>
-      <c r="H135" s="37"/>
-      <c r="I135" s="37"/>
+      <c r="G135" s="36"/>
+      <c r="H135" s="36"/>
+      <c r="I135" s="36"/>
       <c r="J135" t="s">
         <v>1</v>
       </c>
@@ -4385,7 +4397,7 @@
       <c r="A136" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B136" s="42">
+      <c r="B136" s="41">
         <v>9</v>
       </c>
       <c r="C136" s="24">
@@ -4397,7 +4409,7 @@
       <c r="E136" s="24">
         <v>14</v>
       </c>
-      <c r="F136" s="33">
+      <c r="F136" s="32">
         <v>15</v>
       </c>
       <c r="G136" s="30">
@@ -4415,7 +4427,7 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="12"/>
-      <c r="B137" s="37"/>
+      <c r="B137" s="36"/>
       <c r="C137" s="9" t="s">
         <v>71</v>
       </c>
@@ -4436,67 +4448,67 @@
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="34"/>
-      <c r="B138" s="37"/>
-      <c r="C138" s="37" t="s">
+      <c r="A138" s="33"/>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="D138" s="37" t="s">
+      <c r="D138" s="36" t="s">
         <v>32</v>
       </c>
       <c r="E138" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F138" s="5"/>
-      <c r="G138" s="37"/>
-      <c r="H138" s="37" t="s">
+      <c r="G138" s="36"/>
+      <c r="H138" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="I138" s="37"/>
+      <c r="I138" s="36"/>
       <c r="J138" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="34"/>
-      <c r="B139" s="37"/>
-      <c r="C139" s="37" t="s">
+      <c r="A139" s="33"/>
+      <c r="B139" s="36"/>
+      <c r="C139" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D139" s="37" t="s">
+      <c r="D139" s="36" t="s">
         <v>74</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>50</v>
       </c>
       <c r="F139" s="5"/>
-      <c r="G139" s="37"/>
-      <c r="H139" s="37" t="s">
+      <c r="G139" s="36"/>
+      <c r="H139" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="I139" s="37"/>
+      <c r="I139" s="36"/>
       <c r="J139" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" s="34"/>
-      <c r="B140" s="37"/>
-      <c r="C140" s="37" t="s">
+      <c r="A140" s="33"/>
+      <c r="B140" s="36"/>
+      <c r="C140" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D140" s="37" t="s">
+      <c r="D140" s="36" t="s">
         <v>72</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>77</v>
       </c>
       <c r="F140" s="5"/>
-      <c r="G140" s="37"/>
-      <c r="H140" s="37" t="s">
+      <c r="G140" s="36"/>
+      <c r="H140" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="I140" s="37"/>
+      <c r="I140" s="36"/>
       <c r="J140" t="s">
         <v>1</v>
       </c>
@@ -4505,7 +4517,7 @@
       <c r="A141" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="B141" s="42">
+      <c r="B141" s="41">
         <v>9</v>
       </c>
       <c r="C141" s="24">
@@ -4517,7 +4529,7 @@
       <c r="E141" s="24">
         <v>14</v>
       </c>
-      <c r="F141" s="33">
+      <c r="F141" s="32">
         <v>15</v>
       </c>
       <c r="G141" s="30">
@@ -4535,9 +4547,9 @@
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="12"/>
-      <c r="B142" s="37"/>
+      <c r="B142" s="36"/>
       <c r="C142" s="9" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D142" s="9" t="s">
         <v>29</v>
@@ -4552,64 +4564,64 @@
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="34"/>
-      <c r="B143" s="37"/>
-      <c r="C143" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="D143" s="37" t="s">
+      <c r="A143" s="33"/>
+      <c r="B143" s="36"/>
+      <c r="C143" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D143" s="36" t="s">
         <v>30</v>
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
-      <c r="G143" s="37"/>
-      <c r="H143" s="37"/>
-      <c r="I143" s="37"/>
+      <c r="G143" s="36"/>
+      <c r="H143" s="36"/>
+      <c r="I143" s="36"/>
       <c r="J143" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" s="34"/>
-      <c r="B144" s="37"/>
-      <c r="C144" s="37" t="s">
+      <c r="A144" s="33"/>
+      <c r="B144" s="36"/>
+      <c r="C144" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D144" s="37" t="s">
+      <c r="D144" s="36" t="s">
         <v>50</v>
       </c>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
-      <c r="G144" s="37"/>
-      <c r="H144" s="37"/>
-      <c r="I144" s="37"/>
+      <c r="G144" s="36"/>
+      <c r="H144" s="36"/>
+      <c r="I144" s="36"/>
       <c r="J144" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" s="34"/>
-      <c r="B145" s="37"/>
-      <c r="C145" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="D145" s="37" t="s">
-        <v>80</v>
+      <c r="A145" s="33"/>
+      <c r="B145" s="36"/>
+      <c r="C145" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D145" s="36" t="s">
+        <v>83</v>
       </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
-      <c r="G145" s="37"/>
-      <c r="H145" s="37"/>
-      <c r="I145" s="37"/>
+      <c r="G145" s="36"/>
+      <c r="H145" s="36"/>
+      <c r="I145" s="36"/>
       <c r="J145" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="B146" s="42">
+        <v>84</v>
+      </c>
+      <c r="B146" s="41">
         <v>9</v>
       </c>
       <c r="C146" s="24">
@@ -4621,7 +4633,7 @@
       <c r="E146" s="24">
         <v>14</v>
       </c>
-      <c r="F146" s="33">
+      <c r="F146" s="32">
         <v>15</v>
       </c>
       <c r="G146" s="30">
@@ -4639,16 +4651,16 @@
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="12"/>
-      <c r="B147" s="37" t="s">
-        <v>104</v>
+      <c r="B147" s="36" t="s">
+        <v>85</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D147" s="9"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
@@ -4658,70 +4670,70 @@
       </c>
     </row>
     <row r="148" spans="1:10">
-      <c r="A148" s="34"/>
-      <c r="B148" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="C148" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="D148" s="37"/>
+      <c r="A148" s="33"/>
+      <c r="B148" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C148" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D148" s="36"/>
       <c r="E148" s="5"/>
       <c r="F148" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G148" s="37"/>
-      <c r="H148" s="37"/>
-      <c r="I148" s="37"/>
+        <v>90</v>
+      </c>
+      <c r="G148" s="36"/>
+      <c r="H148" s="36"/>
+      <c r="I148" s="36"/>
       <c r="J148" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" s="34"/>
-      <c r="B149" s="37" t="s">
+      <c r="A149" s="33"/>
+      <c r="B149" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="C149" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="D149" s="37"/>
+      <c r="C149" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="D149" s="36"/>
       <c r="E149" s="5"/>
       <c r="F149" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G149" s="37"/>
-      <c r="H149" s="37"/>
-      <c r="I149" s="37"/>
+        <v>92</v>
+      </c>
+      <c r="G149" s="36"/>
+      <c r="H149" s="36"/>
+      <c r="I149" s="36"/>
       <c r="J149" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" s="34"/>
-      <c r="B150" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C150" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D150" s="37"/>
+      <c r="A150" s="33"/>
+      <c r="B150" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C150" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="D150" s="36"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G150" s="37"/>
-      <c r="H150" s="37"/>
-      <c r="I150" s="37"/>
+        <v>95</v>
+      </c>
+      <c r="G150" s="36"/>
+      <c r="H150" s="36"/>
+      <c r="I150" s="36"/>
       <c r="J150" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B151" s="42">
+        <v>96</v>
+      </c>
+      <c r="B151" s="41">
         <v>9</v>
       </c>
       <c r="C151" s="24">
@@ -4733,7 +4745,7 @@
       <c r="E151" s="24">
         <v>14</v>
       </c>
-      <c r="F151" s="33">
+      <c r="F151" s="32">
         <v>15</v>
       </c>
       <c r="G151" s="30">
@@ -4751,8 +4763,8 @@
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="12"/>
-      <c r="B152" s="37" t="s">
-        <v>96</v>
+      <c r="B152" s="36" t="s">
+        <v>97</v>
       </c>
       <c r="C152" s="9" t="s">
         <v>29</v>
@@ -4764,7 +4776,7 @@
         <v>98</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G152" s="9" t="s">
         <v>29</v>
@@ -4772,49 +4784,53 @@
       <c r="H152" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I152" s="9"/>
+      <c r="I152" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="J152" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="34"/>
-      <c r="B153" s="37" t="s">
+      <c r="A153" s="33"/>
+      <c r="B153" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C153" s="37" t="s">
+      <c r="C153" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D153" s="37" t="s">
+      <c r="D153" s="36" t="s">
         <v>30</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F153" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G153" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H153" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="G153" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="H153" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="I153" s="37"/>
+      <c r="I153" s="36" t="s">
+        <v>113</v>
+      </c>
       <c r="J153" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="34"/>
-      <c r="B154" s="37" t="s">
+      <c r="A154" s="33"/>
+      <c r="B154" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="C154" s="37" t="s">
+      <c r="C154" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D154" s="37" t="s">
-        <v>87</v>
+      <c r="D154" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>50</v>
@@ -4822,41 +4838,45 @@
       <c r="F154" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G154" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="H154" s="37" t="s">
+      <c r="G154" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H154" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="I154" s="37"/>
+      <c r="I154" s="36" t="s">
+        <v>114</v>
+      </c>
       <c r="J154" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="34"/>
-      <c r="B155" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C155" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D155" s="37" t="s">
-        <v>90</v>
+      <c r="A155" s="33"/>
+      <c r="B155" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C155" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D155" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G155" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="H155" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="I155" s="37"/>
+        <v>109</v>
+      </c>
+      <c r="G155" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="H155" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="I155" s="36" t="s">
+        <v>115</v>
+      </c>
       <c r="J155" t="s">
         <v>1</v>
       </c>

--- a/test.xlsx
+++ b/test.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>01.10.25</t>
   </si>
@@ -441,6 +441,42 @@
   </si>
   <si>
     <t>по сосоп</t>
+  </si>
+  <si>
+    <t>12.11.25</t>
+  </si>
+  <si>
+    <t>13.11.25</t>
+  </si>
+  <si>
+    <t>14.11.25</t>
+  </si>
+  <si>
+    <t>15.11.25</t>
+  </si>
+  <si>
+    <t>16.11.25</t>
+  </si>
+  <si>
+    <t>17.11.25</t>
+  </si>
+  <si>
+    <t>18.11.25</t>
+  </si>
+  <si>
+    <t>19.11.25</t>
+  </si>
+  <si>
+    <t>20.11.25</t>
+  </si>
+  <si>
+    <t>аиао</t>
+  </si>
+  <si>
+    <t>аоаоп</t>
+  </si>
+  <si>
+    <t>попооп</t>
   </si>
 </sst>
 </file>
@@ -1036,9 +1072,9 @@
     <col customWidth="true" max="24" min="24" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:10">
       <c r="A1" s="25" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B1" s="41">
         <v>9</v>
@@ -1068,7 +1104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:10">
       <c r="A2" s="12"/>
       <c r="B2" s="36"/>
       <c r="C2" s="9"/>
@@ -1082,7 +1118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:10">
       <c r="A3" s="33"/>
       <c r="B3" s="36"/>
       <c r="C3" s="36"/>
@@ -1096,7 +1132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:10">
       <c r="A4" s="33"/>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -1110,7 +1146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:10">
       <c r="A5" s="33"/>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -1124,9 +1160,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32">
+    <row r="6" spans="1:10">
       <c r="A6" s="25" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B6" s="41">
         <v>9</v>
@@ -1156,7 +1192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:10">
       <c r="A7" s="12"/>
       <c r="B7" s="36"/>
       <c r="C7" s="9"/>
@@ -1170,7 +1206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:10">
       <c r="A8" s="33"/>
       <c r="B8" s="36"/>
       <c r="C8" s="36"/>
@@ -1184,7 +1220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:10">
       <c r="A9" s="33"/>
       <c r="B9" s="36"/>
       <c r="C9" s="36"/>
@@ -1214,7 +1250,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="25" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B11" s="41">
         <v>9</v>
@@ -1302,7 +1338,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="25" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B16" s="41">
         <v>9</v>
@@ -1335,7 +1371,9 @@
     <row r="17" spans="1:10">
       <c r="A17" s="12"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="9"/>
+      <c r="C17" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="D17" s="9"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -1349,7 +1387,9 @@
     <row r="18" spans="1:10">
       <c r="A18" s="33"/>
       <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
+      <c r="C18" s="36" t="s">
+        <v>38</v>
+      </c>
       <c r="D18" s="36"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -1363,7 +1403,9 @@
     <row r="19" spans="1:10">
       <c r="A19" s="33"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
+      <c r="C19" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="D19" s="36"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -1377,7 +1419,9 @@
     <row r="20" spans="1:10">
       <c r="A20" s="33"/>
       <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
+      <c r="C20" s="36" t="s">
+        <v>40</v>
+      </c>
       <c r="D20" s="36"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -1390,7 +1434,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="25" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B21" s="41">
         <v>9</v>
@@ -1425,7 +1469,9 @@
       <c r="B22" s="36"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="F22" s="5"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
@@ -1439,7 +1485,9 @@
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="F23" s="5"/>
       <c r="G23" s="36"/>
       <c r="H23" s="36"/>
@@ -1453,7 +1501,9 @@
       <c r="B24" s="36"/>
       <c r="C24" s="36"/>
       <c r="D24" s="36"/>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="F24" s="5"/>
       <c r="G24" s="36"/>
       <c r="H24" s="36"/>
@@ -1467,7 +1517,9 @@
       <c r="B25" s="36"/>
       <c r="C25" s="36"/>
       <c r="D25" s="36"/>
-      <c r="E25" s="5"/>
+      <c r="E25" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F25" s="5"/>
       <c r="G25" s="36"/>
       <c r="H25" s="36"/>
@@ -1478,7 +1530,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="25" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B26" s="41">
         <v>9</v>
@@ -1510,9 +1562,15 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="12"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
+      <c r="B27" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="9"/>
@@ -1524,9 +1582,15 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="33"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
+      <c r="B28" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>48</v>
+      </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="36"/>
@@ -1538,9 +1602,15 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="33"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
+      <c r="B29" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>51</v>
+      </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="36"/>
@@ -1552,9 +1622,15 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="33"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
+      <c r="B30" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>54</v>
+      </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="36"/>
@@ -1566,7 +1642,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="25" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B31" s="41">
         <v>9</v>
@@ -1598,10 +1674,18 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="12"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="5"/>
+      <c r="B32" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="F32" s="5"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -1612,10 +1696,18 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="33"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="5"/>
+      <c r="B33" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="F33" s="5"/>
       <c r="G33" s="36"/>
       <c r="H33" s="36"/>
@@ -1626,10 +1718,18 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="33"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="5"/>
+      <c r="B34" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="F34" s="5"/>
       <c r="G34" s="36"/>
       <c r="H34" s="36"/>
@@ -1640,10 +1740,18 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="33"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="5"/>
+      <c r="B35" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="F35" s="5"/>
       <c r="G35" s="36"/>
       <c r="H35" s="36"/>
@@ -1654,7 +1762,7 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="25" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="B36" s="41">
         <v>9</v>
@@ -1687,14 +1795,20 @@
     <row r="37" spans="1:10">
       <c r="A37" s="12"/>
       <c r="B37" s="36"/>
-      <c r="C37" s="9"/>
+      <c r="C37" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="D37" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
+      <c r="H37" s="9" t="s">
+        <v>59</v>
+      </c>
       <c r="I37" s="9"/>
       <c r="J37" t="s">
         <v>1</v>
@@ -1703,14 +1817,20 @@
     <row r="38" spans="1:10">
       <c r="A38" s="33"/>
       <c r="B38" s="36"/>
-      <c r="C38" s="36"/>
+      <c r="C38" s="36" t="s">
+        <v>73</v>
+      </c>
       <c r="D38" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="F38" s="5"/>
       <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
+      <c r="H38" s="36" t="s">
+        <v>30</v>
+      </c>
       <c r="I38" s="36"/>
       <c r="J38" t="s">
         <v>1</v>
@@ -1719,14 +1839,20 @@
     <row r="39" spans="1:10">
       <c r="A39" s="33"/>
       <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
+      <c r="C39" s="36" t="s">
+        <v>65</v>
+      </c>
       <c r="D39" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" s="5"/>
+        <v>74</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="F39" s="5"/>
       <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
+      <c r="H39" s="36" t="s">
+        <v>75</v>
+      </c>
       <c r="I39" s="36"/>
       <c r="J39" t="s">
         <v>1</v>
@@ -1735,14 +1861,20 @@
     <row r="40" spans="1:10">
       <c r="A40" s="33"/>
       <c r="B40" s="36"/>
-      <c r="C40" s="36"/>
+      <c r="C40" s="36" t="s">
+        <v>76</v>
+      </c>
       <c r="D40" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E40" s="5"/>
+        <v>72</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="F40" s="5"/>
       <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
+      <c r="H40" s="36" t="s">
+        <v>78</v>
+      </c>
       <c r="I40" s="36"/>
       <c r="J40" t="s">
         <v>1</v>
@@ -1750,7 +1882,7 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="25" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="B41" s="41">
         <v>9</v>
@@ -1783,8 +1915,12 @@
     <row r="42" spans="1:10">
       <c r="A42" s="12"/>
       <c r="B42" s="36"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
+      <c r="C42" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>29</v>
+      </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="9"/>
@@ -1797,8 +1933,12 @@
     <row r="43" spans="1:10">
       <c r="A43" s="33"/>
       <c r="B43" s="36"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
+      <c r="C43" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>30</v>
+      </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="36"/>
@@ -1811,8 +1951,12 @@
     <row r="44" spans="1:10">
       <c r="A44" s="33"/>
       <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
+      <c r="C44" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>50</v>
+      </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
       <c r="G44" s="36"/>
@@ -1825,8 +1969,12 @@
     <row r="45" spans="1:10">
       <c r="A45" s="33"/>
       <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
+      <c r="C45" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>83</v>
+      </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="36"/>
@@ -1838,7 +1986,7 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="25" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="B46" s="41">
         <v>9</v>
@@ -1870,11 +2018,17 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="12"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="9"/>
+      <c r="B47" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="D47" s="9"/>
       <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
+      <c r="F47" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -1884,11 +2038,17 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="33"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
+      <c r="B48" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>89</v>
+      </c>
       <c r="D48" s="36"/>
       <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="F48" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G48" s="36"/>
       <c r="H48" s="36"/>
       <c r="I48" s="36"/>
@@ -1898,11 +2058,17 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="33"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
+      <c r="B49" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>91</v>
+      </c>
       <c r="D49" s="36"/>
       <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="G49" s="36"/>
       <c r="H49" s="36"/>
       <c r="I49" s="36"/>
@@ -1912,11 +2078,17 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="33"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
+      <c r="B50" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>94</v>
+      </c>
       <c r="D50" s="36"/>
       <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+      <c r="F50" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="G50" s="36"/>
       <c r="H50" s="36"/>
       <c r="I50" s="36"/>
@@ -1926,7 +2098,7 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="25" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="B51" s="41">
         <v>9</v>
@@ -1958,1063 +2130,595 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="12"/>
-      <c r="B52" s="36"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
+      <c r="B52" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="J52" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="33"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
+      <c r="B53" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G53" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H53" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="I53" s="36" t="s">
+        <v>113</v>
+      </c>
       <c r="J53" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="33"/>
-      <c r="B54" s="36"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
+      <c r="B54" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G54" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H54" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I54" s="36" t="s">
+        <v>114</v>
+      </c>
       <c r="J54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="33"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="36"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="36"/>
+      <c r="B55" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G55" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="H55" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="I55" s="36" t="s">
+        <v>115</v>
+      </c>
       <c r="J55" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B56" s="41">
-        <v>9</v>
-      </c>
-      <c r="C56" s="24">
-        <v>10</v>
-      </c>
-      <c r="D56" s="29">
-        <v>11</v>
-      </c>
-      <c r="E56" s="24">
-        <v>14</v>
-      </c>
-      <c r="F56" s="32">
-        <v>15</v>
-      </c>
-      <c r="G56" s="30">
-        <v>16</v>
-      </c>
-      <c r="H56" s="24">
-        <v>17</v>
-      </c>
-      <c r="I56" s="24">
-        <v>18</v>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>116</v>
+      </c>
+      <c r="B56" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" t="s">
+        <v>119</v>
+      </c>
+      <c r="E56" t="s">
+        <v>120</v>
+      </c>
+      <c r="F56" t="s">
+        <v>121</v>
+      </c>
+      <c r="G56" t="s">
+        <v>122</v>
+      </c>
+      <c r="H56" t="s">
+        <v>123</v>
+      </c>
+      <c r="I56" t="s">
+        <v>124</v>
       </c>
       <c r="J56" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="12"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
+    <row r="57">
       <c r="J57" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="33"/>
-      <c r="B58" s="36"/>
-      <c r="C58" s="36"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="36"/>
-      <c r="I58" s="36"/>
+    <row r="58">
       <c r="J58" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="33"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36"/>
+    <row r="59">
       <c r="J59" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="33"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="36"/>
-      <c r="H60" s="36"/>
-      <c r="I60" s="36"/>
+    <row r="60">
       <c r="J60" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="41">
-        <v>9</v>
-      </c>
-      <c r="C61" s="24">
-        <v>10</v>
-      </c>
-      <c r="D61" s="29">
-        <v>11</v>
-      </c>
-      <c r="E61" s="24">
-        <v>14</v>
-      </c>
-      <c r="F61" s="32">
-        <v>15</v>
-      </c>
-      <c r="G61" s="30">
-        <v>16</v>
-      </c>
-      <c r="H61" s="24">
-        <v>17</v>
-      </c>
-      <c r="I61" s="24">
-        <v>18</v>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" t="s">
+        <v>119</v>
+      </c>
+      <c r="E61" t="s">
+        <v>120</v>
+      </c>
+      <c r="F61" t="s">
+        <v>121</v>
+      </c>
+      <c r="G61" t="s">
+        <v>122</v>
+      </c>
+      <c r="H61" t="s">
+        <v>123</v>
+      </c>
+      <c r="I61" t="s">
+        <v>124</v>
       </c>
       <c r="J61" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="12"/>
-      <c r="B62" s="36"/>
-      <c r="C62" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D62" s="9"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
+    <row r="62">
       <c r="J62" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="33"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D63" s="36"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="36"/>
-      <c r="H63" s="36"/>
-      <c r="I63" s="36"/>
+    <row r="63">
       <c r="J63" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="33"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="D64" s="36"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="36"/>
-      <c r="H64" s="36"/>
-      <c r="I64" s="36"/>
+    <row r="64">
       <c r="J64" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
-      <c r="A65" s="33"/>
-      <c r="B65" s="36"/>
-      <c r="C65" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="D65" s="36"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="36"/>
-      <c r="H65" s="36"/>
-      <c r="I65" s="36"/>
+    <row r="65">
       <c r="J65" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
-      <c r="A66" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="41">
-        <v>9</v>
-      </c>
-      <c r="C66" s="24">
-        <v>10</v>
-      </c>
-      <c r="D66" s="29">
-        <v>11</v>
-      </c>
-      <c r="E66" s="24">
-        <v>14</v>
-      </c>
-      <c r="F66" s="32">
-        <v>15</v>
-      </c>
-      <c r="G66" s="30">
-        <v>16</v>
-      </c>
-      <c r="H66" s="24">
-        <v>17</v>
-      </c>
-      <c r="I66" s="24">
-        <v>18</v>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" t="s">
+        <v>117</v>
+      </c>
+      <c r="C66" t="s">
+        <v>118</v>
+      </c>
+      <c r="D66" t="s">
+        <v>119</v>
+      </c>
+      <c r="E66" t="s">
+        <v>120</v>
+      </c>
+      <c r="F66" t="s">
+        <v>121</v>
+      </c>
+      <c r="G66" t="s">
+        <v>122</v>
+      </c>
+      <c r="H66" t="s">
+        <v>123</v>
+      </c>
+      <c r="I66" t="s">
+        <v>124</v>
       </c>
       <c r="J66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
-      <c r="A67" s="12"/>
-      <c r="B67" s="36"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F67" s="5"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="9"/>
+    <row r="67">
       <c r="J67" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
-      <c r="A68" s="33"/>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F68" s="5"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36"/>
+    <row r="68">
       <c r="J68" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
-      <c r="A69" s="33"/>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F69" s="5"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36"/>
-      <c r="I69" s="36"/>
+    <row r="69">
       <c r="J69" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
-      <c r="A70" s="33"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F70" s="5"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
+    <row r="70">
       <c r="J70" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
-      <c r="A71" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B71" s="41">
-        <v>9</v>
-      </c>
-      <c r="C71" s="24">
-        <v>10</v>
-      </c>
-      <c r="D71" s="29">
-        <v>11</v>
-      </c>
-      <c r="E71" s="24">
-        <v>14</v>
-      </c>
-      <c r="F71" s="32">
-        <v>15</v>
-      </c>
-      <c r="G71" s="30">
-        <v>16</v>
-      </c>
-      <c r="H71" s="24">
-        <v>17</v>
-      </c>
-      <c r="I71" s="24">
-        <v>18</v>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>127</v>
+      </c>
+      <c r="B71" t="s">
+        <v>117</v>
+      </c>
+      <c r="C71" t="s">
+        <v>118</v>
+      </c>
+      <c r="D71" t="s">
+        <v>119</v>
+      </c>
+      <c r="E71" t="s">
+        <v>120</v>
+      </c>
+      <c r="F71" t="s">
+        <v>121</v>
+      </c>
+      <c r="G71" t="s">
+        <v>122</v>
+      </c>
+      <c r="H71" t="s">
+        <v>123</v>
+      </c>
+      <c r="I71" t="s">
+        <v>124</v>
       </c>
       <c r="J71" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
-      <c r="A72" s="12"/>
-      <c r="B72" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="9"/>
+    <row r="72">
       <c r="J72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
-      <c r="A73" s="33"/>
-      <c r="B73" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C73" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D73" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="36"/>
-      <c r="H73" s="36"/>
-      <c r="I73" s="36"/>
+    <row r="73">
       <c r="J73" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
-      <c r="A74" s="33"/>
-      <c r="B74" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C74" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="36"/>
-      <c r="I74" s="36"/>
+    <row r="74">
       <c r="J74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
-      <c r="A75" s="33"/>
-      <c r="B75" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D75" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="36"/>
-      <c r="H75" s="36"/>
-      <c r="I75" s="36"/>
+    <row r="75">
       <c r="J75" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
-      <c r="A76" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B76" s="41">
-        <v>9</v>
-      </c>
-      <c r="C76" s="24">
-        <v>10</v>
-      </c>
-      <c r="D76" s="29">
-        <v>11</v>
-      </c>
-      <c r="E76" s="24">
-        <v>14</v>
-      </c>
-      <c r="F76" s="32">
-        <v>15</v>
-      </c>
-      <c r="G76" s="30">
-        <v>16</v>
-      </c>
-      <c r="H76" s="24">
-        <v>17</v>
-      </c>
-      <c r="I76" s="24">
-        <v>18</v>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76" t="s">
+        <v>118</v>
+      </c>
+      <c r="D76" t="s">
+        <v>119</v>
+      </c>
+      <c r="E76" t="s">
+        <v>120</v>
+      </c>
+      <c r="F76" t="s">
+        <v>121</v>
+      </c>
+      <c r="G76" t="s">
+        <v>122</v>
+      </c>
+      <c r="H76" t="s">
+        <v>123</v>
+      </c>
+      <c r="I76" t="s">
+        <v>124</v>
       </c>
       <c r="J76" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
-      <c r="A77" s="12"/>
-      <c r="B77" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F77" s="5"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="9"/>
+    <row r="77">
       <c r="J77" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
-      <c r="A78" s="33"/>
-      <c r="B78" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="C78" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D78" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F78" s="5"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
+    <row r="78">
       <c r="J78" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
-      <c r="A79" s="33"/>
-      <c r="B79" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="C79" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D79" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F79" s="5"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
+    <row r="79">
       <c r="J79" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
-      <c r="A80" s="33"/>
-      <c r="B80" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C80" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="D80" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F80" s="5"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+    <row r="80">
       <c r="J80" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
-      <c r="A81" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B81" s="41">
-        <v>9</v>
-      </c>
-      <c r="C81" s="24">
-        <v>10</v>
-      </c>
-      <c r="D81" s="29">
-        <v>11</v>
-      </c>
-      <c r="E81" s="24">
-        <v>14</v>
-      </c>
-      <c r="F81" s="32">
-        <v>15</v>
-      </c>
-      <c r="G81" s="30">
-        <v>16</v>
-      </c>
-      <c r="H81" s="24">
-        <v>17</v>
-      </c>
-      <c r="I81" s="24">
-        <v>18</v>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>129</v>
+      </c>
+      <c r="B81" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81" t="s">
+        <v>118</v>
+      </c>
+      <c r="D81" t="s">
+        <v>119</v>
+      </c>
+      <c r="E81" t="s">
+        <v>120</v>
+      </c>
+      <c r="F81" t="s">
+        <v>121</v>
+      </c>
+      <c r="G81" t="s">
+        <v>122</v>
+      </c>
+      <c r="H81" t="s">
+        <v>123</v>
+      </c>
+      <c r="I81" t="s">
+        <v>124</v>
       </c>
       <c r="J81" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
-      <c r="A82" s="12"/>
-      <c r="B82" s="36"/>
-      <c r="C82" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F82" s="5"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I82" s="9"/>
+    <row r="82">
       <c r="J82" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
-      <c r="A83" s="33"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="D83" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F83" s="5"/>
-      <c r="G83" s="36"/>
-      <c r="H83" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="I83" s="36"/>
+    <row r="83">
       <c r="J83" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
-      <c r="A84" s="33"/>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="D84" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F84" s="5"/>
-      <c r="G84" s="36"/>
-      <c r="H84" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="I84" s="36"/>
+    <row r="84">
       <c r="J84" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="33"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D85" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F85" s="5"/>
-      <c r="G85" s="36"/>
-      <c r="H85" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="I85" s="36"/>
+    <row r="85">
       <c r="J85" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
-      <c r="A86" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="B86" s="41">
-        <v>9</v>
-      </c>
-      <c r="C86" s="24">
-        <v>10</v>
-      </c>
-      <c r="D86" s="29">
-        <v>11</v>
-      </c>
-      <c r="E86" s="24">
-        <v>14</v>
-      </c>
-      <c r="F86" s="32">
-        <v>15</v>
-      </c>
-      <c r="G86" s="30">
-        <v>16</v>
-      </c>
-      <c r="H86" s="24">
-        <v>17</v>
-      </c>
-      <c r="I86" s="24">
-        <v>18</v>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>130</v>
+      </c>
+      <c r="B86" t="s">
+        <v>117</v>
+      </c>
+      <c r="C86" t="s">
+        <v>118</v>
+      </c>
+      <c r="D86" t="s">
+        <v>119</v>
+      </c>
+      <c r="E86" t="s">
+        <v>120</v>
+      </c>
+      <c r="F86" t="s">
+        <v>121</v>
+      </c>
+      <c r="G86" t="s">
+        <v>122</v>
+      </c>
+      <c r="H86" t="s">
+        <v>123</v>
+      </c>
+      <c r="I86" t="s">
+        <v>124</v>
       </c>
       <c r="J86" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
-      <c r="A87" s="12"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="9"/>
+    <row r="87">
       <c r="J87" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
-      <c r="A88" s="33"/>
-      <c r="B88" s="36"/>
-      <c r="C88" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D88" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="36"/>
-      <c r="H88" s="36"/>
-      <c r="I88" s="36"/>
+    <row r="88">
       <c r="J88" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
-      <c r="A89" s="33"/>
-      <c r="B89" s="36"/>
-      <c r="C89" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D89" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="36"/>
-      <c r="H89" s="36"/>
-      <c r="I89" s="36"/>
+    <row r="89">
       <c r="J89" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
-      <c r="A90" s="33"/>
-      <c r="B90" s="36"/>
-      <c r="C90" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D90" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="36"/>
-      <c r="H90" s="36"/>
-      <c r="I90" s="36"/>
+    <row r="90">
       <c r="J90" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
-      <c r="A91" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="B91" s="41">
-        <v>9</v>
-      </c>
-      <c r="C91" s="24">
-        <v>10</v>
-      </c>
-      <c r="D91" s="29">
-        <v>11</v>
-      </c>
-      <c r="E91" s="24">
-        <v>14</v>
-      </c>
-      <c r="F91" s="32">
-        <v>15</v>
-      </c>
-      <c r="G91" s="30">
-        <v>16</v>
-      </c>
-      <c r="H91" s="24">
-        <v>17</v>
-      </c>
-      <c r="I91" s="24">
-        <v>18</v>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>131</v>
+      </c>
+      <c r="B91" t="s">
+        <v>117</v>
+      </c>
+      <c r="C91" t="s">
+        <v>118</v>
+      </c>
+      <c r="D91" t="s">
+        <v>119</v>
+      </c>
+      <c r="E91" t="s">
+        <v>120</v>
+      </c>
+      <c r="F91" t="s">
+        <v>121</v>
+      </c>
+      <c r="G91" t="s">
+        <v>122</v>
+      </c>
+      <c r="H91" t="s">
+        <v>123</v>
+      </c>
+      <c r="I91" t="s">
+        <v>124</v>
       </c>
       <c r="J91" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
-      <c r="A92" s="12"/>
-      <c r="B92" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C92" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D92" s="9"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="9"/>
+    <row r="92">
       <c r="J92" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
-      <c r="A93" s="33"/>
-      <c r="B93" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C93" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D93" s="36"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G93" s="36"/>
-      <c r="H93" s="36"/>
-      <c r="I93" s="36"/>
+    <row r="93">
       <c r="J93" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
-      <c r="A94" s="33"/>
-      <c r="B94" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C94" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="D94" s="36"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G94" s="36"/>
-      <c r="H94" s="36"/>
-      <c r="I94" s="36"/>
+    <row r="94">
       <c r="J94" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
-      <c r="A95" s="33"/>
-      <c r="B95" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="C95" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="D95" s="36"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G95" s="36"/>
-      <c r="H95" s="36"/>
-      <c r="I95" s="36"/>
+    <row r="95">
       <c r="J95" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
-      <c r="A96" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B96" s="41">
-        <v>9</v>
-      </c>
-      <c r="C96" s="24">
-        <v>10</v>
-      </c>
-      <c r="D96" s="29">
-        <v>11</v>
-      </c>
-      <c r="E96" s="24">
-        <v>14</v>
-      </c>
-      <c r="F96" s="32">
-        <v>15</v>
-      </c>
-      <c r="G96" s="30">
-        <v>16</v>
-      </c>
-      <c r="H96" s="24">
-        <v>17</v>
-      </c>
-      <c r="I96" s="24">
-        <v>18</v>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>132</v>
+      </c>
+      <c r="B96" t="s">
+        <v>117</v>
+      </c>
+      <c r="C96" t="s">
+        <v>118</v>
+      </c>
+      <c r="D96" t="s">
+        <v>119</v>
+      </c>
+      <c r="E96" t="s">
+        <v>120</v>
+      </c>
+      <c r="F96" t="s">
+        <v>121</v>
+      </c>
+      <c r="G96" t="s">
+        <v>122</v>
+      </c>
+      <c r="H96" t="s">
+        <v>123</v>
+      </c>
+      <c r="I96" t="s">
+        <v>124</v>
       </c>
       <c r="J96" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
-      <c r="A97" s="12"/>
-      <c r="B97" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>112</v>
-      </c>
+    <row r="97">
       <c r="J97" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
-      <c r="A98" s="33"/>
-      <c r="B98" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C98" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D98" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G98" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="H98" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="I98" s="36" t="s">
-        <v>113</v>
-      </c>
+    <row r="98">
       <c r="J98" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
-      <c r="A99" s="33"/>
-      <c r="B99" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C99" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D99" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G99" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H99" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="I99" s="36" t="s">
-        <v>114</v>
-      </c>
+    <row r="99">
       <c r="J99" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
-      <c r="A100" s="33"/>
-      <c r="B100" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="C100" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D100" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G100" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="H100" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="I100" s="36" t="s">
-        <v>115</v>
-      </c>
+    <row r="100">
       <c r="J100" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B101" t="s">
         <v>117</v>
@@ -3045,28 +2749,40 @@
       </c>
     </row>
     <row r="102">
+      <c r="E102" t="s">
+        <v>135</v>
+      </c>
       <c r="J102" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="103">
+      <c r="E103" t="s">
+        <v>98</v>
+      </c>
       <c r="J103" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="104">
+      <c r="E104" t="s">
+        <v>50</v>
+      </c>
       <c r="J104" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="105">
+      <c r="E105" t="s">
+        <v>136</v>
+      </c>
       <c r="J105" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B106" t="s">
         <v>117</v>
@@ -3118,7 +2834,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B111" t="s">
         <v>117</v>
@@ -3170,7 +2886,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B116" t="s">
         <v>117</v>
@@ -3222,7 +2938,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B121" t="s">
         <v>117</v>
@@ -3274,7 +2990,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B126" t="s">
         <v>117</v>
@@ -3326,7 +3042,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B131" t="s">
         <v>117</v>
@@ -3378,7 +3094,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B136" t="s">
         <v>117</v>
@@ -3430,7 +3146,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B141" t="s">
         <v>117</v>
@@ -3482,7 +3198,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B146" t="s">
         <v>117</v>
@@ -3513,23 +3229,23 @@
       </c>
     </row>
     <row r="147">
-      <c r="E147" t="s">
-        <v>135</v>
+      <c r="H147" t="s">
+        <v>146</v>
       </c>
       <c r="J147" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="148">
-      <c r="E148" t="s">
-        <v>98</v>
+      <c r="H148" t="s">
+        <v>147</v>
       </c>
       <c r="J148" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="149">
-      <c r="E149" t="s">
+      <c r="H149" t="s">
         <v>50</v>
       </c>
       <c r="J149" t="s">
@@ -3537,8 +3253,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="E150" t="s">
-        <v>136</v>
+      <c r="H150" t="s">
+        <v>148</v>
       </c>
       <c r="J150" t="s">
         <v>1</v>
@@ -3546,7 +3262,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B151" t="s">
         <v>117</v>

--- a/test.xlsx
+++ b/test.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>|</t>
   </si>
@@ -274,6 +274,39 @@
   </si>
   <si>
     <t>15.11.25</t>
+  </si>
+  <si>
+    <t>молм</t>
+  </si>
+  <si>
+    <t>мтст</t>
+  </si>
+  <si>
+    <t>мллм</t>
+  </si>
+  <si>
+    <t>момо</t>
+  </si>
+  <si>
+    <t>89157457546</t>
+  </si>
+  <si>
+    <t>аос</t>
+  </si>
+  <si>
+    <t>пиблс</t>
+  </si>
+  <si>
+    <t>пибловский</t>
+  </si>
+  <si>
+    <t>+79054763212</t>
+  </si>
+  <si>
+    <t>клинмайбели</t>
+  </si>
+  <si>
+    <t>мтм</t>
   </si>
 </sst>
 </file>
@@ -2003,12 +2036,16 @@
       <c r="A72" s="3"/>
       <c r="B72" s="10"/>
       <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
+      <c r="D72" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G72" s="2"/>
+      <c r="G72" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" t="s">
@@ -2019,12 +2056,16 @@
       <c r="A73" s="9"/>
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
+      <c r="D73" s="10" t="s">
+        <v>95</v>
+      </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G73" s="10"/>
+      <c r="G73" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="H73" s="10"/>
       <c r="I73" s="10"/>
       <c r="J73" t="s">
@@ -2035,12 +2076,16 @@
       <c r="A74" s="9"/>
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
+      <c r="D74" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G74" s="10"/>
+      <c r="G74" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="H74" s="10"/>
       <c r="I74" s="10"/>
       <c r="J74" t="s">
@@ -2051,12 +2096,16 @@
       <c r="A75" s="9"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
+      <c r="D75" s="10" t="s">
+        <v>78</v>
+      </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G75" s="10"/>
+      <c r="G75" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="H75" s="10"/>
       <c r="I75" s="10"/>
       <c r="J75" t="s">
@@ -2897,7 +2946,7 @@
     </row>
     <row r="142" spans="1:10">
       <c r="D142" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J142" t="s">
         <v>0</v>
@@ -2905,7 +2954,7 @@
     </row>
     <row r="143" spans="1:10">
       <c r="D143" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J143" t="s">
         <v>0</v>
@@ -2913,7 +2962,7 @@
     </row>
     <row r="144" spans="1:10">
       <c r="D144" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="J144" t="s">
         <v>0</v>
@@ -2921,7 +2970,7 @@
     </row>
     <row r="145" spans="1:10">
       <c r="D145" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J145" t="s">
         <v>0</v>

--- a/test.xlsx
+++ b/test.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>01.10.25</t>
   </si>
@@ -417,6 +417,12 @@
   </si>
   <si>
     <t>02.12.25</t>
+  </si>
+  <si>
+    <t>03.12.25</t>
+  </si>
+  <si>
+    <t>04.12.25</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1020,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
         <v>90</v>
@@ -1066,7 +1072,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
         <v>90</v>
@@ -1118,7 +1124,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
         <v>90</v>
@@ -1170,7 +1176,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
         <v>90</v>
@@ -1222,7 +1228,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B21" t="s">
         <v>90</v>
@@ -1274,7 +1280,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B26" t="s">
         <v>90</v>
@@ -1326,7 +1332,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
         <v>90</v>
@@ -1378,7 +1384,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
         <v>90</v>
@@ -1430,7 +1436,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
         <v>90</v>
@@ -1482,7 +1488,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B46" t="s">
         <v>90</v>
@@ -1534,7 +1540,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
         <v>90</v>
@@ -1586,7 +1592,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
         <v>90</v>
@@ -1638,7 +1644,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B61" t="s">
         <v>90</v>
@@ -1690,7 +1696,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B66" t="s">
         <v>90</v>
@@ -1742,7 +1748,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B71" t="s">
         <v>90</v>
@@ -1794,7 +1800,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B76" t="s">
         <v>90</v>
@@ -1846,7 +1852,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B81" t="s">
         <v>90</v>
@@ -1898,7 +1904,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B86" t="s">
         <v>90</v>
@@ -1950,7 +1956,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B91" t="s">
         <v>90</v>
@@ -2002,7 +2008,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B96" t="s">
         <v>90</v>
@@ -2054,7 +2060,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B101" t="s">
         <v>90</v>
@@ -2106,7 +2112,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B106" t="s">
         <v>90</v>
@@ -2158,7 +2164,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B111" t="s">
         <v>90</v>
@@ -2210,7 +2216,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B116" t="s">
         <v>90</v>
@@ -2262,7 +2268,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B121" t="s">
         <v>90</v>
@@ -2314,7 +2320,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B126" t="s">
         <v>90</v>
@@ -2366,7 +2372,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B131" t="s">
         <v>90</v>
@@ -2418,7 +2424,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B136" t="s">
         <v>90</v>
@@ -2470,7 +2476,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B141" t="s">
         <v>90</v>
@@ -2522,7 +2528,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B146" t="s">
         <v>90</v>
@@ -2574,7 +2580,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B151" t="s">
         <v>90</v>

--- a/test.xlsx
+++ b/test.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>01.10.25</t>
   </si>
@@ -423,6 +423,18 @@
   </si>
   <si>
     <t>04.12.25</t>
+  </si>
+  <si>
+    <t>оал</t>
+  </si>
+  <si>
+    <t>рпщ</t>
+  </si>
+  <si>
+    <t>ос</t>
+  </si>
+  <si>
+    <t>05.12.25</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1032,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
         <v>90</v>
@@ -1072,7 +1084,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s">
         <v>90</v>
@@ -1124,7 +1136,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
         <v>90</v>
@@ -1176,7 +1188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B16" t="s">
         <v>90</v>
@@ -1207,28 +1219,52 @@
       </c>
     </row>
     <row r="17">
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
       <c r="J17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18">
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
       <c r="J18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19">
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
       <c r="J19" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20">
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
       <c r="J20" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B21" t="s">
         <v>90</v>
@@ -1280,7 +1316,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" t="s">
         <v>90</v>
@@ -1332,7 +1368,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
         <v>90</v>
@@ -1384,7 +1420,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
         <v>90</v>
@@ -1436,7 +1472,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
         <v>90</v>
@@ -1488,7 +1524,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B46" t="s">
         <v>90</v>
@@ -1540,7 +1576,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
         <v>90</v>
@@ -1592,7 +1628,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B56" t="s">
         <v>90</v>
@@ -1644,7 +1680,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B61" t="s">
         <v>90</v>
@@ -1696,7 +1732,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B66" t="s">
         <v>90</v>
@@ -1748,7 +1784,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B71" t="s">
         <v>90</v>
@@ -1800,7 +1836,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B76" t="s">
         <v>90</v>
@@ -1852,7 +1888,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B81" t="s">
         <v>90</v>
@@ -1904,7 +1940,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B86" t="s">
         <v>90</v>
@@ -1956,7 +1992,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B91" t="s">
         <v>90</v>
@@ -2008,7 +2044,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B96" t="s">
         <v>90</v>
@@ -2060,7 +2096,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B101" t="s">
         <v>90</v>
@@ -2112,7 +2148,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B106" t="s">
         <v>90</v>
@@ -2164,7 +2200,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B111" t="s">
         <v>90</v>
@@ -2216,7 +2252,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B116" t="s">
         <v>90</v>
@@ -2268,7 +2304,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B121" t="s">
         <v>90</v>
@@ -2320,7 +2356,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B126" t="s">
         <v>90</v>
@@ -2372,7 +2408,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B131" t="s">
         <v>90</v>
@@ -2424,7 +2460,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B136" t="s">
         <v>90</v>
@@ -2476,7 +2512,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B141" t="s">
         <v>90</v>
@@ -2528,7 +2564,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B146" t="s">
         <v>90</v>
@@ -2580,7 +2616,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B151" t="s">
         <v>90</v>
